--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanos\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.natsikas\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FFAA41-C22E-4A88-85D4-52AAADADEB83}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF06D0C8-D14D-42E3-B664-E4F6B0C867F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,8 +26,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Read Settings'!$A$1:$I$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Time Settings'!$A$1:$J$120</definedName>
   </definedNames>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -1198,7 +1209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="341">
   <si>
     <t>Report Name</t>
   </si>
@@ -1753,9 +1764,6 @@
     <t>Sheet Tags</t>
   </si>
   <si>
-    <t>Header Row</t>
-  </si>
-  <si>
     <t>Use Cols</t>
   </si>
   <si>
@@ -2222,6 +2230,12 @@
   </si>
   <si>
     <t>Resolution</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -2775,133 +2789,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="147">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="115">
     <dxf>
       <fill>
         <patternFill>
@@ -3234,104 +3122,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
@@ -3430,7 +3220,160 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3479,89 +3422,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
@@ -3584,76 +3444,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3737,14 +3527,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF93CDDD"/>
+          <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF99"/>
+          <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3786,6 +3576,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
@@ -3794,20 +3598,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3893,9 +3683,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3933,7 +3723,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4039,7 +3829,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4181,7 +3971,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4739,16 +4529,14 @@
       <c r="F16" s="40">
         <v>44238</v>
       </c>
-      <c r="G16" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G16" s="47"/>
       <c r="H16" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I16" s="7" t="b">
         <f>IF(Metadata!G16="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="13" t="b">
         <f>TRUE()</f>
@@ -5261,7 +5049,7 @@
         <v>42005</v>
       </c>
       <c r="G31" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H31" s="8" t="b">
         <f>TRUE()</f>
@@ -5328,10 +5116,10 @@
         <v>176</v>
       </c>
       <c r="F33" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G33" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H33" s="8" t="b">
         <f>TRUE()</f>
@@ -5363,10 +5151,10 @@
         <v>176</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G34" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H34" s="8" t="b">
         <f>TRUE()</f>
@@ -5398,10 +5186,10 @@
         <v>176</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G35" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H35" s="8" t="b">
         <f>TRUE()</f>
@@ -5433,10 +5221,10 @@
         <v>176</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G36" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H36" s="8" t="b">
         <f>TRUE()</f>
@@ -5470,10 +5258,10 @@
         <v>176</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G37" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H37" s="8" t="b">
         <f>TRUE()</f>
@@ -5505,10 +5293,10 @@
         <v>176</v>
       </c>
       <c r="F38" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G38" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H38" s="8" t="b">
         <f>TRUE()</f>
@@ -5540,10 +5328,10 @@
         <v>176</v>
       </c>
       <c r="F39" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G39" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H39" s="8" t="b">
         <f>TRUE()</f>
@@ -5575,10 +5363,10 @@
         <v>176</v>
       </c>
       <c r="F40" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G40" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H40" s="8" t="b">
         <f>TRUE()</f>
@@ -5612,10 +5400,10 @@
         <v>176</v>
       </c>
       <c r="F41" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G41" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H41" s="8" t="b">
         <f>TRUE()</f>
@@ -5647,10 +5435,10 @@
         <v>176</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G42" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H42" s="8" t="b">
         <f>TRUE()</f>
@@ -5682,10 +5470,10 @@
         <v>176</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G43" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H43" s="8" t="b">
         <f>TRUE()</f>
@@ -5717,10 +5505,10 @@
         <v>176</v>
       </c>
       <c r="F44" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G44" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H44" s="8" t="b">
         <f>TRUE()</f>
@@ -5741,7 +5529,7 @@
     </row>
     <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8" t="s">
@@ -5754,7 +5542,7 @@
         <v>176</v>
       </c>
       <c r="F45" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G45" s="47"/>
       <c r="H45" s="8" t="b">
@@ -5774,7 +5562,7 @@
     </row>
     <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="8" t="s">
@@ -5787,7 +5575,7 @@
         <v>176</v>
       </c>
       <c r="F46" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G46" s="47">
         <v>45930</v>
@@ -5809,7 +5597,7 @@
     </row>
     <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="8" t="s">
@@ -5822,7 +5610,7 @@
         <v>176</v>
       </c>
       <c r="F47" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G47" s="47"/>
       <c r="H47" s="8" t="b">
@@ -5842,7 +5630,7 @@
     </row>
     <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="8" t="s">
@@ -5855,7 +5643,7 @@
         <v>176</v>
       </c>
       <c r="F48" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G48" s="47">
         <v>45930</v>
@@ -5877,7 +5665,7 @@
     </row>
     <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="8" t="s">
@@ -5890,7 +5678,7 @@
         <v>176</v>
       </c>
       <c r="F49" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G49" s="47"/>
       <c r="H49" s="8" t="b">
@@ -5910,7 +5698,7 @@
     </row>
     <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="8" t="s">
@@ -5923,7 +5711,7 @@
         <v>176</v>
       </c>
       <c r="F50" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G50" s="47">
         <v>45930</v>
@@ -5945,7 +5733,7 @@
     </row>
     <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="8" t="s">
@@ -5958,7 +5746,7 @@
         <v>176</v>
       </c>
       <c r="F51" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G51" s="47"/>
       <c r="H51" s="8" t="b">
@@ -5978,7 +5766,7 @@
     </row>
     <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
@@ -5991,7 +5779,7 @@
         <v>176</v>
       </c>
       <c r="F52" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G52" s="47">
         <v>45930</v>
@@ -6013,7 +5801,7 @@
     </row>
     <row r="53" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="8" t="s">
@@ -6026,7 +5814,7 @@
         <v>176</v>
       </c>
       <c r="F53" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G53" s="47"/>
       <c r="H53" s="8" t="b">
@@ -6046,7 +5834,7 @@
     </row>
     <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="8" t="s">
@@ -6059,7 +5847,7 @@
         <v>176</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G54" s="47">
         <v>45930</v>
@@ -6081,7 +5869,7 @@
     </row>
     <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="8" t="s">
@@ -6094,7 +5882,7 @@
         <v>176</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G55" s="47"/>
       <c r="H55" s="8" t="b">
@@ -6114,7 +5902,7 @@
     </row>
     <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="8" t="s">
@@ -6127,7 +5915,7 @@
         <v>176</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G56" s="47">
         <v>45930</v>
@@ -6165,7 +5953,7 @@
         <v>43841</v>
       </c>
       <c r="G57" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H57" s="8" t="b">
         <f>TRUE()</f>
@@ -6200,7 +5988,7 @@
         <v>43841</v>
       </c>
       <c r="G58" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H58" s="8" t="b">
         <f>TRUE()</f>
@@ -6237,7 +6025,7 @@
         <v>43841</v>
       </c>
       <c r="G59" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H59" s="8" t="b">
         <f>TRUE()</f>
@@ -6272,7 +6060,7 @@
         <v>43841</v>
       </c>
       <c r="G60" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H60" s="8" t="b">
         <f>TRUE()</f>
@@ -6309,7 +6097,7 @@
         <v>43841</v>
       </c>
       <c r="G61" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H61" s="8" t="b">
         <f>TRUE()</f>
@@ -6344,7 +6132,7 @@
         <v>43841</v>
       </c>
       <c r="G62" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H62" s="8" t="b">
         <f>TRUE()</f>
@@ -6381,7 +6169,7 @@
         <v>43841</v>
       </c>
       <c r="G63" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H63" s="8" t="b">
         <f>TRUE()</f>
@@ -6416,7 +6204,7 @@
         <v>43841</v>
       </c>
       <c r="G64" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H64" s="8" t="b">
         <f>TRUE()</f>
@@ -6453,7 +6241,7 @@
         <v>43841</v>
       </c>
       <c r="G65" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H65" s="8" t="b">
         <f>TRUE()</f>
@@ -6488,7 +6276,7 @@
         <v>43841</v>
       </c>
       <c r="G66" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H66" s="8" t="b">
         <f>TRUE()</f>
@@ -6525,7 +6313,7 @@
         <v>43841</v>
       </c>
       <c r="G67" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H67" s="8" t="b">
         <f>TRUE()</f>
@@ -6560,7 +6348,7 @@
         <v>43841</v>
       </c>
       <c r="G68" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H68" s="8" t="b">
         <f>TRUE()</f>
@@ -7451,7 +7239,7 @@
         <v>1</v>
       </c>
       <c r="J94" s="13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" s="14"/>
       <c r="L94" s="15"/>
@@ -10884,460 +10672,320 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L120" xr:uid="{D0972C50-907B-4A2C-82F0-ED51F06329AA}">
-    <sortState ref="A2:L120">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L120">
       <sortCondition ref="A2:A120"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A103">
-    <cfRule type="expression" dxfId="146" priority="116">
+    <cfRule type="expression" dxfId="114" priority="117">
+      <formula>ROW()=CELL("row")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="116">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="117">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A104">
+    <cfRule type="expression" dxfId="112" priority="113">
+      <formula>COLUMN()=CELL("col")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="111" priority="112">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A104">
-    <cfRule type="expression" dxfId="144" priority="112">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="143" priority="113">
+  <conditionalFormatting sqref="A106">
+    <cfRule type="expression" dxfId="110" priority="56">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A106">
-    <cfRule type="expression" dxfId="142" priority="56">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="141" priority="57">
+    <cfRule type="expression" dxfId="109" priority="57">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="expression" dxfId="140" priority="52">
+    <cfRule type="expression" dxfId="108" priority="52">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="139" priority="53">
+    <cfRule type="expression" dxfId="107" priority="53">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78:C81">
-    <cfRule type="expression" dxfId="138" priority="287">
+    <cfRule type="expression" dxfId="106" priority="287">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102:C102">
-    <cfRule type="expression" dxfId="137" priority="152">
+    <cfRule type="expression" dxfId="105" priority="153">
+      <formula>ROW()=CELL("row")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="152">
       <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="136" priority="153">
-      <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102:C104">
-    <cfRule type="expression" dxfId="135" priority="114">
+    <cfRule type="expression" dxfId="103" priority="114">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105:C105">
-    <cfRule type="expression" dxfId="134" priority="99">
+    <cfRule type="expression" dxfId="102" priority="99">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="100">
+    <cfRule type="expression" dxfId="101" priority="100">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:D101">
-    <cfRule type="expression" dxfId="132" priority="168">
+    <cfRule type="expression" dxfId="100" priority="168">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108:D111">
-    <cfRule type="expression" dxfId="131" priority="288">
+    <cfRule type="expression" dxfId="99" priority="288">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112:D300">
-    <cfRule type="expression" dxfId="130" priority="40">
+    <cfRule type="expression" dxfId="98" priority="40">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:E101">
-    <cfRule type="expression" dxfId="129" priority="167">
+    <cfRule type="expression" dxfId="97" priority="167">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:E101">
-    <cfRule type="expression" dxfId="128" priority="165">
+    <cfRule type="expression" dxfId="96" priority="165">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105:E107">
-    <cfRule type="expression" dxfId="127" priority="54">
+    <cfRule type="expression" dxfId="95" priority="54">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112:E300">
-    <cfRule type="expression" dxfId="126" priority="37">
+    <cfRule type="expression" dxfId="94" priority="37">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="39">
+    <cfRule type="expression" dxfId="93" priority="39">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B103:C104">
-    <cfRule type="expression" dxfId="124" priority="122">
+    <cfRule type="expression" dxfId="92" priority="123">
+      <formula>ROW()=CELL("row")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="91" priority="122">
       <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="123" priority="123">
-      <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C107">
-    <cfRule type="expression" dxfId="122" priority="71">
+    <cfRule type="expression" dxfId="90" priority="72">
+      <formula>ROW()=CELL("row")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="71">
       <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="121" priority="72">
-      <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78:D82">
-    <cfRule type="expression" dxfId="120" priority="342">
+    <cfRule type="expression" dxfId="88" priority="342">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D102:D104">
-    <cfRule type="expression" dxfId="119" priority="110">
+    <cfRule type="expression" dxfId="87" priority="110">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D102:D107">
-    <cfRule type="expression" dxfId="118" priority="60">
+    <cfRule type="expression" dxfId="86" priority="60">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D102:E104">
-    <cfRule type="expression" dxfId="117" priority="111">
+    <cfRule type="expression" dxfId="85" priority="111">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105:E107">
-    <cfRule type="expression" dxfId="116" priority="59">
+    <cfRule type="expression" dxfId="84" priority="59">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E102:E104">
-    <cfRule type="expression" dxfId="115" priority="126">
+    <cfRule type="expression" dxfId="83" priority="126">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:H12 F21:H44 F13:F20 H13:H20 F57:H68 F45:F56 H45:H56 F71:H72 F69:F70 H69:H70 F88:H88 F73:F87 H73:H87 F91:H107 F89:F90 H89:H90">
-    <cfRule type="expression" dxfId="114" priority="50">
+  <conditionalFormatting sqref="F3:H107">
+    <cfRule type="expression" dxfId="82" priority="2">
+      <formula>COLUMN()=CELL("col")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="1">
       <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="51">
-      <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112:H120 F121:I300">
-    <cfRule type="expression" dxfId="112" priority="35">
+    <cfRule type="expression" dxfId="80" priority="36">
+      <formula>COLUMN()=CELL("col")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="35">
       <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="111" priority="36">
-      <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:I2 I3:I120 A108:H111">
-    <cfRule type="expression" dxfId="110" priority="259">
+    <cfRule type="expression" dxfId="78" priority="259">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:I2 I3:I120 A108:H111">
-    <cfRule type="expression" dxfId="109" priority="258">
+    <cfRule type="expression" dxfId="77" priority="258">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H78:H81">
-    <cfRule type="expression" dxfId="108" priority="357">
+    <cfRule type="expression" dxfId="76" priority="357">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H88:H107">
-    <cfRule type="expression" dxfId="107" priority="76">
+    <cfRule type="expression" dxfId="75" priority="76">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H108:H111">
-    <cfRule type="expression" dxfId="106" priority="358">
+    <cfRule type="expression" dxfId="74" priority="358">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H112:H120 H121:I300">
-    <cfRule type="expression" dxfId="105" priority="45">
+    <cfRule type="expression" dxfId="73" priority="45">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J300">
-    <cfRule type="cellIs" dxfId="104" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="34" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="33" operator="equal">
       <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="34" operator="equal">
-      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L98 K108:L111">
-    <cfRule type="expression" dxfId="102" priority="386">
+    <cfRule type="expression" dxfId="70" priority="386">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:L99">
-    <cfRule type="expression" dxfId="101" priority="205">
+    <cfRule type="expression" dxfId="69" priority="205">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78:L81">
-    <cfRule type="expression" dxfId="100" priority="387">
+    <cfRule type="expression" dxfId="68" priority="387">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K88:L98 K108:L111">
-    <cfRule type="expression" dxfId="99" priority="388">
+    <cfRule type="expression" dxfId="67" priority="388">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:L99">
-    <cfRule type="expression" dxfId="98" priority="204">
+    <cfRule type="expression" dxfId="66" priority="204">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:L101">
-    <cfRule type="expression" dxfId="97" priority="175">
+    <cfRule type="expression" dxfId="65" priority="175">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K100:L100">
-    <cfRule type="expression" dxfId="96" priority="166">
+    <cfRule type="expression" dxfId="64" priority="174">
+      <formula>COLUMN()=CELL("col")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="166">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="95" priority="174">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K101:L101">
+    <cfRule type="expression" dxfId="62" priority="190">
+      <formula>ROW()=CELL("row")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="189">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K101:L101">
-    <cfRule type="expression" dxfId="94" priority="189">
+  <conditionalFormatting sqref="K102:L102">
+    <cfRule type="expression" dxfId="60" priority="159">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="190">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K102:L102">
-    <cfRule type="expression" dxfId="92" priority="159">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="160">
+    <cfRule type="expression" dxfId="59" priority="160">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K102:L104">
-    <cfRule type="expression" dxfId="90" priority="130">
+    <cfRule type="expression" dxfId="58" priority="130">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K103:L103">
-    <cfRule type="expression" dxfId="89" priority="121">
+    <cfRule type="expression" dxfId="57" priority="121">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="129">
+    <cfRule type="expression" dxfId="56" priority="129">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K104:L104">
-    <cfRule type="expression" dxfId="87" priority="144">
+    <cfRule type="expression" dxfId="55" priority="144">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="145">
+    <cfRule type="expression" dxfId="54" priority="145">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K105:L105">
-    <cfRule type="expression" dxfId="85" priority="105">
+    <cfRule type="expression" dxfId="53" priority="105">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="106">
+    <cfRule type="expression" dxfId="52" priority="106">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K105:L107">
-    <cfRule type="expression" dxfId="83" priority="78">
+    <cfRule type="expression" dxfId="51" priority="78">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K106:L106">
-    <cfRule type="expression" dxfId="82" priority="70">
+    <cfRule type="expression" dxfId="50" priority="70">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="77">
+    <cfRule type="expression" dxfId="49" priority="77">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107:L107">
-    <cfRule type="expression" dxfId="80" priority="91">
+    <cfRule type="expression" dxfId="48" priority="91">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107:L111">
-    <cfRule type="expression" dxfId="79" priority="92">
+    <cfRule type="expression" dxfId="47" priority="92">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K112:L300">
-    <cfRule type="expression" dxfId="78" priority="38">
+    <cfRule type="expression" dxfId="46" priority="47">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="46">
+    <cfRule type="expression" dxfId="45" priority="46">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="47">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="75" priority="32">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="74" priority="31">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G14:G20">
-    <cfRule type="expression" dxfId="73" priority="30">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G14:G20">
-    <cfRule type="expression" dxfId="72" priority="29">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G45 G49 G53 G51 G55">
-    <cfRule type="expression" dxfId="71" priority="28">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G45 G49 G53 G51 G55">
-    <cfRule type="expression" dxfId="70" priority="27">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G69">
-    <cfRule type="expression" dxfId="69" priority="26">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G69">
-    <cfRule type="expression" dxfId="68" priority="25">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G70">
-    <cfRule type="expression" dxfId="67" priority="24">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G70">
-    <cfRule type="expression" dxfId="66" priority="23">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G73:G87">
-    <cfRule type="expression" dxfId="65" priority="22">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G73:G87">
-    <cfRule type="expression" dxfId="64" priority="21">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G89:G90">
-    <cfRule type="expression" dxfId="63" priority="20">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G89:G90">
-    <cfRule type="expression" dxfId="62" priority="19">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G47">
-    <cfRule type="expression" dxfId="17" priority="18">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G47">
-    <cfRule type="expression" dxfId="16" priority="17">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G46">
-    <cfRule type="expression" dxfId="11" priority="12">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G46">
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G48">
-    <cfRule type="expression" dxfId="9" priority="10">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G48">
-    <cfRule type="expression" dxfId="8" priority="9">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G50">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G50">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G54">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G54">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G56">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G56">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G52">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G52">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="44" priority="38">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11383,10 +11031,10 @@
         <v>182</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -11398,18 +11046,18 @@
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D2" s="18"/>
       <c r="E2" s="18"/>
       <c r="F2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="H2" s="12">
-        <v>0</v>
+      <c r="H2" s="12" t="s">
+        <v>340</v>
       </c>
       <c r="I2" s="19"/>
     </row>
@@ -11454,15 +11102,15 @@
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>188</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>189</v>
       </c>
       <c r="H5" s="12">
         <v>0</v>
@@ -11478,15 +11126,15 @@
         <v>1</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H6" s="12">
         <v>0</v>
@@ -11502,7 +11150,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
@@ -11520,7 +11168,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
@@ -11538,7 +11186,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
@@ -11556,15 +11204,15 @@
         <v>1</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
       <c r="F10" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H10" s="12">
         <v>0</v>
@@ -11580,21 +11228,21 @@
         <v>1</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H11" s="12">
         <v>0</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -11622,15 +11270,15 @@
         <v>1</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H13" s="12">
         <v>0</v>
@@ -11646,15 +11294,15 @@
         <v>1</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H14" s="12">
         <v>0</v>
@@ -11670,15 +11318,15 @@
         <v>1</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H15" s="12">
         <v>0</v>
@@ -11694,15 +11342,15 @@
         <v>1</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="H16" s="12">
         <v>0</v>
@@ -11718,21 +11366,21 @@
         <v>1</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G17" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>197</v>
-      </c>
-      <c r="H17" s="12">
-        <v>0</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -11744,15 +11392,15 @@
         <v>1</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H18" s="12">
         <v>1</v>
@@ -11768,21 +11416,21 @@
         <v>1</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H19" s="12">
         <v>0</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -11794,23 +11442,23 @@
         <v>1</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G20" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H20" s="12">
+        <v>1</v>
+      </c>
+      <c r="I20" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="H20" s="12">
-        <v>1</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -11822,15 +11470,15 @@
         <v>1</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
       <c r="F21" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>207</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>208</v>
       </c>
       <c r="H21" s="12">
         <v>0</v>
@@ -11846,15 +11494,15 @@
         <v>1</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
       <c r="F22" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H22" s="12">
         <v>2</v>
@@ -11870,15 +11518,15 @@
         <v>1</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H23" s="12">
         <v>1</v>
@@ -11894,7 +11542,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
@@ -11928,21 +11576,21 @@
         <v>1</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
       <c r="F26" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H26" s="12">
         <v>2</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -11986,21 +11634,21 @@
         <v>1</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D29" s="18"/>
       <c r="E29" s="18"/>
       <c r="F29" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G29" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H29" s="12">
+        <v>0</v>
+      </c>
+      <c r="I29" s="12" t="s">
         <v>212</v>
-      </c>
-      <c r="H29" s="12">
-        <v>0</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -12044,23 +11692,23 @@
         <v>1</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E32" s="18"/>
       <c r="F32" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G32" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="H32" s="12">
+        <v>0</v>
+      </c>
+      <c r="I32" s="12" t="s">
         <v>215</v>
-      </c>
-      <c r="H32" s="12">
-        <v>0</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
@@ -12072,15 +11720,15 @@
         <v>1</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H33" s="12">
         <v>0</v>
@@ -12096,15 +11744,15 @@
         <v>1</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D34" s="18"/>
       <c r="E34" s="18"/>
       <c r="F34" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G34" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="H34" s="12">
         <v>0</v>
@@ -12120,21 +11768,21 @@
         <v>1</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D35" s="18"/>
       <c r="E35" s="18"/>
       <c r="F35" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H35" s="12">
         <v>0</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -12146,21 +11794,21 @@
         <v>1</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D36" s="18"/>
       <c r="E36" s="18"/>
       <c r="F36" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G36" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H36" s="12">
+        <v>1</v>
+      </c>
+      <c r="I36" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="H36" s="12">
-        <v>1</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -12172,15 +11820,15 @@
         <v>1</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D37" s="18"/>
       <c r="E37" s="18"/>
       <c r="F37" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H37" s="12">
         <v>0</v>
@@ -12196,15 +11844,15 @@
         <v>1</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D38" s="18"/>
       <c r="E38" s="18"/>
       <c r="F38" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G38" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="H38" s="12">
         <v>0</v>
@@ -12220,21 +11868,21 @@
         <v>1</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D39" s="18"/>
       <c r="E39" s="18"/>
       <c r="F39" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H39" s="12">
         <v>0</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
@@ -12246,21 +11894,21 @@
         <v>1</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D40" s="18"/>
       <c r="E40" s="18"/>
       <c r="F40" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G40" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H40" s="12">
+        <v>1</v>
+      </c>
+      <c r="I40" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="H40" s="12">
-        <v>1</v>
-      </c>
-      <c r="I40" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
@@ -12272,15 +11920,15 @@
         <v>1</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D41" s="18"/>
       <c r="E41" s="18"/>
       <c r="F41" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H41" s="12">
         <v>0</v>
@@ -12296,15 +11944,15 @@
         <v>1</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D42" s="18"/>
       <c r="E42" s="18"/>
       <c r="F42" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G42" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="H42" s="12">
         <v>0</v>
@@ -12320,21 +11968,21 @@
         <v>1</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="18"/>
       <c r="F43" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H43" s="12">
         <v>0</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -12346,41 +11994,41 @@
         <v>1</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D44" s="18"/>
       <c r="E44" s="18"/>
       <c r="F44" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G44" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H44" s="12">
+        <v>1</v>
+      </c>
+      <c r="I44" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="H44" s="12">
-        <v>1</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B45" s="41" t="b">
         <f>Metadata!A45=A45</f>
         <v>1</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D45" s="18"/>
       <c r="E45" s="18"/>
       <c r="F45" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H45" s="12">
         <v>0</v>
@@ -12389,22 +12037,22 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B46" s="41" t="b">
         <f>Metadata!A46=A46</f>
         <v>1</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D46" s="18"/>
       <c r="E46" s="18"/>
       <c r="F46" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G46" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="H46" s="12">
         <v>0</v>
@@ -12413,74 +12061,74 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B47" s="41" t="b">
         <f>Metadata!A47=A47</f>
         <v>1</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D47" s="18"/>
       <c r="E47" s="18"/>
       <c r="F47" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H47" s="12">
         <v>0</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B48" s="41" t="b">
         <f>Metadata!A48=A48</f>
         <v>1</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D48" s="18"/>
       <c r="E48" s="18"/>
       <c r="F48" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G48" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H48" s="12">
+        <v>1</v>
+      </c>
+      <c r="I48" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="H48" s="12">
-        <v>1</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B49" s="41" t="b">
         <f>Metadata!A49=A49</f>
         <v>1</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D49" s="18"/>
       <c r="E49" s="18"/>
       <c r="F49" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H49" s="12">
         <v>0</v>
@@ -12489,22 +12137,22 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B50" s="41" t="b">
         <f>Metadata!A50=A50</f>
         <v>1</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D50" s="18"/>
       <c r="E50" s="18"/>
       <c r="F50" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G50" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="H50" s="12">
         <v>0</v>
@@ -12513,74 +12161,74 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B51" s="41" t="b">
         <f>Metadata!A51=A51</f>
         <v>1</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D51" s="18"/>
       <c r="E51" s="18"/>
       <c r="F51" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H51" s="12">
         <v>0</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B52" s="41" t="b">
         <f>Metadata!A52=A52</f>
         <v>1</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D52" s="18"/>
       <c r="E52" s="18"/>
       <c r="F52" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G52" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H52" s="12">
+        <v>1</v>
+      </c>
+      <c r="I52" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="H52" s="12">
-        <v>1</v>
-      </c>
-      <c r="I52" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B53" s="41" t="b">
         <f>Metadata!A53=A53</f>
         <v>1</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D53" s="18"/>
       <c r="E53" s="18"/>
       <c r="F53" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H53" s="12">
         <v>0</v>
@@ -12589,22 +12237,22 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B54" s="41" t="b">
         <f>Metadata!A54=A54</f>
         <v>1</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D54" s="18"/>
       <c r="E54" s="18"/>
       <c r="F54" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G54" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="H54" s="12">
         <v>0</v>
@@ -12613,54 +12261,54 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B55" s="41" t="b">
         <f>Metadata!A55=A55</f>
         <v>1</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D55" s="18"/>
       <c r="E55" s="18"/>
       <c r="F55" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H55" s="12">
         <v>0</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B56" s="41" t="b">
         <f>Metadata!A56=A56</f>
         <v>1</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D56" s="18"/>
       <c r="E56" s="18"/>
       <c r="F56" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G56" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H56" s="12">
+        <v>1</v>
+      </c>
+      <c r="I56" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="H56" s="12">
-        <v>1</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
@@ -12672,15 +12320,15 @@
         <v>1</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D57" s="18"/>
       <c r="E57" s="18"/>
       <c r="F57" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H57" s="12">
         <v>0</v>
@@ -12696,15 +12344,15 @@
         <v>1</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D58" s="18"/>
       <c r="E58" s="18"/>
       <c r="F58" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G58" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="H58" s="12">
         <v>0</v>
@@ -12720,21 +12368,21 @@
         <v>1</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D59" s="18"/>
       <c r="E59" s="18"/>
       <c r="F59" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H59" s="12">
         <v>0</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
@@ -12746,21 +12394,21 @@
         <v>1</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D60" s="18"/>
       <c r="E60" s="18"/>
       <c r="F60" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G60" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H60" s="12">
+        <v>1</v>
+      </c>
+      <c r="I60" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="H60" s="12">
-        <v>1</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
@@ -12772,15 +12420,15 @@
         <v>1</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H61" s="27">
         <v>0</v>
@@ -12796,15 +12444,15 @@
         <v>1</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D62" s="18"/>
       <c r="E62" s="18"/>
       <c r="F62" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G62" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="H62" s="12">
         <v>0</v>
@@ -12820,21 +12468,21 @@
         <v>1</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D63" s="18"/>
       <c r="E63" s="18"/>
       <c r="F63" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H63" s="12">
         <v>0</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
@@ -12846,21 +12494,21 @@
         <v>1</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D64" s="18"/>
       <c r="E64" s="18"/>
       <c r="F64" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G64" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H64" s="12">
+        <v>1</v>
+      </c>
+      <c r="I64" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="H64" s="12">
-        <v>1</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
@@ -12872,15 +12520,15 @@
         <v>1</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D65" s="18"/>
       <c r="E65" s="18"/>
       <c r="F65" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H65" s="12">
         <v>0</v>
@@ -12896,15 +12544,15 @@
         <v>1</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D66" s="18"/>
       <c r="E66" s="18"/>
       <c r="F66" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G66" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>196</v>
       </c>
       <c r="H66" s="12">
         <v>0</v>
@@ -12920,21 +12568,21 @@
         <v>1</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D67" s="18"/>
       <c r="E67" s="18"/>
       <c r="F67" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H67" s="12">
         <v>0</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -12946,21 +12594,21 @@
         <v>1</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D68" s="18"/>
       <c r="E68" s="18"/>
       <c r="F68" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G68" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H68" s="12">
+        <v>1</v>
+      </c>
+      <c r="I68" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="H68" s="12">
-        <v>1</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
@@ -12972,15 +12620,15 @@
         <v>1</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D69" s="18"/>
       <c r="E69" s="18"/>
       <c r="F69" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H69" s="12">
         <v>0</v>
@@ -12996,17 +12644,17 @@
         <v>1</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E70" s="18"/>
       <c r="F70" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H70" s="12">
         <v>0</v>
@@ -13022,7 +12670,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="18"/>
@@ -13056,21 +12704,21 @@
         <v>1</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
       <c r="F73" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H73" s="12">
         <v>2</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -13082,21 +12730,21 @@
         <v>1</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D74" s="18"/>
       <c r="E74" s="18"/>
       <c r="F74" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H74" s="12">
         <v>2</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -13108,15 +12756,15 @@
         <v>1</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="18"/>
       <c r="F75" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G75" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>187</v>
       </c>
       <c r="H75" s="12">
         <v>0</v>
@@ -13132,15 +12780,15 @@
         <v>1</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D76" s="18"/>
       <c r="E76" s="18"/>
       <c r="F76" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H76" s="12">
         <v>0</v>
@@ -13156,21 +12804,21 @@
         <v>1</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D77" s="8"/>
       <c r="E77" s="18"/>
       <c r="F77" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H77" s="12">
         <v>3</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
@@ -13182,21 +12830,21 @@
         <v>1</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D78" s="8"/>
       <c r="E78" s="18"/>
       <c r="F78" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H78" s="12">
         <v>2</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
@@ -13208,21 +12856,21 @@
         <v>1</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D79" s="8"/>
       <c r="E79" s="18"/>
       <c r="F79" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H79" s="12">
         <v>2</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
@@ -13234,15 +12882,15 @@
         <v>1</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="18"/>
       <c r="F80" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G80" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>187</v>
       </c>
       <c r="H80" s="12">
         <v>0</v>
@@ -13258,15 +12906,15 @@
         <v>1</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="18"/>
       <c r="F81" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H81" s="12">
         <v>0</v>
@@ -13282,21 +12930,21 @@
         <v>1</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="18"/>
       <c r="F82" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H82" s="12">
         <v>3</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
@@ -13308,21 +12956,21 @@
         <v>1</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="18"/>
       <c r="F83" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H83" s="12">
         <v>2</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
@@ -13334,21 +12982,21 @@
         <v>1</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D84" s="8"/>
       <c r="E84" s="18"/>
       <c r="F84" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H84" s="12">
         <v>2</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
@@ -13360,15 +13008,15 @@
         <v>1</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D85" s="8"/>
       <c r="E85" s="18"/>
       <c r="F85" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G85" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>187</v>
       </c>
       <c r="H85" s="12">
         <v>0</v>
@@ -13384,15 +13032,15 @@
         <v>1</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D86" s="8"/>
       <c r="E86" s="18"/>
       <c r="F86" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H86" s="12">
         <v>0</v>
@@ -13408,21 +13056,21 @@
         <v>1</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D87" s="8"/>
       <c r="E87" s="18"/>
       <c r="F87" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H87" s="12">
         <v>3</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
@@ -13434,7 +13082,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D88" s="8"/>
       <c r="E88" s="18"/>
@@ -13452,15 +13100,15 @@
         <v>1</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="18"/>
       <c r="F89" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H89" s="12">
         <v>0</v>
@@ -13476,15 +13124,15 @@
         <v>1</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="18"/>
       <c r="F90" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H90" s="12">
         <v>0</v>
@@ -13516,23 +13164,23 @@
         <v>1</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E92" s="18"/>
       <c r="F92" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G92" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="H92" s="12">
+        <v>1</v>
+      </c>
+      <c r="I92" s="12" t="s">
         <v>224</v>
-      </c>
-      <c r="H92" s="12">
-        <v>1</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
@@ -13560,17 +13208,17 @@
         <v>1</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E94" s="18"/>
       <c r="F94" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H94" s="12">
         <v>2</v>
@@ -13618,7 +13266,7 @@
         <v>1</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D97" s="8"/>
       <c r="E97" s="18"/>
@@ -13636,7 +13284,7 @@
         <v>1</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D98" s="8"/>
       <c r="E98" s="18"/>
@@ -13654,7 +13302,7 @@
         <v>1</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D99" s="8"/>
       <c r="E99" s="18"/>
@@ -13688,15 +13336,15 @@
         <v>1</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="18"/>
       <c r="F101" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H101" s="12">
         <v>1</v>
@@ -13712,15 +13360,15 @@
         <v>1</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="18"/>
       <c r="F102" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H102" s="12">
         <v>1</v>
@@ -13752,15 +13400,15 @@
         <v>1</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="18"/>
       <c r="F104" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H104" s="12">
         <v>2</v>
@@ -13776,17 +13424,17 @@
         <v>1</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E105" s="18"/>
       <c r="F105" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H105" s="12">
         <v>0</v>
@@ -13802,23 +13450,23 @@
         <v>1</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E106" s="18"/>
       <c r="F106" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G106" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H106" s="12">
+        <v>0</v>
+      </c>
+      <c r="I106" s="12" t="s">
         <v>232</v>
-      </c>
-      <c r="H106" s="12">
-        <v>0</v>
-      </c>
-      <c r="I106" s="12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
@@ -13830,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D107" s="18"/>
       <c r="E107" s="18"/>
@@ -13848,7 +13496,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D108" s="18"/>
       <c r="E108" s="18"/>
@@ -13866,7 +13514,7 @@
         <v>1</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="18"/>
@@ -13884,21 +13532,21 @@
         <v>1</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="18"/>
       <c r="F110" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="G110" s="8" t="s">
         <v>235</v>
-      </c>
-      <c r="G110" s="8" t="s">
-        <v>236</v>
       </c>
       <c r="H110" s="12">
         <v>4</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
@@ -13942,7 +13590,7 @@
         <v>1</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="18"/>
@@ -13960,7 +13608,7 @@
         <v>1</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="18"/>
@@ -14061,10 +13709,10 @@
       <c r="D120" s="8"/>
       <c r="E120" s="18"/>
       <c r="F120" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="G120" s="8" t="s">
         <v>238</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>239</v>
       </c>
       <c r="H120" s="12">
         <v>2</v>
@@ -16053,76 +15701,76 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I111" xr:uid="{776C4DE2-2957-440A-A09D-B0AB3152981D}">
-    <sortState ref="A2:I120">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I120">
       <sortCondition ref="A1:A111"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A61">
-    <cfRule type="expression" dxfId="61" priority="11">
+    <cfRule type="expression" dxfId="43" priority="11">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:A106 C88:E106">
-    <cfRule type="expression" dxfId="60" priority="32">
+    <cfRule type="expression" dxfId="42" priority="32">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:D61 F61:H61">
-    <cfRule type="expression" dxfId="59" priority="3">
+    <cfRule type="expression" dxfId="41" priority="3">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="4">
+    <cfRule type="expression" dxfId="40" priority="4">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:I1">
-    <cfRule type="expression" dxfId="57" priority="16">
+    <cfRule type="expression" dxfId="39" priority="16">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:I60 A62:I109">
-    <cfRule type="expression" dxfId="56" priority="30">
+    <cfRule type="expression" dxfId="38" priority="30">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:I60 C1:E60 A62:I109">
-    <cfRule type="expression" dxfId="55" priority="29">
+    <cfRule type="expression" dxfId="37" priority="29">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110:I300">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="2">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90">
-    <cfRule type="expression" dxfId="52" priority="114">
+    <cfRule type="expression" dxfId="34" priority="114">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E106">
-    <cfRule type="expression" dxfId="51" priority="5">
+    <cfRule type="expression" dxfId="33" priority="5">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61">
-    <cfRule type="expression" dxfId="50" priority="6">
+    <cfRule type="expression" dxfId="32" priority="6">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25">
-    <cfRule type="expression" dxfId="49" priority="17">
+    <cfRule type="expression" dxfId="31" priority="17">
       <formula>OR(ROW()=CELL("row"),col()=CELL("col"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H61:I61">
-    <cfRule type="expression" dxfId="48" priority="7">
+    <cfRule type="expression" dxfId="30" priority="7">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="8">
+    <cfRule type="expression" dxfId="29" priority="8">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16153,25 +15801,25 @@
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -16183,17 +15831,17 @@
         <v>1</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>249</v>
       </c>
       <c r="H2" s="25"/>
       <c r="I2" s="26"/>
@@ -16243,7 +15891,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="20"/>
@@ -16261,7 +15909,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="20"/>
@@ -16327,7 +15975,7 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H10" s="27" t="b">
         <v>0</v>
@@ -16345,13 +15993,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="20"/>
@@ -16385,7 +16033,7 @@
       <c r="E13" s="14"/>
       <c r="F13" s="8"/>
       <c r="G13" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H13" s="27" t="b">
         <f>TRUE()</f>
@@ -16409,7 +16057,7 @@
       <c r="E14" s="14"/>
       <c r="F14" s="8"/>
       <c r="G14" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H14" s="27" t="b">
         <f>TRUE()</f>
@@ -16433,7 +16081,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H15" s="27" t="b">
         <f>TRUE()</f>
@@ -16457,7 +16105,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="8"/>
       <c r="G16" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H16" s="27" t="b">
         <f>TRUE()</f>
@@ -16481,7 +16129,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="8"/>
       <c r="G17" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H17" s="27" t="b">
         <f>TRUE()</f>
@@ -16501,13 +16149,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="14"/>
       <c r="F18" s="8"/>
       <c r="G18" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H18" s="27" t="b">
         <f>FALSE()</f>
@@ -16528,7 +16176,7 @@
       <c r="E19" s="14"/>
       <c r="F19" s="8"/>
       <c r="G19" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H19" s="27" t="b">
         <f>TRUE()</f>
@@ -16548,13 +16196,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="14"/>
       <c r="F20" s="8"/>
       <c r="G20" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H20" s="27"/>
       <c r="I20" s="20"/>
@@ -16568,15 +16216,15 @@
         <v>1</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H21" s="27" t="b">
         <f>FALSE()</f>
@@ -16595,11 +16243,11 @@
       <c r="C22" s="23"/>
       <c r="D22" s="24"/>
       <c r="E22" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H22" s="27"/>
       <c r="I22" s="20"/>
@@ -16613,13 +16261,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H23" s="27"/>
       <c r="I23" s="20"/>
@@ -16665,15 +16313,15 @@
         <v>1</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H26" s="27"/>
       <c r="I26" s="20"/>
@@ -16719,13 +16367,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H29" s="27"/>
       <c r="I29" s="20"/>
@@ -16775,7 +16423,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H32" s="27" t="b">
         <f>FALSE()</f>
@@ -16799,7 +16447,7 @@
       <c r="E33" s="14"/>
       <c r="F33" s="8"/>
       <c r="G33" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H33" s="27" t="b">
         <f>TRUE()</f>
@@ -16823,7 +16471,7 @@
       <c r="E34" s="14"/>
       <c r="F34" s="8"/>
       <c r="G34" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H34" s="27" t="b">
         <f>TRUE()</f>
@@ -16847,7 +16495,7 @@
       <c r="E35" s="14"/>
       <c r="F35" s="8"/>
       <c r="G35" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H35" s="27" t="b">
         <f>TRUE()</f>
@@ -16867,13 +16515,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="14"/>
       <c r="F36" s="8"/>
       <c r="G36" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H36" s="27"/>
       <c r="I36" s="20"/>
@@ -16891,7 +16539,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="8"/>
       <c r="G37" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H37" s="27" t="b">
         <f>TRUE()</f>
@@ -16915,7 +16563,7 @@
       <c r="E38" s="14"/>
       <c r="F38" s="8"/>
       <c r="G38" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H38" s="27" t="b">
         <f>TRUE()</f>
@@ -16939,7 +16587,7 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8"/>
       <c r="G39" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H39" s="27" t="b">
         <f>TRUE()</f>
@@ -16959,13 +16607,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="14"/>
       <c r="F40" s="8"/>
       <c r="G40" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H40" s="27"/>
       <c r="I40" s="20"/>
@@ -16983,7 +16631,7 @@
       <c r="E41" s="14"/>
       <c r="F41" s="8"/>
       <c r="G41" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H41" s="27" t="b">
         <f>TRUE()</f>
@@ -17007,7 +16655,7 @@
       <c r="E42" s="14"/>
       <c r="F42" s="8"/>
       <c r="G42" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H42" s="27" t="b">
         <f>TRUE()</f>
@@ -17031,7 +16679,7 @@
       <c r="E43" s="14"/>
       <c r="F43" s="8"/>
       <c r="G43" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H43" s="27" t="b">
         <f>TRUE()</f>
@@ -17051,20 +16699,20 @@
         <v>1</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="14"/>
       <c r="F44" s="8"/>
       <c r="G44" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H44" s="27"/>
       <c r="I44" s="20"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B45" s="41" t="b">
         <f>A45=Metadata!A45</f>
@@ -17075,7 +16723,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H45" s="27" t="b">
         <f>TRUE()</f>
@@ -17088,7 +16736,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B46" s="41" t="b">
         <f>A46=Metadata!A46</f>
@@ -17099,7 +16747,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H46" s="27" t="b">
         <f>TRUE()</f>
@@ -17112,7 +16760,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B47" s="41" t="b">
         <f>A47=Metadata!A47</f>
@@ -17123,7 +16771,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H47" s="27" t="b">
         <f>TRUE()</f>
@@ -17136,27 +16784,27 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B48" s="41" t="b">
         <f>A48=Metadata!A48</f>
         <v>1</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H48" s="27"/>
       <c r="I48" s="20"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B49" s="41" t="b">
         <f>A49=Metadata!A49</f>
@@ -17167,7 +16815,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H49" s="27" t="b">
         <f>TRUE()</f>
@@ -17180,7 +16828,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B50" s="41" t="b">
         <f>A50=Metadata!A50</f>
@@ -17191,7 +16839,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
       <c r="G50" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H50" s="27" t="b">
         <f>TRUE()</f>
@@ -17204,7 +16852,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B51" s="41" t="b">
         <f>A51=Metadata!A51</f>
@@ -17215,7 +16863,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H51" s="27" t="b">
         <f>TRUE()</f>
@@ -17228,27 +16876,27 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B52" s="41" t="b">
         <f>A52=Metadata!A52</f>
         <v>1</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H52" s="45"/>
       <c r="I52" s="20"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B53" s="41" t="b">
         <f>A53=Metadata!A53</f>
@@ -17259,7 +16907,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H53" s="27" t="b">
         <f>TRUE()</f>
@@ -17272,7 +16920,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B54" s="41" t="b">
         <f>A54=Metadata!A54</f>
@@ -17283,7 +16931,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H54" s="27" t="b">
         <f>TRUE()</f>
@@ -17296,7 +16944,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B55" s="41" t="b">
         <f>A55=Metadata!A55</f>
@@ -17307,7 +16955,7 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H55" s="27" t="b">
         <f>TRUE()</f>
@@ -17320,20 +16968,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B56" s="41" t="b">
         <f>A56=Metadata!A56</f>
         <v>1</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H56" s="45"/>
       <c r="I56" s="20"/>
@@ -17351,7 +16999,7 @@
       <c r="E57" s="14"/>
       <c r="F57" s="8"/>
       <c r="G57" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H57" s="27" t="b">
         <f>TRUE()</f>
@@ -17375,7 +17023,7 @@
       <c r="E58" s="14"/>
       <c r="F58" s="8"/>
       <c r="G58" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H58" s="27" t="b">
         <f>TRUE()</f>
@@ -17399,7 +17047,7 @@
       <c r="E59" s="14"/>
       <c r="F59" s="8"/>
       <c r="G59" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H59" s="27" t="b">
         <f>TRUE()</f>
@@ -17419,13 +17067,13 @@
         <v>1</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="14"/>
       <c r="F60" s="8"/>
       <c r="G60" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H60" s="27"/>
       <c r="I60" s="20"/>
@@ -17443,7 +17091,7 @@
       <c r="E61" s="14"/>
       <c r="F61" s="8"/>
       <c r="G61" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H61" s="27" t="b">
         <f>TRUE()</f>
@@ -17467,7 +17115,7 @@
       <c r="E62" s="14"/>
       <c r="F62" s="8"/>
       <c r="G62" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H62" s="27" t="b">
         <f>TRUE()</f>
@@ -17491,7 +17139,7 @@
       <c r="E63" s="14"/>
       <c r="F63" s="8"/>
       <c r="G63" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H63" s="27" t="b">
         <f>TRUE()</f>
@@ -17511,13 +17159,13 @@
         <v>1</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="14"/>
       <c r="F64" s="8"/>
       <c r="G64" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H64" s="27"/>
       <c r="I64" s="20"/>
@@ -17535,7 +17183,7 @@
       <c r="E65" s="44"/>
       <c r="F65" s="8"/>
       <c r="G65" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H65" s="27" t="b">
         <f>TRUE()</f>
@@ -17559,7 +17207,7 @@
       <c r="E66" s="14"/>
       <c r="F66" s="8"/>
       <c r="G66" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H66" s="27" t="b">
         <f>TRUE()</f>
@@ -17583,7 +17231,7 @@
       <c r="E67" s="14"/>
       <c r="F67" s="8"/>
       <c r="G67" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H67" s="27" t="b">
         <f>TRUE()</f>
@@ -17603,13 +17251,13 @@
         <v>1</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D68" s="24"/>
       <c r="E68" s="14"/>
       <c r="F68" s="8"/>
       <c r="G68" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H68" s="27"/>
       <c r="I68" s="20"/>
@@ -17627,7 +17275,7 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H69" s="27" t="b">
         <f>TRUE()</f>
@@ -17651,7 +17299,7 @@
       <c r="E70" s="23"/>
       <c r="F70" s="8"/>
       <c r="G70" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H70" s="27"/>
       <c r="I70" s="20"/>
@@ -17701,7 +17349,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H73" s="27"/>
       <c r="I73" s="20"/>
@@ -17719,7 +17367,7 @@
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
       <c r="G74" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H74" s="27"/>
       <c r="I74" s="20"/>
@@ -17733,17 +17381,17 @@
         <v>1</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D75" s="24"/>
       <c r="E75" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="G75" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G75" s="12" t="s">
-        <v>249</v>
       </c>
       <c r="H75" s="27"/>
       <c r="I75" s="20"/>
@@ -17757,13 +17405,13 @@
         <v>1</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D76" s="24"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H76" s="27"/>
       <c r="I76" s="20"/>
@@ -17777,15 +17425,15 @@
         <v>1</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D77" s="24"/>
       <c r="E77" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F77" s="8"/>
       <c r="G77" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H77" s="27"/>
       <c r="I77" s="20"/>
@@ -17803,7 +17451,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H78" s="27"/>
       <c r="I78" s="20"/>
@@ -17821,7 +17469,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H79" s="27"/>
       <c r="I79" s="20"/>
@@ -17835,17 +17483,17 @@
         <v>1</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D80" s="24"/>
       <c r="E80" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="G80" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G80" s="12" t="s">
-        <v>249</v>
       </c>
       <c r="H80" s="27"/>
       <c r="I80" s="20"/>
@@ -17859,13 +17507,13 @@
         <v>1</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D81" s="24"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
       <c r="G81" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H81" s="27"/>
       <c r="I81" s="20"/>
@@ -17879,15 +17527,15 @@
         <v>1</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H82" s="27"/>
       <c r="I82" s="20"/>
@@ -17905,7 +17553,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H83" s="27"/>
       <c r="I83" s="20"/>
@@ -17923,7 +17571,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H84" s="27"/>
       <c r="I84" s="20"/>
@@ -17937,17 +17585,17 @@
         <v>1</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D85" s="24"/>
       <c r="E85" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="G85" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G85" s="12" t="s">
-        <v>249</v>
       </c>
       <c r="H85" s="27"/>
       <c r="I85" s="20"/>
@@ -17961,13 +17609,13 @@
         <v>1</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D86" s="24"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
       <c r="G86" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H86" s="27"/>
       <c r="I86" s="20"/>
@@ -17981,15 +17629,15 @@
         <v>1</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D87" s="24"/>
       <c r="E87" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H87" s="27"/>
       <c r="I87" s="20"/>
@@ -18023,7 +17671,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
       <c r="G89" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H89" s="27" t="b">
         <f>TRUE()</f>
@@ -18047,7 +17695,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
       <c r="G90" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H90" s="27" t="b">
         <f>TRUE()</f>
@@ -18083,15 +17731,15 @@
         <v>1</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D92" s="24"/>
       <c r="E92" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H92" s="27"/>
       <c r="I92" s="20"/>
@@ -18125,7 +17773,7 @@
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
       <c r="G94" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H94" s="27" t="b">
         <v>0</v>
@@ -18243,7 +17891,7 @@
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
       <c r="G101" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H101" s="27"/>
       <c r="I101" s="20"/>
@@ -18261,7 +17909,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
       <c r="G102" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H102" s="27"/>
       <c r="I102" s="20"/>
@@ -18291,17 +17939,17 @@
         <v>1</v>
       </c>
       <c r="C104" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="D104" s="24" t="s">
         <v>261</v>
-      </c>
-      <c r="D104" s="24" t="s">
-        <v>262</v>
       </c>
       <c r="E104" s="8"/>
       <c r="F104" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H104" s="27"/>
       <c r="I104" s="20"/>
@@ -18319,7 +17967,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
       <c r="G105" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H105" s="27"/>
       <c r="I105" s="20"/>
@@ -18337,7 +17985,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
       <c r="G106" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H106" s="27" t="b">
         <f>FALSE()</f>
@@ -18405,15 +18053,15 @@
         <v>1</v>
       </c>
       <c r="C110" s="23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F110" s="8"/>
       <c r="G110" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H110" s="27"/>
       <c r="I110" s="20"/>
@@ -18447,7 +18095,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
       <c r="G112" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H112" s="27"/>
       <c r="I112" s="20"/>
@@ -18545,7 +18193,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
       <c r="G118" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H118" s="27" t="b">
         <f>TRUE()</f>
@@ -18585,7 +18233,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
       <c r="G120" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H120" s="27"/>
       <c r="I120" s="20"/>
@@ -20572,85 +20220,85 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I109" xr:uid="{44BD8FFD-EDA1-47AD-AC03-3890015323F4}">
-    <sortState ref="A2:I120">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I120">
       <sortCondition ref="A1:A109"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A77:A86">
-    <cfRule type="expression" dxfId="46" priority="50">
+    <cfRule type="expression" dxfId="28" priority="50">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:A300">
-    <cfRule type="expression" dxfId="45" priority="11">
+    <cfRule type="expression" dxfId="27" priority="11">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B300">
-    <cfRule type="expression" dxfId="44" priority="9">
+    <cfRule type="expression" dxfId="26" priority="9">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="10">
+    <cfRule type="expression" dxfId="25" priority="10">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C82:C88">
-    <cfRule type="expression" dxfId="42" priority="21">
+    <cfRule type="expression" dxfId="24" priority="21">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95:H300">
-    <cfRule type="expression" dxfId="41" priority="3">
+    <cfRule type="expression" dxfId="23" priority="3">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="4">
+    <cfRule type="expression" dxfId="22" priority="4">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:I2 C3:F63 G56:H68 I56:I81 F64:F68 C64:E94 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94 A1:I1">
-    <cfRule type="expression" dxfId="39" priority="20">
+    <cfRule type="expression" dxfId="21" priority="20">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:I2 C3:F63 G56:H68 I56:I81 F64:F68 C64:E94 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94">
-    <cfRule type="expression" dxfId="38" priority="19">
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D25:F25">
-    <cfRule type="expression" dxfId="37" priority="22">
+    <cfRule type="expression" dxfId="19" priority="22">
       <formula>OR(ROW()=CELL("row"),col()=CELL("col"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G81">
-    <cfRule type="expression" dxfId="36" priority="106">
+    <cfRule type="expression" dxfId="18" priority="106">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="107">
+    <cfRule type="expression" dxfId="17" priority="107">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:I55">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="2">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H94:I94">
-    <cfRule type="expression" dxfId="32" priority="36">
+    <cfRule type="expression" dxfId="14" priority="36">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="37">
+    <cfRule type="expression" dxfId="13" priority="37">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H95:I300">
-    <cfRule type="expression" dxfId="30" priority="7">
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="8">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20683,28 +20331,28 @@
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -20716,23 +20364,23 @@
         <v>1</v>
       </c>
       <c r="C2" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="D2" s="28" t="s">
         <v>271</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>272</v>
       </c>
       <c r="E2" s="28"/>
       <c r="F2" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="G2" s="28">
+        <v>0</v>
+      </c>
+      <c r="H2" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="G2" s="28">
-        <v>0</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>274</v>
-      </c>
       <c r="I2" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J2" s="28"/>
     </row>
@@ -20745,7 +20393,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
@@ -20764,7 +20412,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
@@ -20783,23 +20431,23 @@
         <v>1</v>
       </c>
       <c r="C5" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>275</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>276</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G5" s="12">
         <v>0</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J5" s="12"/>
     </row>
@@ -20812,23 +20460,23 @@
         <v>1</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>275</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>276</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G6" s="12">
         <v>0</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J6" s="12"/>
     </row>
@@ -20841,10 +20489,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>279</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -20862,10 +20510,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>279</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -20883,10 +20531,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>279</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -20904,23 +20552,23 @@
         <v>1</v>
       </c>
       <c r="C10" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J10" s="12"/>
     </row>
@@ -20933,21 +20581,21 @@
         <v>1</v>
       </c>
       <c r="C11" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J11" s="12"/>
     </row>
@@ -20960,19 +20608,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J12" s="12"/>
     </row>
@@ -20985,23 +20633,23 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G13" s="12">
         <v>0</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J13" s="12"/>
     </row>
@@ -21014,23 +20662,23 @@
         <v>1</v>
       </c>
       <c r="C14" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G14" s="12">
         <v>0</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J14" s="12"/>
     </row>
@@ -21043,21 +20691,21 @@
         <v>1</v>
       </c>
       <c r="C15" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J15" s="12"/>
     </row>
@@ -21070,25 +20718,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="E16" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="G16" s="12">
         <v>0</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J16" s="12"/>
     </row>
@@ -21101,23 +20749,23 @@
         <v>1</v>
       </c>
       <c r="C17" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J17" s="12"/>
     </row>
@@ -21130,25 +20778,25 @@
         <v>1</v>
       </c>
       <c r="C18" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="E18" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="G18" s="12">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J18" s="12"/>
     </row>
@@ -21161,25 +20809,25 @@
         <v>1</v>
       </c>
       <c r="C19" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="E19" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F19" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="G19" s="12">
         <v>0</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J19" s="12"/>
     </row>
@@ -21192,25 +20840,25 @@
         <v>1</v>
       </c>
       <c r="C20" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="E20" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F20" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="G20" s="12">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J20" s="12"/>
     </row>
@@ -21223,23 +20871,23 @@
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G21" s="12">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J21" s="12"/>
     </row>
@@ -21252,23 +20900,23 @@
         <v>1</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G22" s="12">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J22" s="12"/>
     </row>
@@ -21281,23 +20929,23 @@
         <v>1</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G23" s="12">
         <v>0</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J23" s="12"/>
     </row>
@@ -21310,10 +20958,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -21331,10 +20979,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -21352,23 +21000,23 @@
         <v>1</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G26" s="12"/>
       <c r="H26" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J26" s="12"/>
     </row>
@@ -21381,19 +21029,19 @@
         <v>1</v>
       </c>
       <c r="C27" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>275</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>276</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J27" s="12"/>
     </row>
@@ -21406,19 +21054,19 @@
         <v>1</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
       <c r="H28" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J28" s="12"/>
     </row>
@@ -21431,21 +21079,21 @@
         <v>1</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G29" s="12">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J29" s="12"/>
     </row>
@@ -21458,19 +21106,19 @@
         <v>1</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
       <c r="F30" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J30" s="12"/>
     </row>
@@ -21483,19 +21131,19 @@
         <v>1</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J31" s="12"/>
     </row>
@@ -21508,23 +21156,23 @@
         <v>1</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G32" s="12">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J32" s="12"/>
     </row>
@@ -21537,23 +21185,23 @@
         <v>1</v>
       </c>
       <c r="C33" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G33" s="12">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J33" s="12"/>
     </row>
@@ -21566,23 +21214,23 @@
         <v>1</v>
       </c>
       <c r="C34" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G34" s="12">
         <v>0</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J34" s="12"/>
     </row>
@@ -21595,23 +21243,23 @@
         <v>1</v>
       </c>
       <c r="C35" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G35" s="12">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J35" s="12"/>
     </row>
@@ -21624,23 +21272,23 @@
         <v>1</v>
       </c>
       <c r="C36" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G36" s="12">
         <v>0</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J36" s="12"/>
     </row>
@@ -21653,23 +21301,23 @@
         <v>1</v>
       </c>
       <c r="C37" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G37" s="12">
         <v>0</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J37" s="12"/>
     </row>
@@ -21682,23 +21330,23 @@
         <v>1</v>
       </c>
       <c r="C38" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G38" s="12">
         <v>0</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J38" s="12"/>
     </row>
@@ -21711,23 +21359,23 @@
         <v>1</v>
       </c>
       <c r="C39" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G39" s="12">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J39" s="12"/>
     </row>
@@ -21740,23 +21388,23 @@
         <v>1</v>
       </c>
       <c r="C40" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G40" s="12">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J40" s="12"/>
     </row>
@@ -21769,23 +21417,23 @@
         <v>1</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G41" s="12">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J41" s="12"/>
     </row>
@@ -21798,23 +21446,23 @@
         <v>1</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G42" s="12">
         <v>12</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J42" s="12"/>
     </row>
@@ -21827,23 +21475,23 @@
         <v>1</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G43" s="12">
         <v>12</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J43" s="12"/>
     </row>
@@ -21856,371 +21504,371 @@
         <v>1</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G44" s="12">
         <v>12</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J44" s="12"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B45" s="46" t="b">
         <f>A45=Metadata!A45</f>
         <v>1</v>
       </c>
       <c r="C45" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G45" s="12">
         <v>0</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J45" s="12"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B46" s="46" t="b">
         <f>A46=Metadata!A46</f>
         <v>1</v>
       </c>
       <c r="C46" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G46" s="12">
         <v>0</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J46" s="12"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B47" s="46" t="b">
         <f>A47=Metadata!A47</f>
         <v>1</v>
       </c>
       <c r="C47" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G47" s="12">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J47" s="12"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B48" s="46" t="b">
         <f>A48=Metadata!A48</f>
         <v>1</v>
       </c>
       <c r="C48" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G48" s="12">
         <v>0</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J48" s="12"/>
     </row>
     <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B49" s="46" t="b">
         <f>A49=Metadata!A49</f>
         <v>1</v>
       </c>
       <c r="C49" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D49" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G49" s="12">
         <v>0</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J49" s="12"/>
     </row>
     <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B50" s="46" t="b">
         <f>A50=Metadata!A50</f>
         <v>1</v>
       </c>
       <c r="C50" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G50" s="12">
         <v>0</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J50" s="12"/>
     </row>
     <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B51" s="46" t="b">
         <f>A51=Metadata!A51</f>
         <v>1</v>
       </c>
       <c r="C51" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G51" s="12">
         <v>0</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J51" s="12"/>
     </row>
     <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B52" s="46" t="b">
         <f>A52=Metadata!A52</f>
         <v>1</v>
       </c>
       <c r="C52" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G52" s="12">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J52" s="12"/>
     </row>
     <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B53" s="46" t="b">
         <f>A53=Metadata!A53</f>
         <v>1</v>
       </c>
       <c r="C53" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G53" s="12">
         <v>0</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J53" s="12"/>
     </row>
     <row r="54" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B54" s="46" t="b">
         <f>A54=Metadata!A54</f>
         <v>1</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G54" s="12">
         <v>12</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J54" s="12"/>
     </row>
     <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B55" s="46" t="b">
         <f>A55=Metadata!A55</f>
         <v>1</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G55" s="12">
         <v>12</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J55" s="12"/>
     </row>
     <row r="56" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B56" s="46" t="b">
         <f>A56=Metadata!A56</f>
         <v>1</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G56" s="12">
         <v>12</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J56" s="12"/>
     </row>
@@ -22233,23 +21881,23 @@
         <v>1</v>
       </c>
       <c r="C57" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D57" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G57" s="12">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J57" s="12"/>
     </row>
@@ -22262,23 +21910,23 @@
         <v>1</v>
       </c>
       <c r="C58" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D58" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G58" s="12">
         <v>0</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J58" s="12"/>
     </row>
@@ -22291,23 +21939,23 @@
         <v>1</v>
       </c>
       <c r="C59" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G59" s="12">
         <v>0</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J59" s="12"/>
     </row>
@@ -22320,23 +21968,23 @@
         <v>1</v>
       </c>
       <c r="C60" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G60" s="12">
         <v>0</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J60" s="12"/>
     </row>
@@ -22349,23 +21997,23 @@
         <v>1</v>
       </c>
       <c r="C61" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D61" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G61" s="12">
         <v>0</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J61" s="12"/>
     </row>
@@ -22378,23 +22026,23 @@
         <v>1</v>
       </c>
       <c r="C62" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G62" s="12">
         <v>0</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J62" s="12"/>
     </row>
@@ -22407,23 +22055,23 @@
         <v>1</v>
       </c>
       <c r="C63" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D63" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G63" s="12">
         <v>0</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J63" s="12"/>
     </row>
@@ -22436,23 +22084,23 @@
         <v>1</v>
       </c>
       <c r="C64" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G64" s="12">
         <v>0</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J64" s="12"/>
     </row>
@@ -22465,23 +22113,23 @@
         <v>1</v>
       </c>
       <c r="C65" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D65" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G65" s="12">
         <v>0</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J65" s="12"/>
     </row>
@@ -22494,23 +22142,23 @@
         <v>1</v>
       </c>
       <c r="C66" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G66" s="12">
         <v>0</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J66" s="12"/>
     </row>
@@ -22523,23 +22171,23 @@
         <v>1</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G67" s="12">
         <v>12</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J67" s="12"/>
     </row>
@@ -22552,23 +22200,23 @@
         <v>1</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G68" s="12">
         <v>12</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J68" s="12"/>
     </row>
@@ -22581,23 +22229,23 @@
         <v>1</v>
       </c>
       <c r="C69" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G69" s="12">
         <v>0</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J69" s="12"/>
     </row>
@@ -22610,21 +22258,21 @@
         <v>1</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="12"/>
       <c r="F70" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G70" s="12">
         <v>0</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J70" s="12"/>
     </row>
@@ -22637,10 +22285,10 @@
         <v>1</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
@@ -22658,19 +22306,19 @@
         <v>1</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
       <c r="G72" s="12"/>
       <c r="H72" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J72" s="12"/>
     </row>
@@ -22683,23 +22331,23 @@
         <v>1</v>
       </c>
       <c r="C73" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D73" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G73" s="12">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G73" s="12">
-        <v>0</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I73" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J73" s="12"/>
     </row>
@@ -22712,23 +22360,23 @@
         <v>1</v>
       </c>
       <c r="C74" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D74" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G74" s="12">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G74" s="12">
-        <v>0</v>
-      </c>
-      <c r="H74" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I74" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J74" s="12"/>
     </row>
@@ -22741,25 +22389,25 @@
         <v>1</v>
       </c>
       <c r="C75" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D75" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="E75" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="F75" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="E75" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="F75" s="12" t="s">
+      <c r="G75" s="12">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G75" s="12">
-        <v>0</v>
-      </c>
-      <c r="H75" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I75" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J75" s="12"/>
     </row>
@@ -22772,23 +22420,23 @@
         <v>1</v>
       </c>
       <c r="C76" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D76" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G76" s="12">
+        <v>0</v>
+      </c>
+      <c r="H76" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G76" s="12">
-        <v>0</v>
-      </c>
-      <c r="H76" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I76" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J76" s="12"/>
     </row>
@@ -22801,21 +22449,21 @@
         <v>1</v>
       </c>
       <c r="C77" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G77" s="12"/>
       <c r="H77" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J77" s="12"/>
     </row>
@@ -22828,23 +22476,23 @@
         <v>1</v>
       </c>
       <c r="C78" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G78" s="12">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G78" s="12">
-        <v>0</v>
-      </c>
-      <c r="H78" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I78" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J78" s="12"/>
     </row>
@@ -22857,23 +22505,23 @@
         <v>1</v>
       </c>
       <c r="C79" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G79" s="12">
+        <v>0</v>
+      </c>
+      <c r="H79" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G79" s="12">
-        <v>0</v>
-      </c>
-      <c r="H79" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I79" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J79" s="12"/>
     </row>
@@ -22886,25 +22534,25 @@
         <v>1</v>
       </c>
       <c r="C80" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D80" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="E80" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="F80" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="E80" s="29" t="s">
-        <v>287</v>
-      </c>
-      <c r="F80" s="12" t="s">
+      <c r="G80" s="12">
+        <v>0</v>
+      </c>
+      <c r="H80" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G80" s="12">
-        <v>0</v>
-      </c>
-      <c r="H80" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I80" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J80" s="12"/>
     </row>
@@ -22917,23 +22565,23 @@
         <v>1</v>
       </c>
       <c r="C81" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G81" s="12">
+        <v>0</v>
+      </c>
+      <c r="H81" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G81" s="12">
-        <v>0</v>
-      </c>
-      <c r="H81" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I81" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J81" s="12"/>
     </row>
@@ -22946,21 +22594,21 @@
         <v>1</v>
       </c>
       <c r="C82" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D82" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G82" s="12"/>
       <c r="H82" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J82" s="12"/>
     </row>
@@ -22973,23 +22621,23 @@
         <v>1</v>
       </c>
       <c r="C83" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D83" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G83" s="12">
+        <v>0</v>
+      </c>
+      <c r="H83" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G83" s="12">
-        <v>0</v>
-      </c>
-      <c r="H83" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I83" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J83" s="12"/>
     </row>
@@ -23002,23 +22650,23 @@
         <v>1</v>
       </c>
       <c r="C84" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D84" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G84" s="12">
+        <v>0</v>
+      </c>
+      <c r="H84" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G84" s="12">
-        <v>0</v>
-      </c>
-      <c r="H84" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I84" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J84" s="12"/>
     </row>
@@ -23031,25 +22679,25 @@
         <v>1</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D85" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E85" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="F85" s="12" t="s">
         <v>272</v>
-      </c>
-      <c r="E85" s="29" t="s">
-        <v>288</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>273</v>
       </c>
       <c r="G85" s="12">
         <v>12</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J85" s="12"/>
     </row>
@@ -23062,23 +22710,23 @@
         <v>1</v>
       </c>
       <c r="C86" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D86" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G86" s="12">
+        <v>0</v>
+      </c>
+      <c r="H86" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G86" s="12">
-        <v>0</v>
-      </c>
-      <c r="H86" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I86" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J86" s="12"/>
     </row>
@@ -23091,21 +22739,21 @@
         <v>1</v>
       </c>
       <c r="C87" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D87" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G87" s="12"/>
       <c r="H87" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J87" s="12"/>
     </row>
@@ -23118,23 +22766,23 @@
         <v>1</v>
       </c>
       <c r="C88" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D88" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G88" s="12">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J88" s="12"/>
     </row>
@@ -23147,23 +22795,23 @@
         <v>1</v>
       </c>
       <c r="C89" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D89" s="12" t="s">
         <v>275</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>276</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G89" s="12">
+        <v>0</v>
+      </c>
+      <c r="H89" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G89" s="12">
-        <v>0</v>
-      </c>
-      <c r="H89" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I89" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J89" s="12"/>
     </row>
@@ -23176,23 +22824,23 @@
         <v>1</v>
       </c>
       <c r="C90" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D90" s="12" t="s">
         <v>275</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>276</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G90" s="12">
+        <v>0</v>
+      </c>
+      <c r="H90" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="G90" s="12">
-        <v>0</v>
-      </c>
-      <c r="H90" s="12" t="s">
-        <v>274</v>
-      </c>
       <c r="I90" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J90" s="12"/>
     </row>
@@ -23205,17 +22853,17 @@
         <v>1</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D91" s="12"/>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I91" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J91" s="12"/>
     </row>
@@ -23228,23 +22876,23 @@
         <v>1</v>
       </c>
       <c r="C92" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D92" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G92" s="12">
         <v>0</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J92" s="12"/>
     </row>
@@ -23257,10 +22905,10 @@
         <v>1</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -23278,23 +22926,23 @@
         <v>1</v>
       </c>
       <c r="C94" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D94" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G94" s="12">
         <v>0</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J94" s="12"/>
     </row>
@@ -23307,17 +22955,17 @@
         <v>1</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J95" s="12"/>
     </row>
@@ -23330,7 +22978,7 @@
         <v>1</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="12"/>
@@ -23349,10 +22997,10 @@
         <v>1</v>
       </c>
       <c r="C97" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>279</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
@@ -23370,10 +23018,10 @@
         <v>1</v>
       </c>
       <c r="C98" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D98" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>279</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
@@ -23391,10 +23039,10 @@
         <v>1</v>
       </c>
       <c r="C99" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D99" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>279</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -23412,19 +23060,19 @@
         <v>1</v>
       </c>
       <c r="C100" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D100" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J100" s="12"/>
     </row>
@@ -23437,23 +23085,23 @@
         <v>1</v>
       </c>
       <c r="C101" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D101" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G101" s="12">
         <v>0</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J101" s="12"/>
     </row>
@@ -23466,23 +23114,23 @@
         <v>1</v>
       </c>
       <c r="C102" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D102" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G102" s="12">
         <v>0</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J102" s="12"/>
     </row>
@@ -23495,10 +23143,10 @@
         <v>1</v>
       </c>
       <c r="C103" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D103" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
@@ -23516,23 +23164,23 @@
         <v>1</v>
       </c>
       <c r="C104" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D104" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G104" s="12">
         <v>0</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J104" s="12"/>
     </row>
@@ -23545,23 +23193,23 @@
         <v>1</v>
       </c>
       <c r="C105" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D105" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D105" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G105" s="12">
         <v>0</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J105" s="12">
         <v>1</v>
@@ -23576,23 +23224,23 @@
         <v>1</v>
       </c>
       <c r="C106" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D106" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G106" s="8">
         <v>0</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J106" s="12"/>
     </row>
@@ -23606,7 +23254,7 @@
       </c>
       <c r="C107" s="12"/>
       <c r="D107" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="8"/>
@@ -23624,19 +23272,19 @@
         <v>1</v>
       </c>
       <c r="C108" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D108" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
       <c r="H108" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J108" s="12"/>
     </row>
@@ -23649,10 +23297,10 @@
         <v>1</v>
       </c>
       <c r="C109" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D109" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="8"/>
@@ -23670,23 +23318,23 @@
         <v>1</v>
       </c>
       <c r="C110" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D110" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="D110" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G110" s="8">
         <v>0</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J110" s="12"/>
     </row>
@@ -23699,19 +23347,19 @@
         <v>1</v>
       </c>
       <c r="C111" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D111" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>284</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
       <c r="H111" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J111" s="12"/>
     </row>
@@ -23724,17 +23372,17 @@
         <v>1</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D112" s="12"/>
       <c r="E112" s="12"/>
       <c r="F112" s="8"/>
       <c r="G112" s="8"/>
       <c r="H112" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J112" s="12"/>
     </row>
@@ -23747,19 +23395,19 @@
         <v>1</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
       <c r="H113" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J113" s="12"/>
     </row>
@@ -23772,14 +23420,14 @@
         <v>1</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G114" s="8"/>
       <c r="H114" s="12"/>
@@ -23795,7 +23443,7 @@
         <v>1</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D115" s="12"/>
       <c r="E115" s="12"/>
@@ -23814,7 +23462,7 @@
         <v>1</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D116" s="12"/>
       <c r="E116" s="12"/>
@@ -23833,10 +23481,10 @@
         <v>1</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="8"/>
@@ -23854,10 +23502,10 @@
         <v>1</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="8"/>
@@ -23875,10 +23523,10 @@
         <v>1</v>
       </c>
       <c r="C119" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D119" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>279</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="8"/>
@@ -23896,23 +23544,23 @@
         <v>1</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G120" s="8">
         <v>0</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I120" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J120" s="12"/>
     </row>
@@ -26078,22 +25726,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A88:A300">
-    <cfRule type="expression" dxfId="28" priority="12">
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:J300">
-    <cfRule type="expression" dxfId="27" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:J300">
-    <cfRule type="expression" dxfId="26" priority="36">
+    <cfRule type="expression" dxfId="8" priority="36">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E300">
-    <cfRule type="expression" dxfId="25" priority="9">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26119,10 +25767,10 @@
         <v>177</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -26130,7 +25778,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C2" s="28"/>
     </row>
@@ -26139,7 +25787,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C3" s="12"/>
     </row>
@@ -26148,7 +25796,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C4" s="12"/>
     </row>
@@ -26157,7 +25805,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -26166,7 +25814,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C6" s="12"/>
     </row>
@@ -26175,7 +25823,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C7" s="12"/>
     </row>
@@ -26184,7 +25832,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C8" s="12"/>
     </row>
@@ -26193,7 +25841,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C9" s="12"/>
     </row>
@@ -26202,7 +25850,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C10" s="12"/>
     </row>
@@ -26211,7 +25859,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C11" s="12"/>
     </row>
@@ -26220,7 +25868,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -26229,7 +25877,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -26238,7 +25886,7 @@
         <v>39</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -26254,16 +25902,16 @@
         <v>45</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="B17" s="31" t="s">
         <v>298</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>299</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -26279,7 +25927,7 @@
         <v>50</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C19" s="12"/>
     </row>
@@ -26295,7 +25943,7 @@
         <v>53</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C21" s="12"/>
     </row>
@@ -26304,7 +25952,7 @@
         <v>55</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C22" s="12"/>
     </row>
@@ -26320,7 +25968,7 @@
         <v>59</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C24" s="12"/>
     </row>
@@ -26329,7 +25977,7 @@
         <v>61</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C25" s="12"/>
     </row>
@@ -26338,7 +25986,7 @@
         <v>62</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C26" s="12"/>
     </row>
@@ -26347,7 +25995,7 @@
         <v>63</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C27" s="12"/>
     </row>
@@ -26356,7 +26004,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C28" s="12"/>
     </row>
@@ -26365,7 +26013,7 @@
         <v>65</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C29" s="12"/>
     </row>
@@ -26374,7 +26022,7 @@
         <v>67</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C30" s="12"/>
     </row>
@@ -26383,7 +26031,7 @@
         <v>69</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C31" s="12"/>
     </row>
@@ -26392,7 +26040,7 @@
         <v>70</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C32" s="12"/>
     </row>
@@ -26401,7 +26049,7 @@
         <v>72</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C33" s="12"/>
     </row>
@@ -26410,7 +26058,7 @@
         <v>73</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C34" s="12"/>
     </row>
@@ -26419,7 +26067,7 @@
         <v>75</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C35" s="12"/>
     </row>
@@ -26435,7 +26083,7 @@
         <v>77</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C37" s="12"/>
     </row>
@@ -26444,7 +26092,7 @@
         <v>78</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C38" s="12"/>
     </row>
@@ -26453,7 +26101,7 @@
         <v>79</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C39" s="12"/>
     </row>
@@ -26469,7 +26117,7 @@
         <v>81</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C41" s="12"/>
     </row>
@@ -26478,7 +26126,7 @@
         <v>82</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C42" s="12"/>
     </row>
@@ -26487,7 +26135,7 @@
         <v>83</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C43" s="12"/>
     </row>
@@ -26594,7 +26242,7 @@
         <v>99</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C58" s="12"/>
     </row>
@@ -26603,7 +26251,7 @@
         <v>100</v>
       </c>
       <c r="B59" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C59" s="12"/>
     </row>
@@ -26612,7 +26260,7 @@
         <v>101</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C60" s="12"/>
     </row>
@@ -26621,7 +26269,7 @@
         <v>102</v>
       </c>
       <c r="B61" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C61" s="12"/>
     </row>
@@ -26630,7 +26278,7 @@
         <v>104</v>
       </c>
       <c r="B62" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C62" s="12"/>
     </row>
@@ -26639,7 +26287,7 @@
         <v>105</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C63" s="12"/>
     </row>
@@ -26648,7 +26296,7 @@
         <v>106</v>
       </c>
       <c r="B64" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C64" s="12"/>
     </row>
@@ -26657,7 +26305,7 @@
         <v>109</v>
       </c>
       <c r="B65" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C65" s="12"/>
     </row>
@@ -26666,7 +26314,7 @@
         <v>111</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C66" s="12"/>
     </row>
@@ -26675,7 +26323,7 @@
         <v>112</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C67" s="12"/>
     </row>
@@ -26684,7 +26332,7 @@
         <v>113</v>
       </c>
       <c r="B68" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="12"/>
     </row>
@@ -26693,7 +26341,7 @@
         <v>114</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C69" s="12"/>
     </row>
@@ -26702,7 +26350,7 @@
         <v>115</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C70" s="12"/>
     </row>
@@ -26711,7 +26359,7 @@
         <v>116</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C71" s="12"/>
     </row>
@@ -26720,7 +26368,7 @@
         <v>117</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C72" s="12"/>
     </row>
@@ -26729,7 +26377,7 @@
         <v>118</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C73" s="12"/>
     </row>
@@ -26738,7 +26386,7 @@
         <v>119</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C74" s="12"/>
     </row>
@@ -26747,7 +26395,7 @@
         <v>120</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C75" s="12"/>
     </row>
@@ -26756,7 +26404,7 @@
         <v>121</v>
       </c>
       <c r="B76" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C76" s="12"/>
     </row>
@@ -26765,7 +26413,7 @@
         <v>123</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C77" s="12"/>
     </row>
@@ -26774,7 +26422,7 @@
         <v>126</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C78" s="12"/>
     </row>
@@ -26783,7 +26431,7 @@
         <v>127</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C79" s="12"/>
     </row>
@@ -26792,7 +26440,7 @@
         <v>128</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C80" s="12"/>
     </row>
@@ -26801,7 +26449,7 @@
         <v>131</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C81" s="12"/>
     </row>
@@ -26810,7 +26458,7 @@
         <v>132</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C82" s="12"/>
     </row>
@@ -26819,7 +26467,7 @@
         <v>133</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C83" s="12"/>
     </row>
@@ -26828,7 +26476,7 @@
         <v>135</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C84" s="12"/>
     </row>
@@ -26837,7 +26485,7 @@
         <v>136</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C85" s="12"/>
     </row>
@@ -26846,7 +26494,7 @@
         <v>138</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C86" s="12"/>
     </row>
@@ -26855,7 +26503,7 @@
         <v>139</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C87" s="12"/>
     </row>
@@ -26864,7 +26512,7 @@
         <v>140</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C88" s="12"/>
     </row>
@@ -26873,7 +26521,7 @@
         <v>142</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C89" s="12"/>
     </row>
@@ -26882,7 +26530,7 @@
         <v>144</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C90" s="12"/>
     </row>
@@ -26891,7 +26539,7 @@
         <v>146</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C91" s="12"/>
     </row>
@@ -26900,7 +26548,7 @@
         <v>148</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C92" s="12"/>
     </row>
@@ -26909,7 +26557,7 @@
         <v>150</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C93" s="12"/>
     </row>
@@ -26918,7 +26566,7 @@
         <v>152</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C94" s="12"/>
     </row>
@@ -26927,7 +26575,7 @@
         <v>154</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C95" s="12"/>
     </row>
@@ -26936,7 +26584,7 @@
         <v>156</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C96" s="12"/>
     </row>
@@ -26945,7 +26593,7 @@
         <v>158</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C97" s="12"/>
     </row>
@@ -26954,7 +26602,7 @@
         <v>160</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C98" s="12"/>
     </row>
@@ -26963,7 +26611,7 @@
         <v>162</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C99" s="12"/>
     </row>
@@ -26972,7 +26620,7 @@
         <v>110</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C100" s="12"/>
     </row>
@@ -26981,7 +26629,7 @@
         <v>165</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C101" s="12"/>
     </row>
@@ -26990,7 +26638,7 @@
         <v>167</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C102" s="12"/>
     </row>
@@ -26999,7 +26647,7 @@
         <v>168</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C103" s="12"/>
     </row>
@@ -27008,7 +26656,7 @@
         <v>169</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C104" s="12"/>
     </row>
@@ -27017,7 +26665,7 @@
         <v>170</v>
       </c>
       <c r="B105" s="32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C105" s="12"/>
     </row>
@@ -27026,7 +26674,7 @@
         <v>171</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C106" s="12"/>
     </row>
@@ -27035,7 +26683,7 @@
         <v>172</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C107" s="12"/>
     </row>
@@ -27044,7 +26692,7 @@
         <v>174</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C108" s="12"/>
     </row>
@@ -27109,35 +26757,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A108">
-    <cfRule type="expression" dxfId="24" priority="11">
+    <cfRule type="expression" dxfId="6" priority="11">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="12">
+    <cfRule type="expression" dxfId="5" priority="12">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A77:A86">
-    <cfRule type="expression" dxfId="22" priority="13">
+    <cfRule type="expression" dxfId="4" priority="13">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:A108">
-    <cfRule type="expression" dxfId="21" priority="18">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112:A116">
-    <cfRule type="expression" dxfId="20" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C80 B81:B108 C81:C110 B106:C116 A109:B111 A112:C121">
-    <cfRule type="expression" dxfId="19" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C80 B81:B108 C81:C111 A109:B111 A112:C121 A1:C1">
-    <cfRule type="expression" dxfId="18" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27161,13 +26809,13 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>45937.610279513887</v>
+        <v>45959.666158217595</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.natsikas\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF06D0C8-D14D-42E3-B664-E4F6B0C867F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5870E3A-790B-4DDB-BEBE-3E7E984E7F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -1209,7 +1209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="342">
   <si>
     <t>Report Name</t>
   </si>
@@ -2236,6 +2236,9 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>MS</t>
   </si>
 </sst>
 </file>
@@ -22926,10 +22929,10 @@
         <v>1</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>283</v>
+        <v>341</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12" t="s">
@@ -26815,7 +26818,7 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>45959.666158217595</v>
+        <v>45959.687491319448</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.natsikas\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanos\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5870E3A-790B-4DDB-BEBE-3E7E984E7F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B4A204-7D62-4EF7-8D48-DAA9BEC30406}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,19 +26,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Read Settings'!$A$1:$I$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Time Settings'!$A$1:$J$120</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -1209,7 +1198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="341">
   <si>
     <t>Report Name</t>
   </si>
@@ -2233,9 +2222,6 @@
   </si>
   <si>
     <t>Header</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
   <si>
     <t>MS</t>
@@ -3686,9 +3672,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3726,7 +3712,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3832,7 +3818,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3974,7 +3960,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -10675,7 +10661,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L120" xr:uid="{D0972C50-907B-4A2C-82F0-ED51F06329AA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L120">
+    <sortState ref="A2:L120">
       <sortCondition ref="A2:A120"/>
     </sortState>
   </autoFilter>
@@ -11059,8 +11045,8 @@
       <c r="G2" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>340</v>
+      <c r="H2" s="12">
+        <v>0</v>
       </c>
       <c r="I2" s="19"/>
     </row>
@@ -15704,7 +15690,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I111" xr:uid="{776C4DE2-2957-440A-A09D-B0AB3152981D}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I120">
+    <sortState ref="A2:I120">
       <sortCondition ref="A1:A111"/>
     </sortState>
   </autoFilter>
@@ -20223,7 +20209,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I109" xr:uid="{44BD8FFD-EDA1-47AD-AC03-3890015323F4}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I120">
+    <sortState ref="A2:I120">
       <sortCondition ref="A1:A109"/>
     </sortState>
   </autoFilter>
@@ -22929,10 +22915,10 @@
         <v>1</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12" t="s">
@@ -26818,7 +26804,7 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>45959.687491319448</v>
+        <v>45960.470200462965</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanos\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B4A204-7D62-4EF7-8D48-DAA9BEC30406}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4622A4F1-3914-4E1A-8CD3-A33C23928E79}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -1858,9 +1858,6 @@
     <t>['IMBABE']</t>
   </si>
   <si>
-    <t>range(1,51,1)</t>
-  </si>
-  <si>
     <t>['ISPRequirements']</t>
   </si>
   <si>
@@ -2225,6 +2222,9 @@
   </si>
   <si>
     <t>MS</t>
+  </si>
+  <si>
+    <t>range(1,101,1)</t>
   </si>
 </sst>
 </file>
@@ -5038,7 +5038,7 @@
         <v>42005</v>
       </c>
       <c r="G31" s="48" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H31" s="8" t="b">
         <f>TRUE()</f>
@@ -5105,10 +5105,10 @@
         <v>176</v>
       </c>
       <c r="F33" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G33" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H33" s="8" t="b">
         <f>TRUE()</f>
@@ -5140,10 +5140,10 @@
         <v>176</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G34" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H34" s="8" t="b">
         <f>TRUE()</f>
@@ -5175,10 +5175,10 @@
         <v>176</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G35" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H35" s="8" t="b">
         <f>TRUE()</f>
@@ -5210,10 +5210,10 @@
         <v>176</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G36" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H36" s="8" t="b">
         <f>TRUE()</f>
@@ -5247,10 +5247,10 @@
         <v>176</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G37" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H37" s="8" t="b">
         <f>TRUE()</f>
@@ -5282,10 +5282,10 @@
         <v>176</v>
       </c>
       <c r="F38" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G38" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H38" s="8" t="b">
         <f>TRUE()</f>
@@ -5317,10 +5317,10 @@
         <v>176</v>
       </c>
       <c r="F39" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G39" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H39" s="8" t="b">
         <f>TRUE()</f>
@@ -5352,10 +5352,10 @@
         <v>176</v>
       </c>
       <c r="F40" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G40" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H40" s="8" t="b">
         <f>TRUE()</f>
@@ -5389,10 +5389,10 @@
         <v>176</v>
       </c>
       <c r="F41" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G41" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H41" s="8" t="b">
         <f>TRUE()</f>
@@ -5424,10 +5424,10 @@
         <v>176</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G42" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H42" s="8" t="b">
         <f>TRUE()</f>
@@ -5459,10 +5459,10 @@
         <v>176</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G43" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H43" s="8" t="b">
         <f>TRUE()</f>
@@ -5494,10 +5494,10 @@
         <v>176</v>
       </c>
       <c r="F44" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G44" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H44" s="8" t="b">
         <f>TRUE()</f>
@@ -5518,7 +5518,7 @@
     </row>
     <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8" t="s">
@@ -5531,7 +5531,7 @@
         <v>176</v>
       </c>
       <c r="F45" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G45" s="47"/>
       <c r="H45" s="8" t="b">
@@ -5551,7 +5551,7 @@
     </row>
     <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="8" t="s">
@@ -5564,7 +5564,7 @@
         <v>176</v>
       </c>
       <c r="F46" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G46" s="47">
         <v>45930</v>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="8" t="s">
@@ -5599,7 +5599,7 @@
         <v>176</v>
       </c>
       <c r="F47" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G47" s="47"/>
       <c r="H47" s="8" t="b">
@@ -5619,7 +5619,7 @@
     </row>
     <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="8" t="s">
@@ -5632,7 +5632,7 @@
         <v>176</v>
       </c>
       <c r="F48" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G48" s="47">
         <v>45930</v>
@@ -5654,7 +5654,7 @@
     </row>
     <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="8" t="s">
@@ -5667,7 +5667,7 @@
         <v>176</v>
       </c>
       <c r="F49" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G49" s="47"/>
       <c r="H49" s="8" t="b">
@@ -5687,7 +5687,7 @@
     </row>
     <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="8" t="s">
@@ -5700,7 +5700,7 @@
         <v>176</v>
       </c>
       <c r="F50" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G50" s="47">
         <v>45930</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="8" t="s">
@@ -5735,7 +5735,7 @@
         <v>176</v>
       </c>
       <c r="F51" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G51" s="47"/>
       <c r="H51" s="8" t="b">
@@ -5755,7 +5755,7 @@
     </row>
     <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
@@ -5768,7 +5768,7 @@
         <v>176</v>
       </c>
       <c r="F52" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G52" s="47">
         <v>45930</v>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="53" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="8" t="s">
@@ -5803,7 +5803,7 @@
         <v>176</v>
       </c>
       <c r="F53" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G53" s="47"/>
       <c r="H53" s="8" t="b">
@@ -5823,7 +5823,7 @@
     </row>
     <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="8" t="s">
@@ -5836,7 +5836,7 @@
         <v>176</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G54" s="47">
         <v>45930</v>
@@ -5858,7 +5858,7 @@
     </row>
     <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="8" t="s">
@@ -5871,7 +5871,7 @@
         <v>176</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G55" s="47"/>
       <c r="H55" s="8" t="b">
@@ -5891,7 +5891,7 @@
     </row>
     <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="8" t="s">
@@ -5904,7 +5904,7 @@
         <v>176</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G56" s="47">
         <v>45930</v>
@@ -5942,7 +5942,7 @@
         <v>43841</v>
       </c>
       <c r="G57" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H57" s="8" t="b">
         <f>TRUE()</f>
@@ -5977,7 +5977,7 @@
         <v>43841</v>
       </c>
       <c r="G58" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H58" s="8" t="b">
         <f>TRUE()</f>
@@ -6014,7 +6014,7 @@
         <v>43841</v>
       </c>
       <c r="G59" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H59" s="8" t="b">
         <f>TRUE()</f>
@@ -6049,7 +6049,7 @@
         <v>43841</v>
       </c>
       <c r="G60" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H60" s="8" t="b">
         <f>TRUE()</f>
@@ -6086,7 +6086,7 @@
         <v>43841</v>
       </c>
       <c r="G61" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H61" s="8" t="b">
         <f>TRUE()</f>
@@ -6121,7 +6121,7 @@
         <v>43841</v>
       </c>
       <c r="G62" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H62" s="8" t="b">
         <f>TRUE()</f>
@@ -6158,7 +6158,7 @@
         <v>43841</v>
       </c>
       <c r="G63" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H63" s="8" t="b">
         <f>TRUE()</f>
@@ -6193,7 +6193,7 @@
         <v>43841</v>
       </c>
       <c r="G64" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H64" s="8" t="b">
         <f>TRUE()</f>
@@ -6230,7 +6230,7 @@
         <v>43841</v>
       </c>
       <c r="G65" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H65" s="8" t="b">
         <f>TRUE()</f>
@@ -6265,7 +6265,7 @@
         <v>43841</v>
       </c>
       <c r="G66" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H66" s="8" t="b">
         <f>TRUE()</f>
@@ -6302,7 +6302,7 @@
         <v>43841</v>
       </c>
       <c r="G67" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H67" s="8" t="b">
         <f>TRUE()</f>
@@ -6337,7 +6337,7 @@
         <v>43841</v>
       </c>
       <c r="G68" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H68" s="8" t="b">
         <f>TRUE()</f>
@@ -6503,16 +6503,14 @@
       <c r="F73" s="40">
         <v>44124</v>
       </c>
-      <c r="G73" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G73" s="47"/>
       <c r="H73" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I73" s="7" t="b">
         <f>IF(Metadata!G73="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="13" t="b">
         <f>TRUE()</f>
@@ -6538,16 +6536,14 @@
       <c r="F74" s="40">
         <v>44124</v>
       </c>
-      <c r="G74" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G74" s="47"/>
       <c r="H74" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I74" s="7" t="b">
         <f>IF(Metadata!G74="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="13" t="b">
         <f>TRUE()</f>
@@ -6674,16 +6670,14 @@
       <c r="F78" s="40">
         <v>44124</v>
       </c>
-      <c r="G78" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G78" s="47"/>
       <c r="H78" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I78" s="7" t="b">
         <f>IF(Metadata!G78="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" s="13" t="b">
         <f>TRUE()</f>
@@ -6709,16 +6703,14 @@
       <c r="F79" s="40">
         <v>44124</v>
       </c>
-      <c r="G79" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G79" s="47"/>
       <c r="H79" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I79" s="7" t="b">
         <f>IF(Metadata!G79="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="13" t="b">
         <f>TRUE()</f>
@@ -6843,16 +6835,14 @@
       <c r="F83" s="40">
         <v>44124</v>
       </c>
-      <c r="G83" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G83" s="47"/>
       <c r="H83" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I83" s="7" t="b">
         <f>IF(Metadata!G83="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" s="13" t="b">
         <f>TRUE()</f>
@@ -6878,16 +6868,14 @@
       <c r="F84" s="40">
         <v>44124</v>
       </c>
-      <c r="G84" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G84" s="47"/>
       <c r="H84" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I84" s="7" t="b">
         <f>IF(Metadata!G84="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="13" t="b">
         <f>TRUE()</f>
@@ -11020,7 +11008,7 @@
         <v>182</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>183</v>
@@ -11201,7 +11189,7 @@
         <v>187</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H10" s="12">
         <v>0</v>
@@ -11225,7 +11213,7 @@
         <v>206</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H11" s="12">
         <v>0</v>
@@ -12002,7 +11990,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B45" s="41" t="b">
         <f>Metadata!A45=A45</f>
@@ -12026,7 +12014,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B46" s="41" t="b">
         <f>Metadata!A46=A46</f>
@@ -12050,7 +12038,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" s="41" t="b">
         <f>Metadata!A47=A47</f>
@@ -12076,7 +12064,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B48" s="41" t="b">
         <f>Metadata!A48=A48</f>
@@ -12102,7 +12090,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" s="41" t="b">
         <f>Metadata!A49=A49</f>
@@ -12126,7 +12114,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B50" s="41" t="b">
         <f>Metadata!A50=A50</f>
@@ -12150,7 +12138,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B51" s="41" t="b">
         <f>Metadata!A51=A51</f>
@@ -12176,7 +12164,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B52" s="41" t="b">
         <f>Metadata!A52=A52</f>
@@ -12202,7 +12190,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B53" s="41" t="b">
         <f>Metadata!A53=A53</f>
@@ -12226,7 +12214,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" s="41" t="b">
         <f>Metadata!A54=A54</f>
@@ -12250,7 +12238,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B55" s="41" t="b">
         <f>Metadata!A55=A55</f>
@@ -12276,7 +12264,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B56" s="41" t="b">
         <f>Metadata!A56=A56</f>
@@ -12704,10 +12692,10 @@
         <v>204</v>
       </c>
       <c r="H73" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -12730,10 +12718,10 @@
         <v>205</v>
       </c>
       <c r="H74" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -12777,7 +12765,7 @@
         <v>187</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H76" s="12">
         <v>0</v>
@@ -12830,10 +12818,10 @@
         <v>204</v>
       </c>
       <c r="H78" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
@@ -12856,10 +12844,10 @@
         <v>205</v>
       </c>
       <c r="H79" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
@@ -12903,7 +12891,7 @@
         <v>187</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H81" s="12">
         <v>0</v>
@@ -12956,10 +12944,10 @@
         <v>204</v>
       </c>
       <c r="H83" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
@@ -12982,10 +12970,10 @@
         <v>205</v>
       </c>
       <c r="H84" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
@@ -13029,7 +13017,7 @@
         <v>187</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H86" s="12">
         <v>0</v>
@@ -13097,7 +13085,7 @@
         <v>187</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H89" s="12">
         <v>0</v>
@@ -13121,7 +13109,7 @@
         <v>187</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H90" s="12">
         <v>0</v>
@@ -13156,20 +13144,20 @@
         <v>203</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E92" s="18"/>
       <c r="F92" s="12" t="s">
         <v>187</v>
       </c>
       <c r="G92" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H92" s="12">
+        <v>1</v>
+      </c>
+      <c r="I92" s="12" t="s">
         <v>223</v>
-      </c>
-      <c r="H92" s="12">
-        <v>1</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
@@ -13200,14 +13188,14 @@
         <v>184</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E94" s="18"/>
       <c r="F94" s="12" t="s">
         <v>194</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H94" s="12">
         <v>2</v>
@@ -13333,7 +13321,7 @@
         <v>187</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H101" s="12">
         <v>1</v>
@@ -13357,7 +13345,7 @@
         <v>187</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H102" s="12">
         <v>1</v>
@@ -13397,7 +13385,7 @@
         <v>187</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H104" s="12">
         <v>2</v>
@@ -13416,14 +13404,14 @@
         <v>203</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E105" s="18"/>
       <c r="F105" s="12" t="s">
         <v>187</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H105" s="12">
         <v>0</v>
@@ -13442,20 +13430,20 @@
         <v>203</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E106" s="18"/>
       <c r="F106" s="12" t="s">
         <v>187</v>
       </c>
       <c r="G106" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="H106" s="12">
+        <v>0</v>
+      </c>
+      <c r="I106" s="12" t="s">
         <v>231</v>
-      </c>
-      <c r="H106" s="12">
-        <v>0</v>
-      </c>
-      <c r="I106" s="12" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
@@ -13485,7 +13473,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D108" s="18"/>
       <c r="E108" s="18"/>
@@ -13526,16 +13514,16 @@
       <c r="D110" s="8"/>
       <c r="E110" s="18"/>
       <c r="F110" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="G110" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="G110" s="8" t="s">
-        <v>235</v>
       </c>
       <c r="H110" s="12">
         <v>4</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
@@ -13579,7 +13567,7 @@
         <v>1</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="18"/>
@@ -13698,10 +13686,10 @@
       <c r="D120" s="8"/>
       <c r="E120" s="18"/>
       <c r="F120" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="G120" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>238</v>
       </c>
       <c r="H120" s="12">
         <v>2</v>
@@ -15790,25 +15778,25 @@
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -15820,17 +15808,17 @@
         <v>1</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>248</v>
       </c>
       <c r="H2" s="25"/>
       <c r="I2" s="26"/>
@@ -15880,7 +15868,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="20"/>
@@ -15898,7 +15886,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="20"/>
@@ -15964,7 +15952,7 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H10" s="27" t="b">
         <v>0</v>
@@ -15982,13 +15970,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="20"/>
@@ -16022,7 +16010,7 @@
       <c r="E13" s="14"/>
       <c r="F13" s="8"/>
       <c r="G13" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H13" s="27" t="b">
         <f>TRUE()</f>
@@ -16046,7 +16034,7 @@
       <c r="E14" s="14"/>
       <c r="F14" s="8"/>
       <c r="G14" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H14" s="27" t="b">
         <f>TRUE()</f>
@@ -16070,7 +16058,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H15" s="27" t="b">
         <f>TRUE()</f>
@@ -16094,7 +16082,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="8"/>
       <c r="G16" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H16" s="27" t="b">
         <f>TRUE()</f>
@@ -16118,7 +16106,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="8"/>
       <c r="G17" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H17" s="27" t="b">
         <f>TRUE()</f>
@@ -16138,13 +16126,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="14"/>
       <c r="F18" s="8"/>
       <c r="G18" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H18" s="27" t="b">
         <f>FALSE()</f>
@@ -16165,7 +16153,7 @@
       <c r="E19" s="14"/>
       <c r="F19" s="8"/>
       <c r="G19" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H19" s="27" t="b">
         <f>TRUE()</f>
@@ -16185,13 +16173,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="14"/>
       <c r="F20" s="8"/>
       <c r="G20" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H20" s="27"/>
       <c r="I20" s="20"/>
@@ -16205,15 +16193,15 @@
         <v>1</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H21" s="27" t="b">
         <f>FALSE()</f>
@@ -16232,11 +16220,11 @@
       <c r="C22" s="23"/>
       <c r="D22" s="24"/>
       <c r="E22" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H22" s="27"/>
       <c r="I22" s="20"/>
@@ -16250,13 +16238,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H23" s="27"/>
       <c r="I23" s="20"/>
@@ -16302,15 +16290,15 @@
         <v>1</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H26" s="27"/>
       <c r="I26" s="20"/>
@@ -16356,13 +16344,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H29" s="27"/>
       <c r="I29" s="20"/>
@@ -16412,7 +16400,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H32" s="27" t="b">
         <f>FALSE()</f>
@@ -16436,7 +16424,7 @@
       <c r="E33" s="14"/>
       <c r="F33" s="8"/>
       <c r="G33" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H33" s="27" t="b">
         <f>TRUE()</f>
@@ -16460,7 +16448,7 @@
       <c r="E34" s="14"/>
       <c r="F34" s="8"/>
       <c r="G34" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H34" s="27" t="b">
         <f>TRUE()</f>
@@ -16484,7 +16472,7 @@
       <c r="E35" s="14"/>
       <c r="F35" s="8"/>
       <c r="G35" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H35" s="27" t="b">
         <f>TRUE()</f>
@@ -16504,13 +16492,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="14"/>
       <c r="F36" s="8"/>
       <c r="G36" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H36" s="27"/>
       <c r="I36" s="20"/>
@@ -16528,7 +16516,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="8"/>
       <c r="G37" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H37" s="27" t="b">
         <f>TRUE()</f>
@@ -16552,7 +16540,7 @@
       <c r="E38" s="14"/>
       <c r="F38" s="8"/>
       <c r="G38" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H38" s="27" t="b">
         <f>TRUE()</f>
@@ -16576,7 +16564,7 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8"/>
       <c r="G39" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H39" s="27" t="b">
         <f>TRUE()</f>
@@ -16596,13 +16584,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="14"/>
       <c r="F40" s="8"/>
       <c r="G40" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H40" s="27"/>
       <c r="I40" s="20"/>
@@ -16620,7 +16608,7 @@
       <c r="E41" s="14"/>
       <c r="F41" s="8"/>
       <c r="G41" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H41" s="27" t="b">
         <f>TRUE()</f>
@@ -16644,7 +16632,7 @@
       <c r="E42" s="14"/>
       <c r="F42" s="8"/>
       <c r="G42" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H42" s="27" t="b">
         <f>TRUE()</f>
@@ -16668,7 +16656,7 @@
       <c r="E43" s="14"/>
       <c r="F43" s="8"/>
       <c r="G43" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H43" s="27" t="b">
         <f>TRUE()</f>
@@ -16688,20 +16676,20 @@
         <v>1</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="14"/>
       <c r="F44" s="8"/>
       <c r="G44" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H44" s="27"/>
       <c r="I44" s="20"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B45" s="41" t="b">
         <f>A45=Metadata!A45</f>
@@ -16712,7 +16700,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H45" s="27" t="b">
         <f>TRUE()</f>
@@ -16725,7 +16713,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B46" s="41" t="b">
         <f>A46=Metadata!A46</f>
@@ -16736,7 +16724,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H46" s="27" t="b">
         <f>TRUE()</f>
@@ -16749,7 +16737,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" s="41" t="b">
         <f>A47=Metadata!A47</f>
@@ -16760,7 +16748,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H47" s="27" t="b">
         <f>TRUE()</f>
@@ -16773,27 +16761,27 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B48" s="41" t="b">
         <f>A48=Metadata!A48</f>
         <v>1</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H48" s="27"/>
       <c r="I48" s="20"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" s="41" t="b">
         <f>A49=Metadata!A49</f>
@@ -16804,7 +16792,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H49" s="27" t="b">
         <f>TRUE()</f>
@@ -16817,7 +16805,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B50" s="41" t="b">
         <f>A50=Metadata!A50</f>
@@ -16828,7 +16816,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
       <c r="G50" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H50" s="27" t="b">
         <f>TRUE()</f>
@@ -16841,7 +16829,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B51" s="41" t="b">
         <f>A51=Metadata!A51</f>
@@ -16852,7 +16840,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H51" s="27" t="b">
         <f>TRUE()</f>
@@ -16865,27 +16853,27 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B52" s="41" t="b">
         <f>A52=Metadata!A52</f>
         <v>1</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H52" s="45"/>
       <c r="I52" s="20"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B53" s="41" t="b">
         <f>A53=Metadata!A53</f>
@@ -16896,7 +16884,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H53" s="27" t="b">
         <f>TRUE()</f>
@@ -16909,7 +16897,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" s="41" t="b">
         <f>A54=Metadata!A54</f>
@@ -16920,7 +16908,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H54" s="27" t="b">
         <f>TRUE()</f>
@@ -16933,7 +16921,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B55" s="41" t="b">
         <f>A55=Metadata!A55</f>
@@ -16944,7 +16932,7 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H55" s="27" t="b">
         <f>TRUE()</f>
@@ -16957,20 +16945,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B56" s="41" t="b">
         <f>A56=Metadata!A56</f>
         <v>1</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H56" s="45"/>
       <c r="I56" s="20"/>
@@ -16988,7 +16976,7 @@
       <c r="E57" s="14"/>
       <c r="F57" s="8"/>
       <c r="G57" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H57" s="27" t="b">
         <f>TRUE()</f>
@@ -17012,7 +17000,7 @@
       <c r="E58" s="14"/>
       <c r="F58" s="8"/>
       <c r="G58" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H58" s="27" t="b">
         <f>TRUE()</f>
@@ -17036,7 +17024,7 @@
       <c r="E59" s="14"/>
       <c r="F59" s="8"/>
       <c r="G59" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H59" s="27" t="b">
         <f>TRUE()</f>
@@ -17056,13 +17044,13 @@
         <v>1</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="14"/>
       <c r="F60" s="8"/>
       <c r="G60" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H60" s="27"/>
       <c r="I60" s="20"/>
@@ -17080,7 +17068,7 @@
       <c r="E61" s="14"/>
       <c r="F61" s="8"/>
       <c r="G61" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H61" s="27" t="b">
         <f>TRUE()</f>
@@ -17104,7 +17092,7 @@
       <c r="E62" s="14"/>
       <c r="F62" s="8"/>
       <c r="G62" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H62" s="27" t="b">
         <f>TRUE()</f>
@@ -17128,7 +17116,7 @@
       <c r="E63" s="14"/>
       <c r="F63" s="8"/>
       <c r="G63" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H63" s="27" t="b">
         <f>TRUE()</f>
@@ -17148,13 +17136,13 @@
         <v>1</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="14"/>
       <c r="F64" s="8"/>
       <c r="G64" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H64" s="27"/>
       <c r="I64" s="20"/>
@@ -17172,7 +17160,7 @@
       <c r="E65" s="44"/>
       <c r="F65" s="8"/>
       <c r="G65" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H65" s="27" t="b">
         <f>TRUE()</f>
@@ -17196,7 +17184,7 @@
       <c r="E66" s="14"/>
       <c r="F66" s="8"/>
       <c r="G66" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H66" s="27" t="b">
         <f>TRUE()</f>
@@ -17220,7 +17208,7 @@
       <c r="E67" s="14"/>
       <c r="F67" s="8"/>
       <c r="G67" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H67" s="27" t="b">
         <f>TRUE()</f>
@@ -17240,13 +17228,13 @@
         <v>1</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D68" s="24"/>
       <c r="E68" s="14"/>
       <c r="F68" s="8"/>
       <c r="G68" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H68" s="27"/>
       <c r="I68" s="20"/>
@@ -17264,7 +17252,7 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H69" s="27" t="b">
         <f>TRUE()</f>
@@ -17288,7 +17276,7 @@
       <c r="E70" s="23"/>
       <c r="F70" s="8"/>
       <c r="G70" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H70" s="27"/>
       <c r="I70" s="20"/>
@@ -17338,7 +17326,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H73" s="27"/>
       <c r="I73" s="20"/>
@@ -17356,7 +17344,7 @@
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
       <c r="G74" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H74" s="27"/>
       <c r="I74" s="20"/>
@@ -17370,17 +17358,17 @@
         <v>1</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D75" s="24"/>
       <c r="E75" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G75" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="G75" s="12" t="s">
-        <v>248</v>
       </c>
       <c r="H75" s="27"/>
       <c r="I75" s="20"/>
@@ -17394,13 +17382,13 @@
         <v>1</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D76" s="24"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H76" s="27"/>
       <c r="I76" s="20"/>
@@ -17414,15 +17402,15 @@
         <v>1</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D77" s="24"/>
       <c r="E77" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F77" s="8"/>
       <c r="G77" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H77" s="27"/>
       <c r="I77" s="20"/>
@@ -17440,7 +17428,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H78" s="27"/>
       <c r="I78" s="20"/>
@@ -17458,7 +17446,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H79" s="27"/>
       <c r="I79" s="20"/>
@@ -17472,17 +17460,17 @@
         <v>1</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D80" s="24"/>
       <c r="E80" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G80" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="G80" s="12" t="s">
-        <v>248</v>
       </c>
       <c r="H80" s="27"/>
       <c r="I80" s="20"/>
@@ -17496,13 +17484,13 @@
         <v>1</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D81" s="24"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
       <c r="G81" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H81" s="27"/>
       <c r="I81" s="20"/>
@@ -17516,15 +17504,15 @@
         <v>1</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H82" s="27"/>
       <c r="I82" s="20"/>
@@ -17542,7 +17530,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H83" s="27"/>
       <c r="I83" s="20"/>
@@ -17560,7 +17548,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H84" s="27"/>
       <c r="I84" s="20"/>
@@ -17574,17 +17562,17 @@
         <v>1</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D85" s="24"/>
       <c r="E85" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G85" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="G85" s="12" t="s">
-        <v>248</v>
       </c>
       <c r="H85" s="27"/>
       <c r="I85" s="20"/>
@@ -17598,13 +17586,13 @@
         <v>1</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D86" s="24"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
       <c r="G86" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H86" s="27"/>
       <c r="I86" s="20"/>
@@ -17618,15 +17606,15 @@
         <v>1</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D87" s="24"/>
       <c r="E87" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H87" s="27"/>
       <c r="I87" s="20"/>
@@ -17660,7 +17648,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
       <c r="G89" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H89" s="27" t="b">
         <f>TRUE()</f>
@@ -17684,7 +17672,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
       <c r="G90" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H90" s="27" t="b">
         <f>TRUE()</f>
@@ -17720,15 +17708,15 @@
         <v>1</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D92" s="24"/>
       <c r="E92" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H92" s="27"/>
       <c r="I92" s="20"/>
@@ -17762,7 +17750,7 @@
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
       <c r="G94" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H94" s="27" t="b">
         <v>0</v>
@@ -17880,7 +17868,7 @@
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
       <c r="G101" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H101" s="27"/>
       <c r="I101" s="20"/>
@@ -17898,7 +17886,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
       <c r="G102" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H102" s="27"/>
       <c r="I102" s="20"/>
@@ -17928,17 +17916,17 @@
         <v>1</v>
       </c>
       <c r="C104" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="D104" s="24" t="s">
         <v>260</v>
-      </c>
-      <c r="D104" s="24" t="s">
-        <v>261</v>
       </c>
       <c r="E104" s="8"/>
       <c r="F104" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H104" s="27"/>
       <c r="I104" s="20"/>
@@ -17956,7 +17944,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
       <c r="G105" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H105" s="27"/>
       <c r="I105" s="20"/>
@@ -17974,7 +17962,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
       <c r="G106" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H106" s="27" t="b">
         <f>FALSE()</f>
@@ -18042,15 +18030,15 @@
         <v>1</v>
       </c>
       <c r="C110" s="23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F110" s="8"/>
       <c r="G110" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H110" s="27"/>
       <c r="I110" s="20"/>
@@ -18084,7 +18072,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
       <c r="G112" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H112" s="27"/>
       <c r="I112" s="20"/>
@@ -18182,7 +18170,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
       <c r="G118" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H118" s="27" t="b">
         <f>TRUE()</f>
@@ -18222,7 +18210,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
       <c r="G120" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H120" s="27"/>
       <c r="I120" s="20"/>
@@ -20320,28 +20308,28 @@
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -20353,23 +20341,23 @@
         <v>1</v>
       </c>
       <c r="C2" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2" s="28" t="s">
         <v>270</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>271</v>
       </c>
       <c r="E2" s="28"/>
       <c r="F2" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="G2" s="28">
+        <v>0</v>
+      </c>
+      <c r="H2" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="G2" s="28">
-        <v>0</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>273</v>
-      </c>
       <c r="I2" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J2" s="28"/>
     </row>
@@ -20382,7 +20370,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
@@ -20401,7 +20389,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
@@ -20420,23 +20408,23 @@
         <v>1</v>
       </c>
       <c r="C5" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G5" s="12">
         <v>0</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J5" s="12"/>
     </row>
@@ -20449,23 +20437,23 @@
         <v>1</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G6" s="12">
         <v>0</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J6" s="12"/>
     </row>
@@ -20478,10 +20466,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -20499,10 +20487,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -20520,10 +20508,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -20541,23 +20529,23 @@
         <v>1</v>
       </c>
       <c r="C10" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J10" s="12"/>
     </row>
@@ -20570,21 +20558,21 @@
         <v>1</v>
       </c>
       <c r="C11" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J11" s="12"/>
     </row>
@@ -20597,19 +20585,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J12" s="12"/>
     </row>
@@ -20622,23 +20610,23 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G13" s="12">
         <v>0</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J13" s="12"/>
     </row>
@@ -20651,23 +20639,23 @@
         <v>1</v>
       </c>
       <c r="C14" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G14" s="12">
         <v>0</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J14" s="12"/>
     </row>
@@ -20680,21 +20668,21 @@
         <v>1</v>
       </c>
       <c r="C15" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J15" s="12"/>
     </row>
@@ -20707,25 +20695,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="E16" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="G16" s="12">
         <v>0</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J16" s="12"/>
     </row>
@@ -20738,23 +20726,23 @@
         <v>1</v>
       </c>
       <c r="C17" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J17" s="12"/>
     </row>
@@ -20767,25 +20755,25 @@
         <v>1</v>
       </c>
       <c r="C18" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="E18" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="G18" s="12">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J18" s="12"/>
     </row>
@@ -20798,25 +20786,25 @@
         <v>1</v>
       </c>
       <c r="C19" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="E19" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F19" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="G19" s="12">
         <v>0</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J19" s="12"/>
     </row>
@@ -20829,25 +20817,25 @@
         <v>1</v>
       </c>
       <c r="C20" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="E20" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F20" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="G20" s="12">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J20" s="12"/>
     </row>
@@ -20860,23 +20848,23 @@
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G21" s="12">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J21" s="12"/>
     </row>
@@ -20889,23 +20877,23 @@
         <v>1</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G22" s="12">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J22" s="12"/>
     </row>
@@ -20918,23 +20906,23 @@
         <v>1</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G23" s="12">
         <v>0</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J23" s="12"/>
     </row>
@@ -20947,10 +20935,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -20968,10 +20956,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -20989,23 +20977,23 @@
         <v>1</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G26" s="12"/>
       <c r="H26" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J26" s="12"/>
     </row>
@@ -21018,19 +21006,19 @@
         <v>1</v>
       </c>
       <c r="C27" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J27" s="12"/>
     </row>
@@ -21043,19 +21031,19 @@
         <v>1</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
       <c r="H28" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J28" s="12"/>
     </row>
@@ -21068,21 +21056,21 @@
         <v>1</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G29" s="12">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J29" s="12"/>
     </row>
@@ -21095,19 +21083,19 @@
         <v>1</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
       <c r="F30" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J30" s="12"/>
     </row>
@@ -21120,19 +21108,19 @@
         <v>1</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J31" s="12"/>
     </row>
@@ -21145,23 +21133,23 @@
         <v>1</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G32" s="12">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J32" s="12"/>
     </row>
@@ -21174,23 +21162,23 @@
         <v>1</v>
       </c>
       <c r="C33" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G33" s="12">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J33" s="12"/>
     </row>
@@ -21203,23 +21191,23 @@
         <v>1</v>
       </c>
       <c r="C34" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G34" s="12">
         <v>0</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J34" s="12"/>
     </row>
@@ -21232,23 +21220,23 @@
         <v>1</v>
       </c>
       <c r="C35" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G35" s="12">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J35" s="12"/>
     </row>
@@ -21261,23 +21249,23 @@
         <v>1</v>
       </c>
       <c r="C36" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G36" s="12">
         <v>0</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J36" s="12"/>
     </row>
@@ -21290,23 +21278,23 @@
         <v>1</v>
       </c>
       <c r="C37" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G37" s="12">
         <v>0</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J37" s="12"/>
     </row>
@@ -21319,23 +21307,23 @@
         <v>1</v>
       </c>
       <c r="C38" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G38" s="12">
         <v>0</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J38" s="12"/>
     </row>
@@ -21348,23 +21336,23 @@
         <v>1</v>
       </c>
       <c r="C39" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G39" s="12">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J39" s="12"/>
     </row>
@@ -21377,23 +21365,23 @@
         <v>1</v>
       </c>
       <c r="C40" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G40" s="12">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J40" s="12"/>
     </row>
@@ -21406,23 +21394,23 @@
         <v>1</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G41" s="12">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J41" s="12"/>
     </row>
@@ -21435,23 +21423,23 @@
         <v>1</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G42" s="12">
         <v>12</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J42" s="12"/>
     </row>
@@ -21464,23 +21452,23 @@
         <v>1</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G43" s="12">
         <v>12</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J43" s="12"/>
     </row>
@@ -21493,371 +21481,371 @@
         <v>1</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G44" s="12">
         <v>12</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J44" s="12"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B45" s="46" t="b">
         <f>A45=Metadata!A45</f>
         <v>1</v>
       </c>
       <c r="C45" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G45" s="12">
         <v>0</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J45" s="12"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B46" s="46" t="b">
         <f>A46=Metadata!A46</f>
         <v>1</v>
       </c>
       <c r="C46" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G46" s="12">
         <v>0</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J46" s="12"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" s="46" t="b">
         <f>A47=Metadata!A47</f>
         <v>1</v>
       </c>
       <c r="C47" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G47" s="12">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J47" s="12"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B48" s="46" t="b">
         <f>A48=Metadata!A48</f>
         <v>1</v>
       </c>
       <c r="C48" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G48" s="12">
         <v>0</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J48" s="12"/>
     </row>
     <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" s="46" t="b">
         <f>A49=Metadata!A49</f>
         <v>1</v>
       </c>
       <c r="C49" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D49" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G49" s="12">
         <v>0</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J49" s="12"/>
     </row>
     <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B50" s="46" t="b">
         <f>A50=Metadata!A50</f>
         <v>1</v>
       </c>
       <c r="C50" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G50" s="12">
         <v>0</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J50" s="12"/>
     </row>
     <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B51" s="46" t="b">
         <f>A51=Metadata!A51</f>
         <v>1</v>
       </c>
       <c r="C51" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G51" s="12">
         <v>0</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J51" s="12"/>
     </row>
     <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B52" s="46" t="b">
         <f>A52=Metadata!A52</f>
         <v>1</v>
       </c>
       <c r="C52" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G52" s="12">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J52" s="12"/>
     </row>
     <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B53" s="46" t="b">
         <f>A53=Metadata!A53</f>
         <v>1</v>
       </c>
       <c r="C53" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G53" s="12">
         <v>0</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J53" s="12"/>
     </row>
     <row r="54" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" s="46" t="b">
         <f>A54=Metadata!A54</f>
         <v>1</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G54" s="12">
         <v>12</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J54" s="12"/>
     </row>
     <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B55" s="46" t="b">
         <f>A55=Metadata!A55</f>
         <v>1</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G55" s="12">
         <v>12</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J55" s="12"/>
     </row>
     <row r="56" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B56" s="46" t="b">
         <f>A56=Metadata!A56</f>
         <v>1</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G56" s="12">
         <v>12</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J56" s="12"/>
     </row>
@@ -21870,23 +21858,23 @@
         <v>1</v>
       </c>
       <c r="C57" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D57" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G57" s="12">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J57" s="12"/>
     </row>
@@ -21899,23 +21887,23 @@
         <v>1</v>
       </c>
       <c r="C58" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D58" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G58" s="12">
         <v>0</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J58" s="12"/>
     </row>
@@ -21928,23 +21916,23 @@
         <v>1</v>
       </c>
       <c r="C59" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G59" s="12">
         <v>0</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J59" s="12"/>
     </row>
@@ -21957,23 +21945,23 @@
         <v>1</v>
       </c>
       <c r="C60" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G60" s="12">
         <v>0</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J60" s="12"/>
     </row>
@@ -21986,23 +21974,23 @@
         <v>1</v>
       </c>
       <c r="C61" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D61" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G61" s="12">
         <v>0</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J61" s="12"/>
     </row>
@@ -22015,23 +22003,23 @@
         <v>1</v>
       </c>
       <c r="C62" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G62" s="12">
         <v>0</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J62" s="12"/>
     </row>
@@ -22044,23 +22032,23 @@
         <v>1</v>
       </c>
       <c r="C63" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D63" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G63" s="12">
         <v>0</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J63" s="12"/>
     </row>
@@ -22073,23 +22061,23 @@
         <v>1</v>
       </c>
       <c r="C64" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G64" s="12">
         <v>0</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J64" s="12"/>
     </row>
@@ -22102,23 +22090,23 @@
         <v>1</v>
       </c>
       <c r="C65" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D65" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G65" s="12">
         <v>0</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J65" s="12"/>
     </row>
@@ -22131,23 +22119,23 @@
         <v>1</v>
       </c>
       <c r="C66" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G66" s="12">
         <v>0</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J66" s="12"/>
     </row>
@@ -22160,23 +22148,23 @@
         <v>1</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G67" s="12">
         <v>12</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J67" s="12"/>
     </row>
@@ -22189,23 +22177,23 @@
         <v>1</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G68" s="12">
         <v>12</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J68" s="12"/>
     </row>
@@ -22218,23 +22206,23 @@
         <v>1</v>
       </c>
       <c r="C69" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G69" s="12">
         <v>0</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J69" s="12"/>
     </row>
@@ -22247,21 +22235,21 @@
         <v>1</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="12"/>
       <c r="F70" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G70" s="12">
         <v>0</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J70" s="12"/>
     </row>
@@ -22274,10 +22262,10 @@
         <v>1</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
@@ -22295,19 +22283,19 @@
         <v>1</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
       <c r="G72" s="12"/>
       <c r="H72" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J72" s="12"/>
     </row>
@@ -22320,23 +22308,23 @@
         <v>1</v>
       </c>
       <c r="C73" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D73" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G73" s="12">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G73" s="12">
-        <v>0</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I73" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J73" s="12"/>
     </row>
@@ -22349,23 +22337,23 @@
         <v>1</v>
       </c>
       <c r="C74" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D74" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G74" s="12">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G74" s="12">
-        <v>0</v>
-      </c>
-      <c r="H74" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I74" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J74" s="12"/>
     </row>
@@ -22378,25 +22366,25 @@
         <v>1</v>
       </c>
       <c r="C75" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D75" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="E75" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="F75" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E75" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="F75" s="12" t="s">
+      <c r="G75" s="12">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G75" s="12">
-        <v>0</v>
-      </c>
-      <c r="H75" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I75" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J75" s="12"/>
     </row>
@@ -22409,23 +22397,23 @@
         <v>1</v>
       </c>
       <c r="C76" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D76" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G76" s="12">
+        <v>0</v>
+      </c>
+      <c r="H76" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G76" s="12">
-        <v>0</v>
-      </c>
-      <c r="H76" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I76" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J76" s="12"/>
     </row>
@@ -22438,21 +22426,21 @@
         <v>1</v>
       </c>
       <c r="C77" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G77" s="12"/>
       <c r="H77" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J77" s="12"/>
     </row>
@@ -22465,23 +22453,23 @@
         <v>1</v>
       </c>
       <c r="C78" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G78" s="12">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G78" s="12">
-        <v>0</v>
-      </c>
-      <c r="H78" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I78" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J78" s="12"/>
     </row>
@@ -22494,23 +22482,23 @@
         <v>1</v>
       </c>
       <c r="C79" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G79" s="12">
+        <v>0</v>
+      </c>
+      <c r="H79" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G79" s="12">
-        <v>0</v>
-      </c>
-      <c r="H79" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I79" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J79" s="12"/>
     </row>
@@ -22523,25 +22511,25 @@
         <v>1</v>
       </c>
       <c r="C80" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D80" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="E80" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="F80" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E80" s="29" t="s">
-        <v>286</v>
-      </c>
-      <c r="F80" s="12" t="s">
+      <c r="G80" s="12">
+        <v>0</v>
+      </c>
+      <c r="H80" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G80" s="12">
-        <v>0</v>
-      </c>
-      <c r="H80" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I80" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J80" s="12"/>
     </row>
@@ -22554,23 +22542,23 @@
         <v>1</v>
       </c>
       <c r="C81" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G81" s="12">
+        <v>0</v>
+      </c>
+      <c r="H81" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G81" s="12">
-        <v>0</v>
-      </c>
-      <c r="H81" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I81" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J81" s="12"/>
     </row>
@@ -22583,21 +22571,21 @@
         <v>1</v>
       </c>
       <c r="C82" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D82" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G82" s="12"/>
       <c r="H82" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J82" s="12"/>
     </row>
@@ -22610,23 +22598,23 @@
         <v>1</v>
       </c>
       <c r="C83" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D83" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G83" s="12">
+        <v>0</v>
+      </c>
+      <c r="H83" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G83" s="12">
-        <v>0</v>
-      </c>
-      <c r="H83" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I83" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J83" s="12"/>
     </row>
@@ -22639,23 +22627,23 @@
         <v>1</v>
       </c>
       <c r="C84" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D84" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G84" s="12">
+        <v>0</v>
+      </c>
+      <c r="H84" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G84" s="12">
-        <v>0</v>
-      </c>
-      <c r="H84" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I84" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J84" s="12"/>
     </row>
@@ -22668,25 +22656,25 @@
         <v>1</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D85" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E85" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="F85" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="E85" s="29" t="s">
-        <v>287</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="G85" s="12">
         <v>12</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J85" s="12"/>
     </row>
@@ -22699,23 +22687,23 @@
         <v>1</v>
       </c>
       <c r="C86" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D86" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G86" s="12">
+        <v>0</v>
+      </c>
+      <c r="H86" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G86" s="12">
-        <v>0</v>
-      </c>
-      <c r="H86" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I86" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J86" s="12"/>
     </row>
@@ -22728,21 +22716,21 @@
         <v>1</v>
       </c>
       <c r="C87" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D87" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G87" s="12"/>
       <c r="H87" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J87" s="12"/>
     </row>
@@ -22755,23 +22743,23 @@
         <v>1</v>
       </c>
       <c r="C88" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D88" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G88" s="12">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J88" s="12"/>
     </row>
@@ -22784,23 +22772,23 @@
         <v>1</v>
       </c>
       <c r="C89" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D89" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G89" s="12">
+        <v>0</v>
+      </c>
+      <c r="H89" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G89" s="12">
-        <v>0</v>
-      </c>
-      <c r="H89" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I89" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J89" s="12"/>
     </row>
@@ -22813,23 +22801,23 @@
         <v>1</v>
       </c>
       <c r="C90" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D90" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G90" s="12">
+        <v>0</v>
+      </c>
+      <c r="H90" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G90" s="12">
-        <v>0</v>
-      </c>
-      <c r="H90" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I90" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J90" s="12"/>
     </row>
@@ -22842,17 +22830,17 @@
         <v>1</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D91" s="12"/>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I91" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J91" s="12"/>
     </row>
@@ -22865,23 +22853,23 @@
         <v>1</v>
       </c>
       <c r="C92" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D92" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G92" s="12">
         <v>0</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J92" s="12"/>
     </row>
@@ -22894,10 +22882,10 @@
         <v>1</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -22915,23 +22903,23 @@
         <v>1</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G94" s="12">
         <v>0</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J94" s="12"/>
     </row>
@@ -22944,17 +22932,17 @@
         <v>1</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J95" s="12"/>
     </row>
@@ -22967,7 +22955,7 @@
         <v>1</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="12"/>
@@ -22986,10 +22974,10 @@
         <v>1</v>
       </c>
       <c r="C97" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
@@ -23007,10 +22995,10 @@
         <v>1</v>
       </c>
       <c r="C98" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D98" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
@@ -23028,10 +23016,10 @@
         <v>1</v>
       </c>
       <c r="C99" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D99" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -23049,19 +23037,19 @@
         <v>1</v>
       </c>
       <c r="C100" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D100" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J100" s="12"/>
     </row>
@@ -23074,23 +23062,23 @@
         <v>1</v>
       </c>
       <c r="C101" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D101" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G101" s="12">
         <v>0</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J101" s="12"/>
     </row>
@@ -23103,23 +23091,23 @@
         <v>1</v>
       </c>
       <c r="C102" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D102" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G102" s="12">
         <v>0</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J102" s="12"/>
     </row>
@@ -23132,10 +23120,10 @@
         <v>1</v>
       </c>
       <c r="C103" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D103" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
@@ -23153,23 +23141,23 @@
         <v>1</v>
       </c>
       <c r="C104" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D104" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G104" s="12">
         <v>0</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J104" s="12"/>
     </row>
@@ -23182,23 +23170,23 @@
         <v>1</v>
       </c>
       <c r="C105" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D105" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D105" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G105" s="12">
         <v>0</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J105" s="12">
         <v>1</v>
@@ -23213,23 +23201,23 @@
         <v>1</v>
       </c>
       <c r="C106" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D106" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G106" s="8">
         <v>0</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J106" s="12"/>
     </row>
@@ -23243,7 +23231,7 @@
       </c>
       <c r="C107" s="12"/>
       <c r="D107" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="8"/>
@@ -23261,19 +23249,19 @@
         <v>1</v>
       </c>
       <c r="C108" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D108" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
       <c r="H108" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J108" s="12"/>
     </row>
@@ -23286,10 +23274,10 @@
         <v>1</v>
       </c>
       <c r="C109" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D109" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="8"/>
@@ -23307,23 +23295,23 @@
         <v>1</v>
       </c>
       <c r="C110" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D110" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D110" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G110" s="8">
         <v>0</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J110" s="12"/>
     </row>
@@ -23336,19 +23324,19 @@
         <v>1</v>
       </c>
       <c r="C111" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D111" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
       <c r="H111" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J111" s="12"/>
     </row>
@@ -23361,17 +23349,17 @@
         <v>1</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D112" s="12"/>
       <c r="E112" s="12"/>
       <c r="F112" s="8"/>
       <c r="G112" s="8"/>
       <c r="H112" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J112" s="12"/>
     </row>
@@ -23384,19 +23372,19 @@
         <v>1</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
       <c r="H113" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J113" s="12"/>
     </row>
@@ -23409,14 +23397,14 @@
         <v>1</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G114" s="8"/>
       <c r="H114" s="12"/>
@@ -23432,7 +23420,7 @@
         <v>1</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D115" s="12"/>
       <c r="E115" s="12"/>
@@ -23451,7 +23439,7 @@
         <v>1</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D116" s="12"/>
       <c r="E116" s="12"/>
@@ -23470,10 +23458,10 @@
         <v>1</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="8"/>
@@ -23491,10 +23479,10 @@
         <v>1</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="8"/>
@@ -23512,10 +23500,10 @@
         <v>1</v>
       </c>
       <c r="C119" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D119" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="8"/>
@@ -23533,23 +23521,23 @@
         <v>1</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G120" s="8">
         <v>0</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I120" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J120" s="12"/>
     </row>
@@ -25756,10 +25744,10 @@
         <v>177</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -25767,7 +25755,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C2" s="28"/>
     </row>
@@ -25776,7 +25764,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C3" s="12"/>
     </row>
@@ -25785,7 +25773,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C4" s="12"/>
     </row>
@@ -25794,7 +25782,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -25803,7 +25791,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C6" s="12"/>
     </row>
@@ -25812,7 +25800,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C7" s="12"/>
     </row>
@@ -25821,7 +25809,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C8" s="12"/>
     </row>
@@ -25830,7 +25818,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C9" s="12"/>
     </row>
@@ -25839,7 +25827,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C10" s="12"/>
     </row>
@@ -25848,7 +25836,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C11" s="12"/>
     </row>
@@ -25857,7 +25845,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -25866,7 +25854,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -25875,7 +25863,7 @@
         <v>39</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -25891,16 +25879,16 @@
         <v>45</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17" s="31" t="s">
         <v>297</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>298</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -25916,7 +25904,7 @@
         <v>50</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C19" s="12"/>
     </row>
@@ -25932,7 +25920,7 @@
         <v>53</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C21" s="12"/>
     </row>
@@ -25941,7 +25929,7 @@
         <v>55</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C22" s="12"/>
     </row>
@@ -25957,7 +25945,7 @@
         <v>59</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C24" s="12"/>
     </row>
@@ -25966,7 +25954,7 @@
         <v>61</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C25" s="12"/>
     </row>
@@ -25975,7 +25963,7 @@
         <v>62</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C26" s="12"/>
     </row>
@@ -25984,7 +25972,7 @@
         <v>63</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C27" s="12"/>
     </row>
@@ -25993,7 +25981,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C28" s="12"/>
     </row>
@@ -26002,7 +25990,7 @@
         <v>65</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C29" s="12"/>
     </row>
@@ -26011,7 +25999,7 @@
         <v>67</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C30" s="12"/>
     </row>
@@ -26020,7 +26008,7 @@
         <v>69</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C31" s="12"/>
     </row>
@@ -26029,7 +26017,7 @@
         <v>70</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C32" s="12"/>
     </row>
@@ -26038,7 +26026,7 @@
         <v>72</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C33" s="12"/>
     </row>
@@ -26047,7 +26035,7 @@
         <v>73</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C34" s="12"/>
     </row>
@@ -26056,7 +26044,7 @@
         <v>75</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C35" s="12"/>
     </row>
@@ -26072,7 +26060,7 @@
         <v>77</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C37" s="12"/>
     </row>
@@ -26081,7 +26069,7 @@
         <v>78</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C38" s="12"/>
     </row>
@@ -26090,7 +26078,7 @@
         <v>79</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C39" s="12"/>
     </row>
@@ -26106,7 +26094,7 @@
         <v>81</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C41" s="12"/>
     </row>
@@ -26115,7 +26103,7 @@
         <v>82</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C42" s="12"/>
     </row>
@@ -26124,7 +26112,7 @@
         <v>83</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C43" s="12"/>
     </row>
@@ -26231,7 +26219,7 @@
         <v>99</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C58" s="12"/>
     </row>
@@ -26240,7 +26228,7 @@
         <v>100</v>
       </c>
       <c r="B59" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C59" s="12"/>
     </row>
@@ -26249,7 +26237,7 @@
         <v>101</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C60" s="12"/>
     </row>
@@ -26258,7 +26246,7 @@
         <v>102</v>
       </c>
       <c r="B61" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C61" s="12"/>
     </row>
@@ -26267,7 +26255,7 @@
         <v>104</v>
       </c>
       <c r="B62" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C62" s="12"/>
     </row>
@@ -26276,7 +26264,7 @@
         <v>105</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C63" s="12"/>
     </row>
@@ -26285,7 +26273,7 @@
         <v>106</v>
       </c>
       <c r="B64" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C64" s="12"/>
     </row>
@@ -26294,7 +26282,7 @@
         <v>109</v>
       </c>
       <c r="B65" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C65" s="12"/>
     </row>
@@ -26303,7 +26291,7 @@
         <v>111</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C66" s="12"/>
     </row>
@@ -26312,7 +26300,7 @@
         <v>112</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C67" s="12"/>
     </row>
@@ -26321,7 +26309,7 @@
         <v>113</v>
       </c>
       <c r="B68" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="12"/>
     </row>
@@ -26330,7 +26318,7 @@
         <v>114</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="12"/>
     </row>
@@ -26339,7 +26327,7 @@
         <v>115</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="12"/>
     </row>
@@ -26348,7 +26336,7 @@
         <v>116</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C71" s="12"/>
     </row>
@@ -26357,7 +26345,7 @@
         <v>117</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C72" s="12"/>
     </row>
@@ -26366,7 +26354,7 @@
         <v>118</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C73" s="12"/>
     </row>
@@ -26375,7 +26363,7 @@
         <v>119</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C74" s="12"/>
     </row>
@@ -26384,7 +26372,7 @@
         <v>120</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C75" s="12"/>
     </row>
@@ -26393,7 +26381,7 @@
         <v>121</v>
       </c>
       <c r="B76" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C76" s="12"/>
     </row>
@@ -26402,7 +26390,7 @@
         <v>123</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C77" s="12"/>
     </row>
@@ -26411,7 +26399,7 @@
         <v>126</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C78" s="12"/>
     </row>
@@ -26420,7 +26408,7 @@
         <v>127</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C79" s="12"/>
     </row>
@@ -26429,7 +26417,7 @@
         <v>128</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C80" s="12"/>
     </row>
@@ -26438,7 +26426,7 @@
         <v>131</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C81" s="12"/>
     </row>
@@ -26447,7 +26435,7 @@
         <v>132</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C82" s="12"/>
     </row>
@@ -26456,7 +26444,7 @@
         <v>133</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C83" s="12"/>
     </row>
@@ -26465,7 +26453,7 @@
         <v>135</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C84" s="12"/>
     </row>
@@ -26474,7 +26462,7 @@
         <v>136</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C85" s="12"/>
     </row>
@@ -26483,7 +26471,7 @@
         <v>138</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C86" s="12"/>
     </row>
@@ -26492,7 +26480,7 @@
         <v>139</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C87" s="12"/>
     </row>
@@ -26501,7 +26489,7 @@
         <v>140</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C88" s="12"/>
     </row>
@@ -26510,7 +26498,7 @@
         <v>142</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C89" s="12"/>
     </row>
@@ -26519,7 +26507,7 @@
         <v>144</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C90" s="12"/>
     </row>
@@ -26528,7 +26516,7 @@
         <v>146</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C91" s="12"/>
     </row>
@@ -26537,7 +26525,7 @@
         <v>148</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C92" s="12"/>
     </row>
@@ -26546,7 +26534,7 @@
         <v>150</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C93" s="12"/>
     </row>
@@ -26555,7 +26543,7 @@
         <v>152</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C94" s="12"/>
     </row>
@@ -26564,7 +26552,7 @@
         <v>154</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C95" s="12"/>
     </row>
@@ -26573,7 +26561,7 @@
         <v>156</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C96" s="12"/>
     </row>
@@ -26582,7 +26570,7 @@
         <v>158</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C97" s="12"/>
     </row>
@@ -26591,7 +26579,7 @@
         <v>160</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C98" s="12"/>
     </row>
@@ -26600,7 +26588,7 @@
         <v>162</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C99" s="12"/>
     </row>
@@ -26609,7 +26597,7 @@
         <v>110</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C100" s="12"/>
     </row>
@@ -26618,7 +26606,7 @@
         <v>165</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C101" s="12"/>
     </row>
@@ -26627,7 +26615,7 @@
         <v>167</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C102" s="12"/>
     </row>
@@ -26636,7 +26624,7 @@
         <v>168</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C103" s="12"/>
     </row>
@@ -26645,7 +26633,7 @@
         <v>169</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C104" s="12"/>
     </row>
@@ -26654,7 +26642,7 @@
         <v>170</v>
       </c>
       <c r="B105" s="32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C105" s="12"/>
     </row>
@@ -26663,7 +26651,7 @@
         <v>171</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C106" s="12"/>
     </row>
@@ -26672,7 +26660,7 @@
         <v>172</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C107" s="12"/>
     </row>
@@ -26681,7 +26669,7 @@
         <v>174</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C108" s="12"/>
     </row>
@@ -26798,13 +26786,13 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>45960.470200462965</v>
+        <v>45960.496010879629</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanos\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B4A204-7D62-4EF7-8D48-DAA9BEC30406}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F5A49F-5FA5-4722-BB97-A5BAF8B6B87E}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1858,9 +1858,6 @@
     <t>['IMBABE']</t>
   </si>
   <si>
-    <t>range(1,51,1)</t>
-  </si>
-  <si>
     <t>['ISPRequirements']</t>
   </si>
   <si>
@@ -2225,6 +2222,9 @@
   </si>
   <si>
     <t>MS</t>
+  </si>
+  <si>
+    <t>range(1,101,1)</t>
   </si>
 </sst>
 </file>
@@ -5038,7 +5038,7 @@
         <v>42005</v>
       </c>
       <c r="G31" s="48" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H31" s="8" t="b">
         <f>TRUE()</f>
@@ -5105,10 +5105,10 @@
         <v>176</v>
       </c>
       <c r="F33" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G33" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H33" s="8" t="b">
         <f>TRUE()</f>
@@ -5140,10 +5140,10 @@
         <v>176</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G34" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H34" s="8" t="b">
         <f>TRUE()</f>
@@ -5175,10 +5175,10 @@
         <v>176</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G35" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H35" s="8" t="b">
         <f>TRUE()</f>
@@ -5210,10 +5210,10 @@
         <v>176</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G36" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H36" s="8" t="b">
         <f>TRUE()</f>
@@ -5247,10 +5247,10 @@
         <v>176</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G37" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H37" s="8" t="b">
         <f>TRUE()</f>
@@ -5282,10 +5282,10 @@
         <v>176</v>
       </c>
       <c r="F38" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G38" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H38" s="8" t="b">
         <f>TRUE()</f>
@@ -5317,10 +5317,10 @@
         <v>176</v>
       </c>
       <c r="F39" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G39" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H39" s="8" t="b">
         <f>TRUE()</f>
@@ -5352,10 +5352,10 @@
         <v>176</v>
       </c>
       <c r="F40" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G40" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H40" s="8" t="b">
         <f>TRUE()</f>
@@ -5389,10 +5389,10 @@
         <v>176</v>
       </c>
       <c r="F41" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G41" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H41" s="8" t="b">
         <f>TRUE()</f>
@@ -5424,10 +5424,10 @@
         <v>176</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G42" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H42" s="8" t="b">
         <f>TRUE()</f>
@@ -5459,10 +5459,10 @@
         <v>176</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G43" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H43" s="8" t="b">
         <f>TRUE()</f>
@@ -5494,10 +5494,10 @@
         <v>176</v>
       </c>
       <c r="F44" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G44" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H44" s="8" t="b">
         <f>TRUE()</f>
@@ -5518,7 +5518,7 @@
     </row>
     <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8" t="s">
@@ -5531,7 +5531,7 @@
         <v>176</v>
       </c>
       <c r="F45" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G45" s="47"/>
       <c r="H45" s="8" t="b">
@@ -5551,7 +5551,7 @@
     </row>
     <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="8" t="s">
@@ -5564,7 +5564,7 @@
         <v>176</v>
       </c>
       <c r="F46" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G46" s="47">
         <v>45930</v>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="8" t="s">
@@ -5599,7 +5599,7 @@
         <v>176</v>
       </c>
       <c r="F47" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G47" s="47"/>
       <c r="H47" s="8" t="b">
@@ -5619,7 +5619,7 @@
     </row>
     <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="8" t="s">
@@ -5632,7 +5632,7 @@
         <v>176</v>
       </c>
       <c r="F48" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G48" s="47">
         <v>45930</v>
@@ -5654,7 +5654,7 @@
     </row>
     <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="8" t="s">
@@ -5667,7 +5667,7 @@
         <v>176</v>
       </c>
       <c r="F49" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G49" s="47"/>
       <c r="H49" s="8" t="b">
@@ -5687,7 +5687,7 @@
     </row>
     <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="8" t="s">
@@ -5700,7 +5700,7 @@
         <v>176</v>
       </c>
       <c r="F50" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G50" s="47">
         <v>45930</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="8" t="s">
@@ -5735,7 +5735,7 @@
         <v>176</v>
       </c>
       <c r="F51" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G51" s="47"/>
       <c r="H51" s="8" t="b">
@@ -5755,7 +5755,7 @@
     </row>
     <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
@@ -5768,7 +5768,7 @@
         <v>176</v>
       </c>
       <c r="F52" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G52" s="47">
         <v>45930</v>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="53" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="8" t="s">
@@ -5803,7 +5803,7 @@
         <v>176</v>
       </c>
       <c r="F53" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G53" s="47"/>
       <c r="H53" s="8" t="b">
@@ -5823,7 +5823,7 @@
     </row>
     <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="8" t="s">
@@ -5836,7 +5836,7 @@
         <v>176</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G54" s="47">
         <v>45930</v>
@@ -5858,7 +5858,7 @@
     </row>
     <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="8" t="s">
@@ -5871,7 +5871,7 @@
         <v>176</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G55" s="47"/>
       <c r="H55" s="8" t="b">
@@ -5891,7 +5891,7 @@
     </row>
     <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="8" t="s">
@@ -5904,7 +5904,7 @@
         <v>176</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G56" s="47">
         <v>45930</v>
@@ -5942,7 +5942,7 @@
         <v>43841</v>
       </c>
       <c r="G57" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H57" s="8" t="b">
         <f>TRUE()</f>
@@ -5977,7 +5977,7 @@
         <v>43841</v>
       </c>
       <c r="G58" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H58" s="8" t="b">
         <f>TRUE()</f>
@@ -6014,7 +6014,7 @@
         <v>43841</v>
       </c>
       <c r="G59" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H59" s="8" t="b">
         <f>TRUE()</f>
@@ -6049,7 +6049,7 @@
         <v>43841</v>
       </c>
       <c r="G60" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H60" s="8" t="b">
         <f>TRUE()</f>
@@ -6086,7 +6086,7 @@
         <v>43841</v>
       </c>
       <c r="G61" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H61" s="8" t="b">
         <f>TRUE()</f>
@@ -6121,7 +6121,7 @@
         <v>43841</v>
       </c>
       <c r="G62" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H62" s="8" t="b">
         <f>TRUE()</f>
@@ -6158,7 +6158,7 @@
         <v>43841</v>
       </c>
       <c r="G63" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H63" s="8" t="b">
         <f>TRUE()</f>
@@ -6193,7 +6193,7 @@
         <v>43841</v>
       </c>
       <c r="G64" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H64" s="8" t="b">
         <f>TRUE()</f>
@@ -6230,7 +6230,7 @@
         <v>43841</v>
       </c>
       <c r="G65" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H65" s="8" t="b">
         <f>TRUE()</f>
@@ -6265,7 +6265,7 @@
         <v>43841</v>
       </c>
       <c r="G66" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H66" s="8" t="b">
         <f>TRUE()</f>
@@ -6302,7 +6302,7 @@
         <v>43841</v>
       </c>
       <c r="G67" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H67" s="8" t="b">
         <f>TRUE()</f>
@@ -6337,7 +6337,7 @@
         <v>43841</v>
       </c>
       <c r="G68" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H68" s="8" t="b">
         <f>TRUE()</f>
@@ -6503,16 +6503,14 @@
       <c r="F73" s="40">
         <v>44124</v>
       </c>
-      <c r="G73" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G73" s="47"/>
       <c r="H73" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I73" s="7" t="b">
         <f>IF(Metadata!G73="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="13" t="b">
         <f>TRUE()</f>
@@ -6538,16 +6536,14 @@
       <c r="F74" s="40">
         <v>44124</v>
       </c>
-      <c r="G74" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G74" s="47"/>
       <c r="H74" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I74" s="7" t="b">
         <f>IF(Metadata!G74="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="13" t="b">
         <f>TRUE()</f>
@@ -6674,16 +6670,14 @@
       <c r="F78" s="40">
         <v>44124</v>
       </c>
-      <c r="G78" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G78" s="47"/>
       <c r="H78" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I78" s="7" t="b">
         <f>IF(Metadata!G78="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" s="13" t="b">
         <f>TRUE()</f>
@@ -6709,16 +6703,14 @@
       <c r="F79" s="40">
         <v>44124</v>
       </c>
-      <c r="G79" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G79" s="47"/>
       <c r="H79" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I79" s="7" t="b">
         <f>IF(Metadata!G79="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="13" t="b">
         <f>TRUE()</f>
@@ -6843,16 +6835,14 @@
       <c r="F83" s="40">
         <v>44124</v>
       </c>
-      <c r="G83" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G83" s="47"/>
       <c r="H83" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I83" s="7" t="b">
         <f>IF(Metadata!G83="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" s="13" t="b">
         <f>TRUE()</f>
@@ -6878,16 +6868,14 @@
       <c r="F84" s="40">
         <v>44124</v>
       </c>
-      <c r="G84" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G84" s="47"/>
       <c r="H84" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I84" s="7" t="b">
         <f>IF(Metadata!G84="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="13" t="b">
         <f>TRUE()</f>
@@ -11020,7 +11008,7 @@
         <v>182</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>183</v>
@@ -11201,7 +11189,7 @@
         <v>187</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H10" s="12">
         <v>0</v>
@@ -11225,7 +11213,7 @@
         <v>206</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H11" s="12">
         <v>0</v>
@@ -12002,7 +11990,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B45" s="41" t="b">
         <f>Metadata!A45=A45</f>
@@ -12026,7 +12014,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B46" s="41" t="b">
         <f>Metadata!A46=A46</f>
@@ -12050,7 +12038,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" s="41" t="b">
         <f>Metadata!A47=A47</f>
@@ -12076,7 +12064,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B48" s="41" t="b">
         <f>Metadata!A48=A48</f>
@@ -12102,7 +12090,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" s="41" t="b">
         <f>Metadata!A49=A49</f>
@@ -12126,7 +12114,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B50" s="41" t="b">
         <f>Metadata!A50=A50</f>
@@ -12150,7 +12138,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B51" s="41" t="b">
         <f>Metadata!A51=A51</f>
@@ -12176,7 +12164,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B52" s="41" t="b">
         <f>Metadata!A52=A52</f>
@@ -12202,7 +12190,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B53" s="41" t="b">
         <f>Metadata!A53=A53</f>
@@ -12226,7 +12214,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" s="41" t="b">
         <f>Metadata!A54=A54</f>
@@ -12250,7 +12238,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B55" s="41" t="b">
         <f>Metadata!A55=A55</f>
@@ -12276,7 +12264,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B56" s="41" t="b">
         <f>Metadata!A56=A56</f>
@@ -12704,10 +12692,10 @@
         <v>204</v>
       </c>
       <c r="H73" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -12730,10 +12718,10 @@
         <v>205</v>
       </c>
       <c r="H74" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -12777,7 +12765,7 @@
         <v>187</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H76" s="12">
         <v>0</v>
@@ -12830,10 +12818,10 @@
         <v>204</v>
       </c>
       <c r="H78" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
@@ -12856,10 +12844,10 @@
         <v>205</v>
       </c>
       <c r="H79" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
@@ -12903,7 +12891,7 @@
         <v>187</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H81" s="12">
         <v>0</v>
@@ -12956,10 +12944,10 @@
         <v>204</v>
       </c>
       <c r="H83" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
@@ -12982,10 +12970,10 @@
         <v>205</v>
       </c>
       <c r="H84" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
@@ -13029,7 +13017,7 @@
         <v>187</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H86" s="12">
         <v>0</v>
@@ -13097,7 +13085,7 @@
         <v>187</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H89" s="12">
         <v>0</v>
@@ -13121,7 +13109,7 @@
         <v>187</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H90" s="12">
         <v>0</v>
@@ -13156,20 +13144,20 @@
         <v>203</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E92" s="18"/>
       <c r="F92" s="12" t="s">
         <v>187</v>
       </c>
       <c r="G92" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H92" s="12">
+        <v>1</v>
+      </c>
+      <c r="I92" s="12" t="s">
         <v>223</v>
-      </c>
-      <c r="H92" s="12">
-        <v>1</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
@@ -13200,14 +13188,14 @@
         <v>184</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E94" s="18"/>
       <c r="F94" s="12" t="s">
         <v>194</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H94" s="12">
         <v>2</v>
@@ -13333,7 +13321,7 @@
         <v>187</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H101" s="12">
         <v>1</v>
@@ -13357,7 +13345,7 @@
         <v>187</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H102" s="12">
         <v>1</v>
@@ -13397,7 +13385,7 @@
         <v>187</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H104" s="12">
         <v>2</v>
@@ -13416,14 +13404,14 @@
         <v>203</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E105" s="18"/>
       <c r="F105" s="12" t="s">
         <v>187</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H105" s="12">
         <v>0</v>
@@ -13442,20 +13430,20 @@
         <v>203</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E106" s="18"/>
       <c r="F106" s="12" t="s">
         <v>187</v>
       </c>
       <c r="G106" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="H106" s="12">
+        <v>0</v>
+      </c>
+      <c r="I106" s="12" t="s">
         <v>231</v>
-      </c>
-      <c r="H106" s="12">
-        <v>0</v>
-      </c>
-      <c r="I106" s="12" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
@@ -13485,7 +13473,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D108" s="18"/>
       <c r="E108" s="18"/>
@@ -13526,16 +13514,16 @@
       <c r="D110" s="8"/>
       <c r="E110" s="18"/>
       <c r="F110" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="G110" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="G110" s="8" t="s">
-        <v>235</v>
       </c>
       <c r="H110" s="12">
         <v>4</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
@@ -13579,7 +13567,7 @@
         <v>1</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="18"/>
@@ -13698,10 +13686,10 @@
       <c r="D120" s="8"/>
       <c r="E120" s="18"/>
       <c r="F120" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="G120" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>238</v>
       </c>
       <c r="H120" s="12">
         <v>2</v>
@@ -15790,25 +15778,25 @@
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -15820,17 +15808,17 @@
         <v>1</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>248</v>
       </c>
       <c r="H2" s="25"/>
       <c r="I2" s="26"/>
@@ -15880,7 +15868,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="20"/>
@@ -15898,7 +15886,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="20"/>
@@ -15964,7 +15952,7 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H10" s="27" t="b">
         <v>0</v>
@@ -15982,13 +15970,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="20"/>
@@ -16022,7 +16010,7 @@
       <c r="E13" s="14"/>
       <c r="F13" s="8"/>
       <c r="G13" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H13" s="27" t="b">
         <f>TRUE()</f>
@@ -16046,7 +16034,7 @@
       <c r="E14" s="14"/>
       <c r="F14" s="8"/>
       <c r="G14" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H14" s="27" t="b">
         <f>TRUE()</f>
@@ -16070,7 +16058,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H15" s="27" t="b">
         <f>TRUE()</f>
@@ -16094,7 +16082,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="8"/>
       <c r="G16" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H16" s="27" t="b">
         <f>TRUE()</f>
@@ -16118,7 +16106,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="8"/>
       <c r="G17" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H17" s="27" t="b">
         <f>TRUE()</f>
@@ -16138,13 +16126,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="14"/>
       <c r="F18" s="8"/>
       <c r="G18" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H18" s="27" t="b">
         <f>FALSE()</f>
@@ -16165,7 +16153,7 @@
       <c r="E19" s="14"/>
       <c r="F19" s="8"/>
       <c r="G19" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H19" s="27" t="b">
         <f>TRUE()</f>
@@ -16185,13 +16173,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="14"/>
       <c r="F20" s="8"/>
       <c r="G20" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H20" s="27"/>
       <c r="I20" s="20"/>
@@ -16205,15 +16193,15 @@
         <v>1</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H21" s="27" t="b">
         <f>FALSE()</f>
@@ -16232,11 +16220,11 @@
       <c r="C22" s="23"/>
       <c r="D22" s="24"/>
       <c r="E22" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H22" s="27"/>
       <c r="I22" s="20"/>
@@ -16250,13 +16238,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H23" s="27"/>
       <c r="I23" s="20"/>
@@ -16302,15 +16290,15 @@
         <v>1</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H26" s="27"/>
       <c r="I26" s="20"/>
@@ -16356,13 +16344,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H29" s="27"/>
       <c r="I29" s="20"/>
@@ -16412,7 +16400,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H32" s="27" t="b">
         <f>FALSE()</f>
@@ -16436,7 +16424,7 @@
       <c r="E33" s="14"/>
       <c r="F33" s="8"/>
       <c r="G33" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H33" s="27" t="b">
         <f>TRUE()</f>
@@ -16460,7 +16448,7 @@
       <c r="E34" s="14"/>
       <c r="F34" s="8"/>
       <c r="G34" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H34" s="27" t="b">
         <f>TRUE()</f>
@@ -16484,7 +16472,7 @@
       <c r="E35" s="14"/>
       <c r="F35" s="8"/>
       <c r="G35" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H35" s="27" t="b">
         <f>TRUE()</f>
@@ -16504,13 +16492,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="14"/>
       <c r="F36" s="8"/>
       <c r="G36" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H36" s="27"/>
       <c r="I36" s="20"/>
@@ -16528,7 +16516,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="8"/>
       <c r="G37" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H37" s="27" t="b">
         <f>TRUE()</f>
@@ -16552,7 +16540,7 @@
       <c r="E38" s="14"/>
       <c r="F38" s="8"/>
       <c r="G38" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H38" s="27" t="b">
         <f>TRUE()</f>
@@ -16576,7 +16564,7 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8"/>
       <c r="G39" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H39" s="27" t="b">
         <f>TRUE()</f>
@@ -16596,13 +16584,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="14"/>
       <c r="F40" s="8"/>
       <c r="G40" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H40" s="27"/>
       <c r="I40" s="20"/>
@@ -16620,7 +16608,7 @@
       <c r="E41" s="14"/>
       <c r="F41" s="8"/>
       <c r="G41" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H41" s="27" t="b">
         <f>TRUE()</f>
@@ -16644,7 +16632,7 @@
       <c r="E42" s="14"/>
       <c r="F42" s="8"/>
       <c r="G42" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H42" s="27" t="b">
         <f>TRUE()</f>
@@ -16668,7 +16656,7 @@
       <c r="E43" s="14"/>
       <c r="F43" s="8"/>
       <c r="G43" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H43" s="27" t="b">
         <f>TRUE()</f>
@@ -16688,20 +16676,20 @@
         <v>1</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="14"/>
       <c r="F44" s="8"/>
       <c r="G44" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H44" s="27"/>
       <c r="I44" s="20"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B45" s="41" t="b">
         <f>A45=Metadata!A45</f>
@@ -16712,7 +16700,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H45" s="27" t="b">
         <f>TRUE()</f>
@@ -16725,7 +16713,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B46" s="41" t="b">
         <f>A46=Metadata!A46</f>
@@ -16736,7 +16724,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H46" s="27" t="b">
         <f>TRUE()</f>
@@ -16749,7 +16737,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" s="41" t="b">
         <f>A47=Metadata!A47</f>
@@ -16760,7 +16748,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H47" s="27" t="b">
         <f>TRUE()</f>
@@ -16773,27 +16761,27 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B48" s="41" t="b">
         <f>A48=Metadata!A48</f>
         <v>1</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H48" s="27"/>
       <c r="I48" s="20"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" s="41" t="b">
         <f>A49=Metadata!A49</f>
@@ -16804,7 +16792,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H49" s="27" t="b">
         <f>TRUE()</f>
@@ -16817,7 +16805,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B50" s="41" t="b">
         <f>A50=Metadata!A50</f>
@@ -16828,7 +16816,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
       <c r="G50" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H50" s="27" t="b">
         <f>TRUE()</f>
@@ -16841,7 +16829,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B51" s="41" t="b">
         <f>A51=Metadata!A51</f>
@@ -16852,7 +16840,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H51" s="27" t="b">
         <f>TRUE()</f>
@@ -16865,27 +16853,27 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B52" s="41" t="b">
         <f>A52=Metadata!A52</f>
         <v>1</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H52" s="45"/>
       <c r="I52" s="20"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B53" s="41" t="b">
         <f>A53=Metadata!A53</f>
@@ -16896,7 +16884,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H53" s="27" t="b">
         <f>TRUE()</f>
@@ -16909,7 +16897,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" s="41" t="b">
         <f>A54=Metadata!A54</f>
@@ -16920,7 +16908,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H54" s="27" t="b">
         <f>TRUE()</f>
@@ -16933,7 +16921,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B55" s="41" t="b">
         <f>A55=Metadata!A55</f>
@@ -16944,7 +16932,7 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H55" s="27" t="b">
         <f>TRUE()</f>
@@ -16957,20 +16945,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B56" s="41" t="b">
         <f>A56=Metadata!A56</f>
         <v>1</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H56" s="45"/>
       <c r="I56" s="20"/>
@@ -16988,7 +16976,7 @@
       <c r="E57" s="14"/>
       <c r="F57" s="8"/>
       <c r="G57" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H57" s="27" t="b">
         <f>TRUE()</f>
@@ -17012,7 +17000,7 @@
       <c r="E58" s="14"/>
       <c r="F58" s="8"/>
       <c r="G58" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H58" s="27" t="b">
         <f>TRUE()</f>
@@ -17036,7 +17024,7 @@
       <c r="E59" s="14"/>
       <c r="F59" s="8"/>
       <c r="G59" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H59" s="27" t="b">
         <f>TRUE()</f>
@@ -17056,13 +17044,13 @@
         <v>1</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="14"/>
       <c r="F60" s="8"/>
       <c r="G60" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H60" s="27"/>
       <c r="I60" s="20"/>
@@ -17080,7 +17068,7 @@
       <c r="E61" s="14"/>
       <c r="F61" s="8"/>
       <c r="G61" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H61" s="27" t="b">
         <f>TRUE()</f>
@@ -17104,7 +17092,7 @@
       <c r="E62" s="14"/>
       <c r="F62" s="8"/>
       <c r="G62" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H62" s="27" t="b">
         <f>TRUE()</f>
@@ -17128,7 +17116,7 @@
       <c r="E63" s="14"/>
       <c r="F63" s="8"/>
       <c r="G63" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H63" s="27" t="b">
         <f>TRUE()</f>
@@ -17148,13 +17136,13 @@
         <v>1</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="14"/>
       <c r="F64" s="8"/>
       <c r="G64" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H64" s="27"/>
       <c r="I64" s="20"/>
@@ -17172,7 +17160,7 @@
       <c r="E65" s="44"/>
       <c r="F65" s="8"/>
       <c r="G65" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H65" s="27" t="b">
         <f>TRUE()</f>
@@ -17196,7 +17184,7 @@
       <c r="E66" s="14"/>
       <c r="F66" s="8"/>
       <c r="G66" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H66" s="27" t="b">
         <f>TRUE()</f>
@@ -17220,7 +17208,7 @@
       <c r="E67" s="14"/>
       <c r="F67" s="8"/>
       <c r="G67" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H67" s="27" t="b">
         <f>TRUE()</f>
@@ -17240,13 +17228,13 @@
         <v>1</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D68" s="24"/>
       <c r="E68" s="14"/>
       <c r="F68" s="8"/>
       <c r="G68" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H68" s="27"/>
       <c r="I68" s="20"/>
@@ -17264,7 +17252,7 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H69" s="27" t="b">
         <f>TRUE()</f>
@@ -17288,7 +17276,7 @@
       <c r="E70" s="23"/>
       <c r="F70" s="8"/>
       <c r="G70" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H70" s="27"/>
       <c r="I70" s="20"/>
@@ -17338,7 +17326,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H73" s="27"/>
       <c r="I73" s="20"/>
@@ -17356,7 +17344,7 @@
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
       <c r="G74" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H74" s="27"/>
       <c r="I74" s="20"/>
@@ -17370,17 +17358,17 @@
         <v>1</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D75" s="24"/>
       <c r="E75" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G75" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="G75" s="12" t="s">
-        <v>248</v>
       </c>
       <c r="H75" s="27"/>
       <c r="I75" s="20"/>
@@ -17394,13 +17382,13 @@
         <v>1</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D76" s="24"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H76" s="27"/>
       <c r="I76" s="20"/>
@@ -17414,15 +17402,15 @@
         <v>1</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D77" s="24"/>
       <c r="E77" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F77" s="8"/>
       <c r="G77" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H77" s="27"/>
       <c r="I77" s="20"/>
@@ -17440,7 +17428,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H78" s="27"/>
       <c r="I78" s="20"/>
@@ -17458,7 +17446,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H79" s="27"/>
       <c r="I79" s="20"/>
@@ -17472,17 +17460,17 @@
         <v>1</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D80" s="24"/>
       <c r="E80" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G80" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="G80" s="12" t="s">
-        <v>248</v>
       </c>
       <c r="H80" s="27"/>
       <c r="I80" s="20"/>
@@ -17496,13 +17484,13 @@
         <v>1</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D81" s="24"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
       <c r="G81" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H81" s="27"/>
       <c r="I81" s="20"/>
@@ -17516,15 +17504,15 @@
         <v>1</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H82" s="27"/>
       <c r="I82" s="20"/>
@@ -17542,7 +17530,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H83" s="27"/>
       <c r="I83" s="20"/>
@@ -17560,7 +17548,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H84" s="27"/>
       <c r="I84" s="20"/>
@@ -17574,17 +17562,17 @@
         <v>1</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D85" s="24"/>
       <c r="E85" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="G85" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="G85" s="12" t="s">
-        <v>248</v>
       </c>
       <c r="H85" s="27"/>
       <c r="I85" s="20"/>
@@ -17598,13 +17586,13 @@
         <v>1</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D86" s="24"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
       <c r="G86" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H86" s="27"/>
       <c r="I86" s="20"/>
@@ -17618,15 +17606,15 @@
         <v>1</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D87" s="24"/>
       <c r="E87" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H87" s="27"/>
       <c r="I87" s="20"/>
@@ -17660,7 +17648,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
       <c r="G89" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H89" s="27" t="b">
         <f>TRUE()</f>
@@ -17684,7 +17672,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
       <c r="G90" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H90" s="27" t="b">
         <f>TRUE()</f>
@@ -17720,15 +17708,15 @@
         <v>1</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D92" s="24"/>
       <c r="E92" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H92" s="27"/>
       <c r="I92" s="20"/>
@@ -17762,7 +17750,7 @@
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
       <c r="G94" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H94" s="27" t="b">
         <v>0</v>
@@ -17880,7 +17868,7 @@
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
       <c r="G101" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H101" s="27"/>
       <c r="I101" s="20"/>
@@ -17898,7 +17886,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
       <c r="G102" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H102" s="27"/>
       <c r="I102" s="20"/>
@@ -17928,17 +17916,17 @@
         <v>1</v>
       </c>
       <c r="C104" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="D104" s="24" t="s">
         <v>260</v>
-      </c>
-      <c r="D104" s="24" t="s">
-        <v>261</v>
       </c>
       <c r="E104" s="8"/>
       <c r="F104" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H104" s="27"/>
       <c r="I104" s="20"/>
@@ -17956,7 +17944,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
       <c r="G105" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H105" s="27"/>
       <c r="I105" s="20"/>
@@ -17974,7 +17962,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
       <c r="G106" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H106" s="27" t="b">
         <f>FALSE()</f>
@@ -18042,15 +18030,15 @@
         <v>1</v>
       </c>
       <c r="C110" s="23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F110" s="8"/>
       <c r="G110" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H110" s="27"/>
       <c r="I110" s="20"/>
@@ -18084,7 +18072,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
       <c r="G112" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H112" s="27"/>
       <c r="I112" s="20"/>
@@ -18182,7 +18170,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
       <c r="G118" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H118" s="27" t="b">
         <f>TRUE()</f>
@@ -18222,7 +18210,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
       <c r="G120" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H120" s="27"/>
       <c r="I120" s="20"/>
@@ -20320,28 +20308,28 @@
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -20353,23 +20341,23 @@
         <v>1</v>
       </c>
       <c r="C2" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2" s="28" t="s">
         <v>270</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>271</v>
       </c>
       <c r="E2" s="28"/>
       <c r="F2" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="G2" s="28">
+        <v>0</v>
+      </c>
+      <c r="H2" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="G2" s="28">
-        <v>0</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>273</v>
-      </c>
       <c r="I2" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J2" s="28"/>
     </row>
@@ -20382,7 +20370,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
@@ -20401,7 +20389,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
@@ -20420,23 +20408,23 @@
         <v>1</v>
       </c>
       <c r="C5" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G5" s="12">
         <v>0</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J5" s="12"/>
     </row>
@@ -20449,23 +20437,23 @@
         <v>1</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G6" s="12">
         <v>0</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J6" s="12"/>
     </row>
@@ -20478,10 +20466,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -20499,10 +20487,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -20520,10 +20508,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -20541,23 +20529,23 @@
         <v>1</v>
       </c>
       <c r="C10" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J10" s="12"/>
     </row>
@@ -20570,21 +20558,21 @@
         <v>1</v>
       </c>
       <c r="C11" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J11" s="12"/>
     </row>
@@ -20597,19 +20585,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J12" s="12"/>
     </row>
@@ -20622,23 +20610,23 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G13" s="12">
         <v>0</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J13" s="12"/>
     </row>
@@ -20651,23 +20639,23 @@
         <v>1</v>
       </c>
       <c r="C14" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G14" s="12">
         <v>0</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J14" s="12"/>
     </row>
@@ -20680,21 +20668,21 @@
         <v>1</v>
       </c>
       <c r="C15" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J15" s="12"/>
     </row>
@@ -20707,25 +20695,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="E16" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="G16" s="12">
         <v>0</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J16" s="12"/>
     </row>
@@ -20738,23 +20726,23 @@
         <v>1</v>
       </c>
       <c r="C17" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J17" s="12"/>
     </row>
@@ -20767,25 +20755,25 @@
         <v>1</v>
       </c>
       <c r="C18" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="E18" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="G18" s="12">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J18" s="12"/>
     </row>
@@ -20798,25 +20786,25 @@
         <v>1</v>
       </c>
       <c r="C19" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="E19" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F19" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="G19" s="12">
         <v>0</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J19" s="12"/>
     </row>
@@ -20829,25 +20817,25 @@
         <v>1</v>
       </c>
       <c r="C20" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="E20" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F20" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="G20" s="12">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J20" s="12"/>
     </row>
@@ -20860,23 +20848,23 @@
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G21" s="12">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J21" s="12"/>
     </row>
@@ -20889,23 +20877,23 @@
         <v>1</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G22" s="12">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J22" s="12"/>
     </row>
@@ -20918,23 +20906,23 @@
         <v>1</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G23" s="12">
         <v>0</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J23" s="12"/>
     </row>
@@ -20947,10 +20935,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -20968,10 +20956,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -20989,23 +20977,23 @@
         <v>1</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G26" s="12"/>
       <c r="H26" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J26" s="12"/>
     </row>
@@ -21018,19 +21006,19 @@
         <v>1</v>
       </c>
       <c r="C27" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J27" s="12"/>
     </row>
@@ -21043,19 +21031,19 @@
         <v>1</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
       <c r="H28" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J28" s="12"/>
     </row>
@@ -21068,21 +21056,21 @@
         <v>1</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G29" s="12">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J29" s="12"/>
     </row>
@@ -21095,19 +21083,19 @@
         <v>1</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
       <c r="F30" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J30" s="12"/>
     </row>
@@ -21120,19 +21108,19 @@
         <v>1</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J31" s="12"/>
     </row>
@@ -21145,23 +21133,23 @@
         <v>1</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G32" s="12">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J32" s="12"/>
     </row>
@@ -21174,23 +21162,23 @@
         <v>1</v>
       </c>
       <c r="C33" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G33" s="12">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J33" s="12"/>
     </row>
@@ -21203,23 +21191,23 @@
         <v>1</v>
       </c>
       <c r="C34" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G34" s="12">
         <v>0</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J34" s="12"/>
     </row>
@@ -21232,23 +21220,23 @@
         <v>1</v>
       </c>
       <c r="C35" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G35" s="12">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J35" s="12"/>
     </row>
@@ -21261,23 +21249,23 @@
         <v>1</v>
       </c>
       <c r="C36" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G36" s="12">
         <v>0</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J36" s="12"/>
     </row>
@@ -21290,23 +21278,23 @@
         <v>1</v>
       </c>
       <c r="C37" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G37" s="12">
         <v>0</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J37" s="12"/>
     </row>
@@ -21319,23 +21307,23 @@
         <v>1</v>
       </c>
       <c r="C38" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G38" s="12">
         <v>0</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J38" s="12"/>
     </row>
@@ -21348,23 +21336,23 @@
         <v>1</v>
       </c>
       <c r="C39" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G39" s="12">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J39" s="12"/>
     </row>
@@ -21377,23 +21365,23 @@
         <v>1</v>
       </c>
       <c r="C40" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G40" s="12">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J40" s="12"/>
     </row>
@@ -21406,23 +21394,23 @@
         <v>1</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G41" s="12">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J41" s="12"/>
     </row>
@@ -21435,23 +21423,23 @@
         <v>1</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G42" s="12">
         <v>12</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J42" s="12"/>
     </row>
@@ -21464,23 +21452,23 @@
         <v>1</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G43" s="12">
         <v>12</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J43" s="12"/>
     </row>
@@ -21493,371 +21481,371 @@
         <v>1</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G44" s="12">
         <v>12</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J44" s="12"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B45" s="46" t="b">
         <f>A45=Metadata!A45</f>
         <v>1</v>
       </c>
       <c r="C45" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G45" s="12">
         <v>0</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J45" s="12"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B46" s="46" t="b">
         <f>A46=Metadata!A46</f>
         <v>1</v>
       </c>
       <c r="C46" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G46" s="12">
         <v>0</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J46" s="12"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" s="46" t="b">
         <f>A47=Metadata!A47</f>
         <v>1</v>
       </c>
       <c r="C47" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G47" s="12">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J47" s="12"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B48" s="46" t="b">
         <f>A48=Metadata!A48</f>
         <v>1</v>
       </c>
       <c r="C48" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G48" s="12">
         <v>0</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J48" s="12"/>
     </row>
     <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" s="46" t="b">
         <f>A49=Metadata!A49</f>
         <v>1</v>
       </c>
       <c r="C49" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D49" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G49" s="12">
         <v>0</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J49" s="12"/>
     </row>
     <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B50" s="46" t="b">
         <f>A50=Metadata!A50</f>
         <v>1</v>
       </c>
       <c r="C50" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G50" s="12">
         <v>0</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J50" s="12"/>
     </row>
     <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B51" s="46" t="b">
         <f>A51=Metadata!A51</f>
         <v>1</v>
       </c>
       <c r="C51" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G51" s="12">
         <v>0</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J51" s="12"/>
     </row>
     <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B52" s="46" t="b">
         <f>A52=Metadata!A52</f>
         <v>1</v>
       </c>
       <c r="C52" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G52" s="12">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J52" s="12"/>
     </row>
     <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B53" s="46" t="b">
         <f>A53=Metadata!A53</f>
         <v>1</v>
       </c>
       <c r="C53" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G53" s="12">
         <v>0</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J53" s="12"/>
     </row>
     <row r="54" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" s="46" t="b">
         <f>A54=Metadata!A54</f>
         <v>1</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G54" s="12">
         <v>12</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J54" s="12"/>
     </row>
     <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="42" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B55" s="46" t="b">
         <f>A55=Metadata!A55</f>
         <v>1</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G55" s="12">
         <v>12</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J55" s="12"/>
     </row>
     <row r="56" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B56" s="46" t="b">
         <f>A56=Metadata!A56</f>
         <v>1</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G56" s="12">
         <v>12</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J56" s="12"/>
     </row>
@@ -21870,23 +21858,23 @@
         <v>1</v>
       </c>
       <c r="C57" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D57" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G57" s="12">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J57" s="12"/>
     </row>
@@ -21899,23 +21887,23 @@
         <v>1</v>
       </c>
       <c r="C58" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D58" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G58" s="12">
         <v>0</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J58" s="12"/>
     </row>
@@ -21928,23 +21916,23 @@
         <v>1</v>
       </c>
       <c r="C59" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G59" s="12">
         <v>0</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J59" s="12"/>
     </row>
@@ -21957,23 +21945,23 @@
         <v>1</v>
       </c>
       <c r="C60" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G60" s="12">
         <v>0</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J60" s="12"/>
     </row>
@@ -21986,23 +21974,23 @@
         <v>1</v>
       </c>
       <c r="C61" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D61" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G61" s="12">
         <v>0</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J61" s="12"/>
     </row>
@@ -22015,23 +22003,23 @@
         <v>1</v>
       </c>
       <c r="C62" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G62" s="12">
         <v>0</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J62" s="12"/>
     </row>
@@ -22044,23 +22032,23 @@
         <v>1</v>
       </c>
       <c r="C63" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D63" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G63" s="12">
         <v>0</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J63" s="12"/>
     </row>
@@ -22073,23 +22061,23 @@
         <v>1</v>
       </c>
       <c r="C64" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G64" s="12">
         <v>0</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J64" s="12"/>
     </row>
@@ -22102,23 +22090,23 @@
         <v>1</v>
       </c>
       <c r="C65" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D65" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G65" s="12">
         <v>0</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J65" s="12"/>
     </row>
@@ -22131,23 +22119,23 @@
         <v>1</v>
       </c>
       <c r="C66" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G66" s="12">
         <v>0</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J66" s="12"/>
     </row>
@@ -22160,23 +22148,23 @@
         <v>1</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G67" s="12">
         <v>12</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J67" s="12"/>
     </row>
@@ -22189,23 +22177,23 @@
         <v>1</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G68" s="12">
         <v>12</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J68" s="12"/>
     </row>
@@ -22218,23 +22206,23 @@
         <v>1</v>
       </c>
       <c r="C69" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G69" s="12">
         <v>0</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J69" s="12"/>
     </row>
@@ -22247,21 +22235,21 @@
         <v>1</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="12"/>
       <c r="F70" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G70" s="12">
         <v>0</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J70" s="12"/>
     </row>
@@ -22274,10 +22262,10 @@
         <v>1</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
@@ -22295,19 +22283,19 @@
         <v>1</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
       <c r="G72" s="12"/>
       <c r="H72" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J72" s="12"/>
     </row>
@@ -22320,23 +22308,23 @@
         <v>1</v>
       </c>
       <c r="C73" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D73" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G73" s="12">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G73" s="12">
-        <v>0</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I73" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J73" s="12"/>
     </row>
@@ -22349,23 +22337,23 @@
         <v>1</v>
       </c>
       <c r="C74" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D74" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G74" s="12">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G74" s="12">
-        <v>0</v>
-      </c>
-      <c r="H74" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I74" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J74" s="12"/>
     </row>
@@ -22378,25 +22366,25 @@
         <v>1</v>
       </c>
       <c r="C75" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D75" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="E75" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="F75" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E75" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="F75" s="12" t="s">
+      <c r="G75" s="12">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G75" s="12">
-        <v>0</v>
-      </c>
-      <c r="H75" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I75" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J75" s="12"/>
     </row>
@@ -22409,23 +22397,23 @@
         <v>1</v>
       </c>
       <c r="C76" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D76" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G76" s="12">
+        <v>0</v>
+      </c>
+      <c r="H76" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G76" s="12">
-        <v>0</v>
-      </c>
-      <c r="H76" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I76" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J76" s="12"/>
     </row>
@@ -22438,21 +22426,21 @@
         <v>1</v>
       </c>
       <c r="C77" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G77" s="12"/>
       <c r="H77" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J77" s="12"/>
     </row>
@@ -22465,23 +22453,23 @@
         <v>1</v>
       </c>
       <c r="C78" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G78" s="12">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G78" s="12">
-        <v>0</v>
-      </c>
-      <c r="H78" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I78" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J78" s="12"/>
     </row>
@@ -22494,23 +22482,23 @@
         <v>1</v>
       </c>
       <c r="C79" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G79" s="12">
+        <v>0</v>
+      </c>
+      <c r="H79" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G79" s="12">
-        <v>0</v>
-      </c>
-      <c r="H79" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I79" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J79" s="12"/>
     </row>
@@ -22523,25 +22511,25 @@
         <v>1</v>
       </c>
       <c r="C80" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D80" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="E80" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="F80" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E80" s="29" t="s">
-        <v>286</v>
-      </c>
-      <c r="F80" s="12" t="s">
+      <c r="G80" s="12">
+        <v>0</v>
+      </c>
+      <c r="H80" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G80" s="12">
-        <v>0</v>
-      </c>
-      <c r="H80" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I80" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J80" s="12"/>
     </row>
@@ -22554,23 +22542,23 @@
         <v>1</v>
       </c>
       <c r="C81" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G81" s="12">
+        <v>0</v>
+      </c>
+      <c r="H81" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G81" s="12">
-        <v>0</v>
-      </c>
-      <c r="H81" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I81" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J81" s="12"/>
     </row>
@@ -22583,21 +22571,21 @@
         <v>1</v>
       </c>
       <c r="C82" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D82" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G82" s="12"/>
       <c r="H82" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J82" s="12"/>
     </row>
@@ -22610,23 +22598,23 @@
         <v>1</v>
       </c>
       <c r="C83" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D83" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G83" s="12">
+        <v>0</v>
+      </c>
+      <c r="H83" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G83" s="12">
-        <v>0</v>
-      </c>
-      <c r="H83" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I83" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J83" s="12"/>
     </row>
@@ -22639,23 +22627,23 @@
         <v>1</v>
       </c>
       <c r="C84" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D84" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G84" s="12">
+        <v>0</v>
+      </c>
+      <c r="H84" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G84" s="12">
-        <v>0</v>
-      </c>
-      <c r="H84" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I84" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J84" s="12"/>
     </row>
@@ -22668,25 +22656,25 @@
         <v>1</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D85" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E85" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="F85" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="E85" s="29" t="s">
-        <v>287</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="G85" s="12">
         <v>12</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J85" s="12"/>
     </row>
@@ -22699,23 +22687,23 @@
         <v>1</v>
       </c>
       <c r="C86" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D86" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G86" s="12">
+        <v>0</v>
+      </c>
+      <c r="H86" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G86" s="12">
-        <v>0</v>
-      </c>
-      <c r="H86" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I86" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J86" s="12"/>
     </row>
@@ -22728,21 +22716,21 @@
         <v>1</v>
       </c>
       <c r="C87" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D87" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G87" s="12"/>
       <c r="H87" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J87" s="12"/>
     </row>
@@ -22755,23 +22743,23 @@
         <v>1</v>
       </c>
       <c r="C88" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D88" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G88" s="12">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J88" s="12"/>
     </row>
@@ -22784,23 +22772,23 @@
         <v>1</v>
       </c>
       <c r="C89" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D89" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G89" s="12">
+        <v>0</v>
+      </c>
+      <c r="H89" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G89" s="12">
-        <v>0</v>
-      </c>
-      <c r="H89" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I89" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J89" s="12"/>
     </row>
@@ -22813,23 +22801,23 @@
         <v>1</v>
       </c>
       <c r="C90" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D90" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G90" s="12">
+        <v>0</v>
+      </c>
+      <c r="H90" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G90" s="12">
-        <v>0</v>
-      </c>
-      <c r="H90" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I90" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J90" s="12"/>
     </row>
@@ -22842,17 +22830,17 @@
         <v>1</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D91" s="12"/>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I91" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J91" s="12"/>
     </row>
@@ -22865,23 +22853,23 @@
         <v>1</v>
       </c>
       <c r="C92" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D92" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G92" s="12">
         <v>0</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J92" s="12"/>
     </row>
@@ -22894,10 +22882,10 @@
         <v>1</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -22915,23 +22903,23 @@
         <v>1</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G94" s="12">
         <v>0</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J94" s="12"/>
     </row>
@@ -22944,17 +22932,17 @@
         <v>1</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J95" s="12"/>
     </row>
@@ -22967,7 +22955,7 @@
         <v>1</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="12"/>
@@ -22986,10 +22974,10 @@
         <v>1</v>
       </c>
       <c r="C97" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
@@ -23007,10 +22995,10 @@
         <v>1</v>
       </c>
       <c r="C98" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D98" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
@@ -23028,10 +23016,10 @@
         <v>1</v>
       </c>
       <c r="C99" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D99" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -23049,19 +23037,19 @@
         <v>1</v>
       </c>
       <c r="C100" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D100" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J100" s="12"/>
     </row>
@@ -23074,23 +23062,23 @@
         <v>1</v>
       </c>
       <c r="C101" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D101" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G101" s="12">
         <v>0</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J101" s="12"/>
     </row>
@@ -23103,23 +23091,23 @@
         <v>1</v>
       </c>
       <c r="C102" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D102" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G102" s="12">
         <v>0</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J102" s="12"/>
     </row>
@@ -23132,10 +23120,10 @@
         <v>1</v>
       </c>
       <c r="C103" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D103" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
@@ -23153,23 +23141,23 @@
         <v>1</v>
       </c>
       <c r="C104" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D104" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G104" s="12">
         <v>0</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J104" s="12"/>
     </row>
@@ -23182,23 +23170,23 @@
         <v>1</v>
       </c>
       <c r="C105" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D105" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D105" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G105" s="12">
         <v>0</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J105" s="12">
         <v>1</v>
@@ -23213,23 +23201,23 @@
         <v>1</v>
       </c>
       <c r="C106" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D106" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G106" s="8">
         <v>0</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J106" s="12"/>
     </row>
@@ -23243,7 +23231,7 @@
       </c>
       <c r="C107" s="12"/>
       <c r="D107" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="8"/>
@@ -23261,19 +23249,19 @@
         <v>1</v>
       </c>
       <c r="C108" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D108" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
       <c r="H108" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J108" s="12"/>
     </row>
@@ -23286,10 +23274,10 @@
         <v>1</v>
       </c>
       <c r="C109" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D109" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="8"/>
@@ -23307,23 +23295,23 @@
         <v>1</v>
       </c>
       <c r="C110" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D110" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="D110" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G110" s="8">
         <v>0</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J110" s="12"/>
     </row>
@@ -23336,19 +23324,19 @@
         <v>1</v>
       </c>
       <c r="C111" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D111" s="12" t="s">
         <v>282</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>283</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
       <c r="H111" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J111" s="12"/>
     </row>
@@ -23361,17 +23349,17 @@
         <v>1</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D112" s="12"/>
       <c r="E112" s="12"/>
       <c r="F112" s="8"/>
       <c r="G112" s="8"/>
       <c r="H112" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J112" s="12"/>
     </row>
@@ -23384,19 +23372,19 @@
         <v>1</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
       <c r="H113" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J113" s="12"/>
     </row>
@@ -23409,14 +23397,14 @@
         <v>1</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G114" s="8"/>
       <c r="H114" s="12"/>
@@ -23432,7 +23420,7 @@
         <v>1</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D115" s="12"/>
       <c r="E115" s="12"/>
@@ -23451,7 +23439,7 @@
         <v>1</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D116" s="12"/>
       <c r="E116" s="12"/>
@@ -23470,10 +23458,10 @@
         <v>1</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="8"/>
@@ -23491,10 +23479,10 @@
         <v>1</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="8"/>
@@ -23512,10 +23500,10 @@
         <v>1</v>
       </c>
       <c r="C119" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D119" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="8"/>
@@ -23533,23 +23521,23 @@
         <v>1</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G120" s="8">
         <v>0</v>
       </c>
       <c r="H120" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I120" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J120" s="12"/>
     </row>
@@ -25756,10 +25744,10 @@
         <v>177</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -25767,7 +25755,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C2" s="28"/>
     </row>
@@ -25776,7 +25764,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C3" s="12"/>
     </row>
@@ -25785,7 +25773,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C4" s="12"/>
     </row>
@@ -25794,7 +25782,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -25803,7 +25791,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C6" s="12"/>
     </row>
@@ -25812,7 +25800,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C7" s="12"/>
     </row>
@@ -25821,7 +25809,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C8" s="12"/>
     </row>
@@ -25830,7 +25818,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C9" s="12"/>
     </row>
@@ -25839,7 +25827,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C10" s="12"/>
     </row>
@@ -25848,7 +25836,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C11" s="12"/>
     </row>
@@ -25857,7 +25845,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -25866,7 +25854,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -25875,7 +25863,7 @@
         <v>39</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -25891,16 +25879,16 @@
         <v>45</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17" s="31" t="s">
         <v>297</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>298</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -25916,7 +25904,7 @@
         <v>50</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C19" s="12"/>
     </row>
@@ -25932,7 +25920,7 @@
         <v>53</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C21" s="12"/>
     </row>
@@ -25941,7 +25929,7 @@
         <v>55</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C22" s="12"/>
     </row>
@@ -25957,7 +25945,7 @@
         <v>59</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C24" s="12"/>
     </row>
@@ -25966,7 +25954,7 @@
         <v>61</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C25" s="12"/>
     </row>
@@ -25975,7 +25963,7 @@
         <v>62</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C26" s="12"/>
     </row>
@@ -25984,7 +25972,7 @@
         <v>63</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C27" s="12"/>
     </row>
@@ -25993,7 +25981,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C28" s="12"/>
     </row>
@@ -26002,7 +25990,7 @@
         <v>65</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C29" s="12"/>
     </row>
@@ -26011,7 +25999,7 @@
         <v>67</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C30" s="12"/>
     </row>
@@ -26020,7 +26008,7 @@
         <v>69</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C31" s="12"/>
     </row>
@@ -26029,7 +26017,7 @@
         <v>70</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C32" s="12"/>
     </row>
@@ -26038,7 +26026,7 @@
         <v>72</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C33" s="12"/>
     </row>
@@ -26047,7 +26035,7 @@
         <v>73</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C34" s="12"/>
     </row>
@@ -26056,7 +26044,7 @@
         <v>75</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C35" s="12"/>
     </row>
@@ -26072,7 +26060,7 @@
         <v>77</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C37" s="12"/>
     </row>
@@ -26081,7 +26069,7 @@
         <v>78</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C38" s="12"/>
     </row>
@@ -26090,7 +26078,7 @@
         <v>79</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C39" s="12"/>
     </row>
@@ -26106,7 +26094,7 @@
         <v>81</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C41" s="12"/>
     </row>
@@ -26115,7 +26103,7 @@
         <v>82</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C42" s="12"/>
     </row>
@@ -26124,7 +26112,7 @@
         <v>83</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C43" s="12"/>
     </row>
@@ -26231,7 +26219,7 @@
         <v>99</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C58" s="12"/>
     </row>
@@ -26240,7 +26228,7 @@
         <v>100</v>
       </c>
       <c r="B59" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C59" s="12"/>
     </row>
@@ -26249,7 +26237,7 @@
         <v>101</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C60" s="12"/>
     </row>
@@ -26258,7 +26246,7 @@
         <v>102</v>
       </c>
       <c r="B61" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C61" s="12"/>
     </row>
@@ -26267,7 +26255,7 @@
         <v>104</v>
       </c>
       <c r="B62" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C62" s="12"/>
     </row>
@@ -26276,7 +26264,7 @@
         <v>105</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C63" s="12"/>
     </row>
@@ -26285,7 +26273,7 @@
         <v>106</v>
       </c>
       <c r="B64" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C64" s="12"/>
     </row>
@@ -26294,7 +26282,7 @@
         <v>109</v>
       </c>
       <c r="B65" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C65" s="12"/>
     </row>
@@ -26303,7 +26291,7 @@
         <v>111</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C66" s="12"/>
     </row>
@@ -26312,7 +26300,7 @@
         <v>112</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C67" s="12"/>
     </row>
@@ -26321,7 +26309,7 @@
         <v>113</v>
       </c>
       <c r="B68" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="12"/>
     </row>
@@ -26330,7 +26318,7 @@
         <v>114</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="12"/>
     </row>
@@ -26339,7 +26327,7 @@
         <v>115</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="12"/>
     </row>
@@ -26348,7 +26336,7 @@
         <v>116</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C71" s="12"/>
     </row>
@@ -26357,7 +26345,7 @@
         <v>117</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C72" s="12"/>
     </row>
@@ -26366,7 +26354,7 @@
         <v>118</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C73" s="12"/>
     </row>
@@ -26375,7 +26363,7 @@
         <v>119</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C74" s="12"/>
     </row>
@@ -26384,7 +26372,7 @@
         <v>120</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C75" s="12"/>
     </row>
@@ -26393,7 +26381,7 @@
         <v>121</v>
       </c>
       <c r="B76" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C76" s="12"/>
     </row>
@@ -26402,7 +26390,7 @@
         <v>123</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C77" s="12"/>
     </row>
@@ -26411,7 +26399,7 @@
         <v>126</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C78" s="12"/>
     </row>
@@ -26420,7 +26408,7 @@
         <v>127</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C79" s="12"/>
     </row>
@@ -26429,7 +26417,7 @@
         <v>128</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C80" s="12"/>
     </row>
@@ -26438,7 +26426,7 @@
         <v>131</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C81" s="12"/>
     </row>
@@ -26447,7 +26435,7 @@
         <v>132</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C82" s="12"/>
     </row>
@@ -26456,7 +26444,7 @@
         <v>133</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C83" s="12"/>
     </row>
@@ -26465,7 +26453,7 @@
         <v>135</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C84" s="12"/>
     </row>
@@ -26474,7 +26462,7 @@
         <v>136</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C85" s="12"/>
     </row>
@@ -26483,7 +26471,7 @@
         <v>138</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C86" s="12"/>
     </row>
@@ -26492,7 +26480,7 @@
         <v>139</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C87" s="12"/>
     </row>
@@ -26501,7 +26489,7 @@
         <v>140</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C88" s="12"/>
     </row>
@@ -26510,7 +26498,7 @@
         <v>142</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C89" s="12"/>
     </row>
@@ -26519,7 +26507,7 @@
         <v>144</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C90" s="12"/>
     </row>
@@ -26528,7 +26516,7 @@
         <v>146</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C91" s="12"/>
     </row>
@@ -26537,7 +26525,7 @@
         <v>148</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C92" s="12"/>
     </row>
@@ -26546,7 +26534,7 @@
         <v>150</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C93" s="12"/>
     </row>
@@ -26555,7 +26543,7 @@
         <v>152</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C94" s="12"/>
     </row>
@@ -26564,7 +26552,7 @@
         <v>154</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C95" s="12"/>
     </row>
@@ -26573,7 +26561,7 @@
         <v>156</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C96" s="12"/>
     </row>
@@ -26582,7 +26570,7 @@
         <v>158</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C97" s="12"/>
     </row>
@@ -26591,7 +26579,7 @@
         <v>160</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C98" s="12"/>
     </row>
@@ -26600,7 +26588,7 @@
         <v>162</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C99" s="12"/>
     </row>
@@ -26609,7 +26597,7 @@
         <v>110</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C100" s="12"/>
     </row>
@@ -26618,7 +26606,7 @@
         <v>165</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C101" s="12"/>
     </row>
@@ -26627,7 +26615,7 @@
         <v>167</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C102" s="12"/>
     </row>
@@ -26636,7 +26624,7 @@
         <v>168</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C103" s="12"/>
     </row>
@@ -26645,7 +26633,7 @@
         <v>169</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C104" s="12"/>
     </row>
@@ -26654,7 +26642,7 @@
         <v>170</v>
       </c>
       <c r="B105" s="32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C105" s="12"/>
     </row>
@@ -26663,7 +26651,7 @@
         <v>171</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C106" s="12"/>
     </row>
@@ -26672,7 +26660,7 @@
         <v>172</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C107" s="12"/>
     </row>
@@ -26681,7 +26669,7 @@
         <v>174</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C108" s="12"/>
     </row>
@@ -26798,13 +26786,13 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>45960.470200462965</v>
+        <v>45960.506171875</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanos\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.natsikas\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F5A49F-5FA5-4722-BB97-A5BAF8B6B87E}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA4ACF1-EE57-4CCA-ACF0-5BE54D9362BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Read Settings'!$A$1:$I$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Time Settings'!$A$1:$J$120</definedName>
   </definedNames>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -1198,7 +1209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="340">
   <si>
     <t>Report Name</t>
   </si>
@@ -1873,9 +1884,6 @@
     <t>['LTPTRsNominationsSummary']</t>
   </si>
   <si>
-    <t>range(2,27,1)</t>
-  </si>
-  <si>
     <t>['RealTimeSCADARES']</t>
   </si>
   <si>
@@ -1978,9 +1986,6 @@
     <t>ISPRequirements.txt</t>
   </si>
   <si>
-    <t>{'FYROM':'NORTH MACEDONIA'}</t>
-  </si>
-  <si>
     <t>ReservoirFillingRate.txt</t>
   </si>
   <si>
@@ -2225,6 +2230,9 @@
   </si>
   <si>
     <t>range(1,101,1)</t>
+  </si>
+  <si>
+    <t>{'FYROM':'NORTH MACEDONIA', 'CET Hour': 'Hour (CET)'}</t>
   </si>
 </sst>
 </file>
@@ -3672,9 +3680,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3712,7 +3720,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3818,7 +3826,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3960,7 +3968,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5038,7 +5046,7 @@
         <v>42005</v>
       </c>
       <c r="G31" s="48" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H31" s="8" t="b">
         <f>TRUE()</f>
@@ -5105,10 +5113,10 @@
         <v>176</v>
       </c>
       <c r="F33" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G33" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H33" s="8" t="b">
         <f>TRUE()</f>
@@ -5140,10 +5148,10 @@
         <v>176</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G34" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H34" s="8" t="b">
         <f>TRUE()</f>
@@ -5175,10 +5183,10 @@
         <v>176</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G35" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H35" s="8" t="b">
         <f>TRUE()</f>
@@ -5210,10 +5218,10 @@
         <v>176</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G36" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H36" s="8" t="b">
         <f>TRUE()</f>
@@ -5247,10 +5255,10 @@
         <v>176</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G37" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H37" s="8" t="b">
         <f>TRUE()</f>
@@ -5282,10 +5290,10 @@
         <v>176</v>
       </c>
       <c r="F38" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G38" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H38" s="8" t="b">
         <f>TRUE()</f>
@@ -5317,10 +5325,10 @@
         <v>176</v>
       </c>
       <c r="F39" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G39" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H39" s="8" t="b">
         <f>TRUE()</f>
@@ -5352,10 +5360,10 @@
         <v>176</v>
       </c>
       <c r="F40" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G40" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H40" s="8" t="b">
         <f>TRUE()</f>
@@ -5389,10 +5397,10 @@
         <v>176</v>
       </c>
       <c r="F41" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G41" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H41" s="8" t="b">
         <f>TRUE()</f>
@@ -5424,10 +5432,10 @@
         <v>176</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G42" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H42" s="8" t="b">
         <f>TRUE()</f>
@@ -5459,10 +5467,10 @@
         <v>176</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G43" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H43" s="8" t="b">
         <f>TRUE()</f>
@@ -5494,10 +5502,10 @@
         <v>176</v>
       </c>
       <c r="F44" s="40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G44" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H44" s="8" t="b">
         <f>TRUE()</f>
@@ -5518,7 +5526,7 @@
     </row>
     <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8" t="s">
@@ -5531,7 +5539,7 @@
         <v>176</v>
       </c>
       <c r="F45" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G45" s="47"/>
       <c r="H45" s="8" t="b">
@@ -5551,7 +5559,7 @@
     </row>
     <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="8" t="s">
@@ -5564,7 +5572,7 @@
         <v>176</v>
       </c>
       <c r="F46" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G46" s="47">
         <v>45930</v>
@@ -5586,7 +5594,7 @@
     </row>
     <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="8" t="s">
@@ -5599,7 +5607,7 @@
         <v>176</v>
       </c>
       <c r="F47" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G47" s="47"/>
       <c r="H47" s="8" t="b">
@@ -5619,7 +5627,7 @@
     </row>
     <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="8" t="s">
@@ -5632,7 +5640,7 @@
         <v>176</v>
       </c>
       <c r="F48" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G48" s="47">
         <v>45930</v>
@@ -5654,7 +5662,7 @@
     </row>
     <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="8" t="s">
@@ -5667,7 +5675,7 @@
         <v>176</v>
       </c>
       <c r="F49" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G49" s="47"/>
       <c r="H49" s="8" t="b">
@@ -5687,7 +5695,7 @@
     </row>
     <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="8" t="s">
@@ -5700,7 +5708,7 @@
         <v>176</v>
       </c>
       <c r="F50" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G50" s="47">
         <v>45930</v>
@@ -5722,7 +5730,7 @@
     </row>
     <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="8" t="s">
@@ -5735,7 +5743,7 @@
         <v>176</v>
       </c>
       <c r="F51" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G51" s="47"/>
       <c r="H51" s="8" t="b">
@@ -5755,7 +5763,7 @@
     </row>
     <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
@@ -5768,7 +5776,7 @@
         <v>176</v>
       </c>
       <c r="F52" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G52" s="47">
         <v>45930</v>
@@ -5790,7 +5798,7 @@
     </row>
     <row r="53" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="8" t="s">
@@ -5803,7 +5811,7 @@
         <v>176</v>
       </c>
       <c r="F53" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G53" s="47"/>
       <c r="H53" s="8" t="b">
@@ -5823,7 +5831,7 @@
     </row>
     <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="8" t="s">
@@ -5836,7 +5844,7 @@
         <v>176</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G54" s="47">
         <v>45930</v>
@@ -5858,7 +5866,7 @@
     </row>
     <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="8" t="s">
@@ -5871,7 +5879,7 @@
         <v>176</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G55" s="47"/>
       <c r="H55" s="8" t="b">
@@ -5891,7 +5899,7 @@
     </row>
     <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="8" t="s">
@@ -5904,7 +5912,7 @@
         <v>176</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G56" s="47">
         <v>45930</v>
@@ -5942,7 +5950,7 @@
         <v>43841</v>
       </c>
       <c r="G57" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H57" s="8" t="b">
         <f>TRUE()</f>
@@ -5977,7 +5985,7 @@
         <v>43841</v>
       </c>
       <c r="G58" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H58" s="8" t="b">
         <f>TRUE()</f>
@@ -6014,7 +6022,7 @@
         <v>43841</v>
       </c>
       <c r="G59" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H59" s="8" t="b">
         <f>TRUE()</f>
@@ -6049,7 +6057,7 @@
         <v>43841</v>
       </c>
       <c r="G60" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H60" s="8" t="b">
         <f>TRUE()</f>
@@ -6086,7 +6094,7 @@
         <v>43841</v>
       </c>
       <c r="G61" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H61" s="8" t="b">
         <f>TRUE()</f>
@@ -6121,7 +6129,7 @@
         <v>43841</v>
       </c>
       <c r="G62" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H62" s="8" t="b">
         <f>TRUE()</f>
@@ -6158,7 +6166,7 @@
         <v>43841</v>
       </c>
       <c r="G63" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H63" s="8" t="b">
         <f>TRUE()</f>
@@ -6193,7 +6201,7 @@
         <v>43841</v>
       </c>
       <c r="G64" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H64" s="8" t="b">
         <f>TRUE()</f>
@@ -6230,7 +6238,7 @@
         <v>43841</v>
       </c>
       <c r="G65" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H65" s="8" t="b">
         <f>TRUE()</f>
@@ -6265,7 +6273,7 @@
         <v>43841</v>
       </c>
       <c r="G66" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H66" s="8" t="b">
         <f>TRUE()</f>
@@ -6302,7 +6310,7 @@
         <v>43841</v>
       </c>
       <c r="G67" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H67" s="8" t="b">
         <f>TRUE()</f>
@@ -6337,7 +6345,7 @@
         <v>43841</v>
       </c>
       <c r="G68" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H68" s="8" t="b">
         <f>TRUE()</f>
@@ -10649,7 +10657,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L120" xr:uid="{D0972C50-907B-4A2C-82F0-ED51F06329AA}">
-    <sortState ref="A2:L120">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L120">
       <sortCondition ref="A2:A120"/>
     </sortState>
   </autoFilter>
@@ -11008,7 +11016,7 @@
         <v>182</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>183</v>
@@ -11189,7 +11197,7 @@
         <v>187</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H10" s="12">
         <v>0</v>
@@ -11213,7 +11221,7 @@
         <v>206</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H11" s="12">
         <v>0</v>
@@ -11990,7 +11998,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="42" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B45" s="41" t="b">
         <f>Metadata!A45=A45</f>
@@ -12014,7 +12022,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="42" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B46" s="41" t="b">
         <f>Metadata!A46=A46</f>
@@ -12038,7 +12046,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="42" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B47" s="41" t="b">
         <f>Metadata!A47=A47</f>
@@ -12064,7 +12072,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="42" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B48" s="41" t="b">
         <f>Metadata!A48=A48</f>
@@ -12090,7 +12098,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B49" s="41" t="b">
         <f>Metadata!A49=A49</f>
@@ -12114,7 +12122,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="42" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B50" s="41" t="b">
         <f>Metadata!A50=A50</f>
@@ -12138,7 +12146,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B51" s="41" t="b">
         <f>Metadata!A51=A51</f>
@@ -12164,7 +12172,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="42" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B52" s="41" t="b">
         <f>Metadata!A52=A52</f>
@@ -12190,7 +12198,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B53" s="41" t="b">
         <f>Metadata!A53=A53</f>
@@ -12214,7 +12222,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="42" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B54" s="41" t="b">
         <f>Metadata!A54=A54</f>
@@ -12238,7 +12246,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="42" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B55" s="41" t="b">
         <f>Metadata!A55=A55</f>
@@ -12264,7 +12272,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="42" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B56" s="41" t="b">
         <f>Metadata!A56=A56</f>
@@ -12695,7 +12703,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
@@ -12721,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -12821,7 +12829,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
@@ -12847,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
@@ -12947,7 +12955,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
@@ -12973,7 +12981,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
@@ -13132,7 +13140,7 @@
       <c r="H91" s="12"/>
       <c r="I91" s="12"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="20" t="s">
         <v>128</v>
       </c>
@@ -13154,11 +13162,9 @@
         <v>222</v>
       </c>
       <c r="H92" s="12">
-        <v>1</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>223</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I92" s="12"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="20" t="s">
@@ -13188,14 +13194,14 @@
         <v>184</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E94" s="18"/>
       <c r="F94" s="12" t="s">
         <v>194</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H94" s="12">
         <v>2</v>
@@ -13321,7 +13327,7 @@
         <v>187</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H101" s="12">
         <v>1</v>
@@ -13345,7 +13351,7 @@
         <v>187</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H102" s="12">
         <v>1</v>
@@ -13385,7 +13391,7 @@
         <v>187</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H104" s="12">
         <v>2</v>
@@ -13404,14 +13410,14 @@
         <v>203</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E105" s="18"/>
       <c r="F105" s="12" t="s">
         <v>187</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H105" s="12">
         <v>0</v>
@@ -13430,20 +13436,20 @@
         <v>203</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E106" s="18"/>
       <c r="F106" s="12" t="s">
         <v>187</v>
       </c>
       <c r="G106" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="H106" s="12">
+        <v>0</v>
+      </c>
+      <c r="I106" s="12" t="s">
         <v>230</v>
-      </c>
-      <c r="H106" s="12">
-        <v>0</v>
-      </c>
-      <c r="I106" s="12" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
@@ -13473,7 +13479,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D108" s="18"/>
       <c r="E108" s="18"/>
@@ -13514,16 +13520,16 @@
       <c r="D110" s="8"/>
       <c r="E110" s="18"/>
       <c r="F110" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="G110" s="8" t="s">
         <v>233</v>
-      </c>
-      <c r="G110" s="8" t="s">
-        <v>234</v>
       </c>
       <c r="H110" s="12">
         <v>4</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
@@ -13567,7 +13573,7 @@
         <v>1</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="18"/>
@@ -13686,10 +13692,10 @@
       <c r="D120" s="8"/>
       <c r="E120" s="18"/>
       <c r="F120" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="G120" s="8" t="s">
         <v>236</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>237</v>
       </c>
       <c r="H120" s="12">
         <v>2</v>
@@ -15678,7 +15684,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I111" xr:uid="{776C4DE2-2957-440A-A09D-B0AB3152981D}">
-    <sortState ref="A2:I120">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I120">
       <sortCondition ref="A1:A111"/>
     </sortState>
   </autoFilter>
@@ -15778,25 +15784,25 @@
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1" s="22" t="s">
         <v>238</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -15808,17 +15814,17 @@
         <v>1</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>246</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>247</v>
       </c>
       <c r="H2" s="25"/>
       <c r="I2" s="26"/>
@@ -15868,7 +15874,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H5" s="27"/>
       <c r="I5" s="20"/>
@@ -15886,7 +15892,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H6" s="27"/>
       <c r="I6" s="20"/>
@@ -15952,7 +15958,7 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H10" s="27" t="b">
         <v>0</v>
@@ -15970,13 +15976,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H11" s="27"/>
       <c r="I11" s="20"/>
@@ -16010,7 +16016,7 @@
       <c r="E13" s="14"/>
       <c r="F13" s="8"/>
       <c r="G13" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H13" s="27" t="b">
         <f>TRUE()</f>
@@ -16034,7 +16040,7 @@
       <c r="E14" s="14"/>
       <c r="F14" s="8"/>
       <c r="G14" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H14" s="27" t="b">
         <f>TRUE()</f>
@@ -16058,7 +16064,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H15" s="27" t="b">
         <f>TRUE()</f>
@@ -16082,7 +16088,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="8"/>
       <c r="G16" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H16" s="27" t="b">
         <f>TRUE()</f>
@@ -16106,7 +16112,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="8"/>
       <c r="G17" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H17" s="27" t="b">
         <f>TRUE()</f>
@@ -16126,13 +16132,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="14"/>
       <c r="F18" s="8"/>
       <c r="G18" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H18" s="27" t="b">
         <f>FALSE()</f>
@@ -16153,7 +16159,7 @@
       <c r="E19" s="14"/>
       <c r="F19" s="8"/>
       <c r="G19" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H19" s="27" t="b">
         <f>TRUE()</f>
@@ -16173,13 +16179,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="14"/>
       <c r="F20" s="8"/>
       <c r="G20" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H20" s="27"/>
       <c r="I20" s="20"/>
@@ -16193,15 +16199,15 @@
         <v>1</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H21" s="27" t="b">
         <f>FALSE()</f>
@@ -16220,11 +16226,11 @@
       <c r="C22" s="23"/>
       <c r="D22" s="24"/>
       <c r="E22" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H22" s="27"/>
       <c r="I22" s="20"/>
@@ -16238,13 +16244,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H23" s="27"/>
       <c r="I23" s="20"/>
@@ -16290,15 +16296,15 @@
         <v>1</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H26" s="27"/>
       <c r="I26" s="20"/>
@@ -16344,13 +16350,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H29" s="27"/>
       <c r="I29" s="20"/>
@@ -16400,7 +16406,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H32" s="27" t="b">
         <f>FALSE()</f>
@@ -16424,7 +16430,7 @@
       <c r="E33" s="14"/>
       <c r="F33" s="8"/>
       <c r="G33" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H33" s="27" t="b">
         <f>TRUE()</f>
@@ -16448,7 +16454,7 @@
       <c r="E34" s="14"/>
       <c r="F34" s="8"/>
       <c r="G34" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H34" s="27" t="b">
         <f>TRUE()</f>
@@ -16472,7 +16478,7 @@
       <c r="E35" s="14"/>
       <c r="F35" s="8"/>
       <c r="G35" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H35" s="27" t="b">
         <f>TRUE()</f>
@@ -16492,13 +16498,13 @@
         <v>1</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="14"/>
       <c r="F36" s="8"/>
       <c r="G36" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H36" s="27"/>
       <c r="I36" s="20"/>
@@ -16516,7 +16522,7 @@
       <c r="E37" s="14"/>
       <c r="F37" s="8"/>
       <c r="G37" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H37" s="27" t="b">
         <f>TRUE()</f>
@@ -16540,7 +16546,7 @@
       <c r="E38" s="14"/>
       <c r="F38" s="8"/>
       <c r="G38" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H38" s="27" t="b">
         <f>TRUE()</f>
@@ -16564,7 +16570,7 @@
       <c r="E39" s="14"/>
       <c r="F39" s="8"/>
       <c r="G39" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H39" s="27" t="b">
         <f>TRUE()</f>
@@ -16584,13 +16590,13 @@
         <v>1</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="14"/>
       <c r="F40" s="8"/>
       <c r="G40" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H40" s="27"/>
       <c r="I40" s="20"/>
@@ -16608,7 +16614,7 @@
       <c r="E41" s="14"/>
       <c r="F41" s="8"/>
       <c r="G41" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H41" s="27" t="b">
         <f>TRUE()</f>
@@ -16632,7 +16638,7 @@
       <c r="E42" s="14"/>
       <c r="F42" s="8"/>
       <c r="G42" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H42" s="27" t="b">
         <f>TRUE()</f>
@@ -16656,7 +16662,7 @@
       <c r="E43" s="14"/>
       <c r="F43" s="8"/>
       <c r="G43" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H43" s="27" t="b">
         <f>TRUE()</f>
@@ -16676,20 +16682,20 @@
         <v>1</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="14"/>
       <c r="F44" s="8"/>
       <c r="G44" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H44" s="27"/>
       <c r="I44" s="20"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="42" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B45" s="41" t="b">
         <f>A45=Metadata!A45</f>
@@ -16700,7 +16706,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H45" s="27" t="b">
         <f>TRUE()</f>
@@ -16713,7 +16719,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="42" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B46" s="41" t="b">
         <f>A46=Metadata!A46</f>
@@ -16724,7 +16730,7 @@
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H46" s="27" t="b">
         <f>TRUE()</f>
@@ -16737,7 +16743,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="42" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B47" s="41" t="b">
         <f>A47=Metadata!A47</f>
@@ -16748,7 +16754,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H47" s="27" t="b">
         <f>TRUE()</f>
@@ -16761,27 +16767,27 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="42" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B48" s="41" t="b">
         <f>A48=Metadata!A48</f>
         <v>1</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H48" s="27"/>
       <c r="I48" s="20"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B49" s="41" t="b">
         <f>A49=Metadata!A49</f>
@@ -16792,7 +16798,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H49" s="27" t="b">
         <f>TRUE()</f>
@@ -16805,7 +16811,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="42" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B50" s="41" t="b">
         <f>A50=Metadata!A50</f>
@@ -16816,7 +16822,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
       <c r="G50" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H50" s="27" t="b">
         <f>TRUE()</f>
@@ -16829,7 +16835,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B51" s="41" t="b">
         <f>A51=Metadata!A51</f>
@@ -16840,7 +16846,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H51" s="27" t="b">
         <f>TRUE()</f>
@@ -16853,27 +16859,27 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="42" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B52" s="41" t="b">
         <f>A52=Metadata!A52</f>
         <v>1</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H52" s="45"/>
       <c r="I52" s="20"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B53" s="41" t="b">
         <f>A53=Metadata!A53</f>
@@ -16884,7 +16890,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H53" s="27" t="b">
         <f>TRUE()</f>
@@ -16897,7 +16903,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="42" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B54" s="41" t="b">
         <f>A54=Metadata!A54</f>
@@ -16908,7 +16914,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H54" s="27" t="b">
         <f>TRUE()</f>
@@ -16921,7 +16927,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="42" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B55" s="41" t="b">
         <f>A55=Metadata!A55</f>
@@ -16932,7 +16938,7 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H55" s="27" t="b">
         <f>TRUE()</f>
@@ -16945,20 +16951,20 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="42" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B56" s="41" t="b">
         <f>A56=Metadata!A56</f>
         <v>1</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H56" s="45"/>
       <c r="I56" s="20"/>
@@ -16976,7 +16982,7 @@
       <c r="E57" s="14"/>
       <c r="F57" s="8"/>
       <c r="G57" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H57" s="27" t="b">
         <f>TRUE()</f>
@@ -17000,7 +17006,7 @@
       <c r="E58" s="14"/>
       <c r="F58" s="8"/>
       <c r="G58" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H58" s="27" t="b">
         <f>TRUE()</f>
@@ -17024,7 +17030,7 @@
       <c r="E59" s="14"/>
       <c r="F59" s="8"/>
       <c r="G59" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H59" s="27" t="b">
         <f>TRUE()</f>
@@ -17044,13 +17050,13 @@
         <v>1</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="14"/>
       <c r="F60" s="8"/>
       <c r="G60" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H60" s="27"/>
       <c r="I60" s="20"/>
@@ -17068,7 +17074,7 @@
       <c r="E61" s="14"/>
       <c r="F61" s="8"/>
       <c r="G61" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H61" s="27" t="b">
         <f>TRUE()</f>
@@ -17092,7 +17098,7 @@
       <c r="E62" s="14"/>
       <c r="F62" s="8"/>
       <c r="G62" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H62" s="27" t="b">
         <f>TRUE()</f>
@@ -17116,7 +17122,7 @@
       <c r="E63" s="14"/>
       <c r="F63" s="8"/>
       <c r="G63" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H63" s="27" t="b">
         <f>TRUE()</f>
@@ -17136,13 +17142,13 @@
         <v>1</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="14"/>
       <c r="F64" s="8"/>
       <c r="G64" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H64" s="27"/>
       <c r="I64" s="20"/>
@@ -17160,7 +17166,7 @@
       <c r="E65" s="44"/>
       <c r="F65" s="8"/>
       <c r="G65" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H65" s="27" t="b">
         <f>TRUE()</f>
@@ -17184,7 +17190,7 @@
       <c r="E66" s="14"/>
       <c r="F66" s="8"/>
       <c r="G66" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H66" s="27" t="b">
         <f>TRUE()</f>
@@ -17208,7 +17214,7 @@
       <c r="E67" s="14"/>
       <c r="F67" s="8"/>
       <c r="G67" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H67" s="27" t="b">
         <f>TRUE()</f>
@@ -17228,13 +17234,13 @@
         <v>1</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D68" s="24"/>
       <c r="E68" s="14"/>
       <c r="F68" s="8"/>
       <c r="G68" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H68" s="27"/>
       <c r="I68" s="20"/>
@@ -17252,7 +17258,7 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H69" s="27" t="b">
         <f>TRUE()</f>
@@ -17276,7 +17282,7 @@
       <c r="E70" s="23"/>
       <c r="F70" s="8"/>
       <c r="G70" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H70" s="27"/>
       <c r="I70" s="20"/>
@@ -17326,7 +17332,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H73" s="27"/>
       <c r="I73" s="20"/>
@@ -17344,7 +17350,7 @@
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
       <c r="G74" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H74" s="27"/>
       <c r="I74" s="20"/>
@@ -17358,17 +17364,17 @@
         <v>1</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D75" s="24"/>
       <c r="E75" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="G75" s="12" t="s">
         <v>246</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G75" s="12" t="s">
-        <v>247</v>
       </c>
       <c r="H75" s="27"/>
       <c r="I75" s="20"/>
@@ -17382,13 +17388,13 @@
         <v>1</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D76" s="24"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H76" s="27"/>
       <c r="I76" s="20"/>
@@ -17402,15 +17408,15 @@
         <v>1</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D77" s="24"/>
       <c r="E77" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F77" s="8"/>
       <c r="G77" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H77" s="27"/>
       <c r="I77" s="20"/>
@@ -17428,7 +17434,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H78" s="27"/>
       <c r="I78" s="20"/>
@@ -17446,7 +17452,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H79" s="27"/>
       <c r="I79" s="20"/>
@@ -17460,17 +17466,17 @@
         <v>1</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D80" s="24"/>
       <c r="E80" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="G80" s="12" t="s">
         <v>246</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G80" s="12" t="s">
-        <v>247</v>
       </c>
       <c r="H80" s="27"/>
       <c r="I80" s="20"/>
@@ -17484,13 +17490,13 @@
         <v>1</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D81" s="24"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
       <c r="G81" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H81" s="27"/>
       <c r="I81" s="20"/>
@@ -17504,15 +17510,15 @@
         <v>1</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H82" s="27"/>
       <c r="I82" s="20"/>
@@ -17530,7 +17536,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H83" s="27"/>
       <c r="I83" s="20"/>
@@ -17548,7 +17554,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H84" s="27"/>
       <c r="I84" s="20"/>
@@ -17562,17 +17568,17 @@
         <v>1</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D85" s="24"/>
       <c r="E85" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="G85" s="12" t="s">
         <v>246</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="G85" s="12" t="s">
-        <v>247</v>
       </c>
       <c r="H85" s="27"/>
       <c r="I85" s="20"/>
@@ -17586,13 +17592,13 @@
         <v>1</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D86" s="24"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
       <c r="G86" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H86" s="27"/>
       <c r="I86" s="20"/>
@@ -17606,15 +17612,15 @@
         <v>1</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D87" s="24"/>
       <c r="E87" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H87" s="27"/>
       <c r="I87" s="20"/>
@@ -17648,7 +17654,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
       <c r="G89" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H89" s="27" t="b">
         <f>TRUE()</f>
@@ -17672,7 +17678,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
       <c r="G90" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H90" s="27" t="b">
         <f>TRUE()</f>
@@ -17712,11 +17718,11 @@
       </c>
       <c r="D92" s="24"/>
       <c r="E92" s="8" t="s">
-        <v>258</v>
+        <v>339</v>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H92" s="27"/>
       <c r="I92" s="20"/>
@@ -17750,7 +17756,7 @@
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
       <c r="G94" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H94" s="27" t="b">
         <v>0</v>
@@ -17868,7 +17874,7 @@
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
       <c r="G101" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H101" s="27"/>
       <c r="I101" s="20"/>
@@ -17886,7 +17892,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
       <c r="G102" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H102" s="27"/>
       <c r="I102" s="20"/>
@@ -17916,17 +17922,17 @@
         <v>1</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D104" s="24" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E104" s="8"/>
       <c r="F104" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H104" s="27"/>
       <c r="I104" s="20"/>
@@ -17944,7 +17950,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
       <c r="G105" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H105" s="27"/>
       <c r="I105" s="20"/>
@@ -17962,7 +17968,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
       <c r="G106" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H106" s="27" t="b">
         <f>FALSE()</f>
@@ -18030,15 +18036,15 @@
         <v>1</v>
       </c>
       <c r="C110" s="23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D110" s="24"/>
       <c r="E110" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F110" s="8"/>
       <c r="G110" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H110" s="27"/>
       <c r="I110" s="20"/>
@@ -18072,7 +18078,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
       <c r="G112" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H112" s="27"/>
       <c r="I112" s="20"/>
@@ -18170,7 +18176,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
       <c r="G118" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H118" s="27" t="b">
         <f>TRUE()</f>
@@ -18210,7 +18216,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
       <c r="G120" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H120" s="27"/>
       <c r="I120" s="20"/>
@@ -20197,7 +20203,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I109" xr:uid="{44BD8FFD-EDA1-47AD-AC03-3890015323F4}">
-    <sortState ref="A2:I120">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I120">
       <sortCondition ref="A1:A109"/>
     </sortState>
   </autoFilter>
@@ -20308,28 +20314,28 @@
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -20341,23 +20347,23 @@
         <v>1</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E2" s="28"/>
       <c r="F2" s="28" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G2" s="28">
         <v>0</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I2" s="28" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J2" s="28"/>
     </row>
@@ -20370,7 +20376,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
@@ -20389,7 +20395,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
@@ -20408,23 +20414,23 @@
         <v>1</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G5" s="12">
         <v>0</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J5" s="12"/>
     </row>
@@ -20437,23 +20443,23 @@
         <v>1</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G6" s="12">
         <v>0</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J6" s="12"/>
     </row>
@@ -20466,10 +20472,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -20487,10 +20493,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -20508,10 +20514,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -20529,23 +20535,23 @@
         <v>1</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J10" s="12"/>
     </row>
@@ -20558,21 +20564,21 @@
         <v>1</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J11" s="12"/>
     </row>
@@ -20585,19 +20591,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J12" s="12"/>
     </row>
@@ -20610,23 +20616,23 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G13" s="12">
         <v>0</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J13" s="12"/>
     </row>
@@ -20639,23 +20645,23 @@
         <v>1</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G14" s="12">
         <v>0</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J14" s="12"/>
     </row>
@@ -20668,21 +20674,21 @@
         <v>1</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J15" s="12"/>
     </row>
@@ -20695,25 +20701,25 @@
         <v>1</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>271</v>
-      </c>
       <c r="G16" s="12">
         <v>0</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J16" s="12"/>
     </row>
@@ -20726,23 +20732,23 @@
         <v>1</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J17" s="12"/>
     </row>
@@ -20755,25 +20761,25 @@
         <v>1</v>
       </c>
       <c r="C18" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>271</v>
-      </c>
       <c r="G18" s="12">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J18" s="12"/>
     </row>
@@ -20786,25 +20792,25 @@
         <v>1</v>
       </c>
       <c r="C19" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="F19" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>271</v>
-      </c>
       <c r="G19" s="12">
         <v>0</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J19" s="12"/>
     </row>
@@ -20817,25 +20823,25 @@
         <v>1</v>
       </c>
       <c r="C20" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="F20" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>271</v>
-      </c>
       <c r="G20" s="12">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J20" s="12"/>
     </row>
@@ -20848,23 +20854,23 @@
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G21" s="12">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J21" s="12"/>
     </row>
@@ -20877,23 +20883,23 @@
         <v>1</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G22" s="12">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J22" s="12"/>
     </row>
@@ -20906,23 +20912,23 @@
         <v>1</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G23" s="12">
         <v>0</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J23" s="12"/>
     </row>
@@ -20935,10 +20941,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -20956,10 +20962,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -20977,23 +20983,23 @@
         <v>1</v>
       </c>
       <c r="C26" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="F26" s="12" t="s">
         <v>269</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="E26" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>271</v>
       </c>
       <c r="G26" s="12"/>
       <c r="H26" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J26" s="12"/>
     </row>
@@ -21006,19 +21012,19 @@
         <v>1</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J27" s="12"/>
     </row>
@@ -21031,19 +21037,19 @@
         <v>1</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
       <c r="H28" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J28" s="12"/>
     </row>
@@ -21056,21 +21062,21 @@
         <v>1</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G29" s="12">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J29" s="12"/>
     </row>
@@ -21083,19 +21089,19 @@
         <v>1</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
       <c r="F30" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J30" s="12"/>
     </row>
@@ -21108,19 +21114,19 @@
         <v>1</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J31" s="12"/>
     </row>
@@ -21133,23 +21139,23 @@
         <v>1</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G32" s="12">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J32" s="12"/>
     </row>
@@ -21162,23 +21168,23 @@
         <v>1</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G33" s="12">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J33" s="12"/>
     </row>
@@ -21191,23 +21197,23 @@
         <v>1</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G34" s="12">
         <v>0</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J34" s="12"/>
     </row>
@@ -21220,23 +21226,23 @@
         <v>1</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G35" s="12">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J35" s="12"/>
     </row>
@@ -21249,23 +21255,23 @@
         <v>1</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G36" s="12">
         <v>0</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J36" s="12"/>
     </row>
@@ -21278,23 +21284,23 @@
         <v>1</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G37" s="12">
         <v>0</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J37" s="12"/>
     </row>
@@ -21307,23 +21313,23 @@
         <v>1</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G38" s="12">
         <v>0</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J38" s="12"/>
     </row>
@@ -21336,23 +21342,23 @@
         <v>1</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G39" s="12">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J39" s="12"/>
     </row>
@@ -21365,23 +21371,23 @@
         <v>1</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G40" s="12">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J40" s="12"/>
     </row>
@@ -21394,23 +21400,23 @@
         <v>1</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G41" s="12">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J41" s="12"/>
     </row>
@@ -21423,23 +21429,23 @@
         <v>1</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G42" s="12">
         <v>12</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J42" s="12"/>
     </row>
@@ -21452,23 +21458,23 @@
         <v>1</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G43" s="12">
         <v>12</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J43" s="12"/>
     </row>
@@ -21481,371 +21487,371 @@
         <v>1</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G44" s="12">
         <v>12</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J44" s="12"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="42" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B45" s="46" t="b">
         <f>A45=Metadata!A45</f>
         <v>1</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G45" s="12">
         <v>0</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J45" s="12"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="42" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B46" s="46" t="b">
         <f>A46=Metadata!A46</f>
         <v>1</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G46" s="12">
         <v>0</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J46" s="12"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="42" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B47" s="46" t="b">
         <f>A47=Metadata!A47</f>
         <v>1</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G47" s="12">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J47" s="12"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="42" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B48" s="46" t="b">
         <f>A48=Metadata!A48</f>
         <v>1</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E48" s="12"/>
       <c r="F48" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G48" s="12">
         <v>0</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J48" s="12"/>
     </row>
     <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="42" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B49" s="46" t="b">
         <f>A49=Metadata!A49</f>
         <v>1</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G49" s="12">
         <v>0</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J49" s="12"/>
     </row>
     <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="42" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B50" s="46" t="b">
         <f>A50=Metadata!A50</f>
         <v>1</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G50" s="12">
         <v>0</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J50" s="12"/>
     </row>
     <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="42" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B51" s="46" t="b">
         <f>A51=Metadata!A51</f>
         <v>1</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G51" s="12">
         <v>0</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J51" s="12"/>
     </row>
     <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="42" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B52" s="46" t="b">
         <f>A52=Metadata!A52</f>
         <v>1</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G52" s="12">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J52" s="12"/>
     </row>
     <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="42" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B53" s="46" t="b">
         <f>A53=Metadata!A53</f>
         <v>1</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G53" s="12">
         <v>0</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J53" s="12"/>
     </row>
     <row r="54" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="42" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B54" s="46" t="b">
         <f>A54=Metadata!A54</f>
         <v>1</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G54" s="12">
         <v>12</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J54" s="12"/>
     </row>
     <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="42" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B55" s="46" t="b">
         <f>A55=Metadata!A55</f>
         <v>1</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G55" s="12">
         <v>12</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J55" s="12"/>
     </row>
     <row r="56" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="42" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B56" s="46" t="b">
         <f>A56=Metadata!A56</f>
         <v>1</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G56" s="12">
         <v>12</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J56" s="12"/>
     </row>
@@ -21858,23 +21864,23 @@
         <v>1</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G57" s="12">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J57" s="12"/>
     </row>
@@ -21887,23 +21893,23 @@
         <v>1</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G58" s="12">
         <v>0</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J58" s="12"/>
     </row>
@@ -21916,23 +21922,23 @@
         <v>1</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G59" s="12">
         <v>0</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J59" s="12"/>
     </row>
@@ -21945,23 +21951,23 @@
         <v>1</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G60" s="12">
         <v>0</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J60" s="12"/>
     </row>
@@ -21974,23 +21980,23 @@
         <v>1</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G61" s="12">
         <v>0</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J61" s="12"/>
     </row>
@@ -22003,23 +22009,23 @@
         <v>1</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G62" s="12">
         <v>0</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J62" s="12"/>
     </row>
@@ -22032,23 +22038,23 @@
         <v>1</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G63" s="12">
         <v>0</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J63" s="12"/>
     </row>
@@ -22061,23 +22067,23 @@
         <v>1</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E64" s="12"/>
       <c r="F64" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G64" s="12">
         <v>0</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J64" s="12"/>
     </row>
@@ -22090,23 +22096,23 @@
         <v>1</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G65" s="12">
         <v>0</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J65" s="12"/>
     </row>
@@ -22119,23 +22125,23 @@
         <v>1</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G66" s="12">
         <v>0</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J66" s="12"/>
     </row>
@@ -22148,23 +22154,23 @@
         <v>1</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G67" s="12">
         <v>12</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J67" s="12"/>
     </row>
@@ -22177,23 +22183,23 @@
         <v>1</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G68" s="12">
         <v>12</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J68" s="12"/>
     </row>
@@ -22206,23 +22212,23 @@
         <v>1</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G69" s="12">
         <v>0</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J69" s="12"/>
     </row>
@@ -22235,21 +22241,21 @@
         <v>1</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="12"/>
       <c r="F70" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G70" s="12">
         <v>0</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J70" s="12"/>
     </row>
@@ -22262,10 +22268,10 @@
         <v>1</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12"/>
@@ -22283,19 +22289,19 @@
         <v>1</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
       <c r="G72" s="12"/>
       <c r="H72" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J72" s="12"/>
     </row>
@@ -22308,23 +22314,23 @@
         <v>1</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G73" s="12">
         <v>0</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J73" s="12"/>
     </row>
@@ -22337,23 +22343,23 @@
         <v>1</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G74" s="12">
         <v>0</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J74" s="12"/>
     </row>
@@ -22366,25 +22372,25 @@
         <v>1</v>
       </c>
       <c r="C75" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E75" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="F75" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="G75" s="12">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="E75" s="29" t="s">
-        <v>278</v>
-      </c>
-      <c r="F75" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="G75" s="12">
-        <v>0</v>
-      </c>
-      <c r="H75" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="I75" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J75" s="12"/>
     </row>
@@ -22397,23 +22403,23 @@
         <v>1</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G76" s="12">
         <v>0</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I76" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J76" s="12"/>
     </row>
@@ -22426,21 +22432,21 @@
         <v>1</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G77" s="12"/>
       <c r="H77" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J77" s="12"/>
     </row>
@@ -22453,23 +22459,23 @@
         <v>1</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G78" s="12">
         <v>0</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J78" s="12"/>
     </row>
@@ -22482,23 +22488,23 @@
         <v>1</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G79" s="12">
         <v>0</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J79" s="12"/>
     </row>
@@ -22511,25 +22517,25 @@
         <v>1</v>
       </c>
       <c r="C80" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E80" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="F80" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="G80" s="12">
+        <v>0</v>
+      </c>
+      <c r="H80" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="E80" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="G80" s="12">
-        <v>0</v>
-      </c>
-      <c r="H80" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="I80" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J80" s="12"/>
     </row>
@@ -22542,23 +22548,23 @@
         <v>1</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G81" s="12">
         <v>0</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I81" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J81" s="12"/>
     </row>
@@ -22571,21 +22577,21 @@
         <v>1</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G82" s="12"/>
       <c r="H82" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J82" s="12"/>
     </row>
@@ -22598,23 +22604,23 @@
         <v>1</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G83" s="12">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J83" s="12"/>
     </row>
@@ -22627,23 +22633,23 @@
         <v>1</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E84" s="12"/>
       <c r="F84" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G84" s="12">
         <v>0</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J84" s="12"/>
     </row>
@@ -22656,25 +22662,25 @@
         <v>1</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E85" s="29" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G85" s="12">
         <v>12</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J85" s="12"/>
     </row>
@@ -22687,23 +22693,23 @@
         <v>1</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E86" s="12"/>
       <c r="F86" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G86" s="12">
         <v>0</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I86" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J86" s="12"/>
     </row>
@@ -22716,21 +22722,21 @@
         <v>1</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G87" s="12"/>
       <c r="H87" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J87" s="12"/>
     </row>
@@ -22743,23 +22749,23 @@
         <v>1</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E88" s="12"/>
       <c r="F88" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G88" s="12">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J88" s="12"/>
     </row>
@@ -22772,23 +22778,23 @@
         <v>1</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E89" s="12"/>
       <c r="F89" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G89" s="12">
         <v>0</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I89" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J89" s="12"/>
     </row>
@@ -22801,23 +22807,23 @@
         <v>1</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E90" s="12"/>
       <c r="F90" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G90" s="12">
         <v>0</v>
       </c>
       <c r="H90" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I90" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J90" s="12"/>
     </row>
@@ -22830,17 +22836,17 @@
         <v>1</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D91" s="12"/>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I91" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J91" s="12"/>
     </row>
@@ -22853,23 +22859,23 @@
         <v>1</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E92" s="12"/>
       <c r="F92" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G92" s="12">
         <v>0</v>
       </c>
       <c r="H92" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J92" s="12"/>
     </row>
@@ -22882,10 +22888,10 @@
         <v>1</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -22903,23 +22909,23 @@
         <v>1</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E94" s="12"/>
       <c r="F94" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G94" s="12">
         <v>0</v>
       </c>
       <c r="H94" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J94" s="12"/>
     </row>
@@ -22932,17 +22938,17 @@
         <v>1</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="12"/>
       <c r="F95" s="12"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J95" s="12"/>
     </row>
@@ -22955,7 +22961,7 @@
         <v>1</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="12"/>
@@ -22974,10 +22980,10 @@
         <v>1</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E97" s="12"/>
       <c r="F97" s="12"/>
@@ -22995,10 +23001,10 @@
         <v>1</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E98" s="12"/>
       <c r="F98" s="12"/>
@@ -23016,10 +23022,10 @@
         <v>1</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -23037,19 +23043,19 @@
         <v>1</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J100" s="12"/>
     </row>
@@ -23062,23 +23068,23 @@
         <v>1</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G101" s="12">
         <v>0</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J101" s="12"/>
     </row>
@@ -23091,23 +23097,23 @@
         <v>1</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G102" s="12">
         <v>0</v>
       </c>
       <c r="H102" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J102" s="12"/>
     </row>
@@ -23120,10 +23126,10 @@
         <v>1</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
@@ -23141,23 +23147,23 @@
         <v>1</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G104" s="12">
         <v>0</v>
       </c>
       <c r="H104" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J104" s="12"/>
     </row>
@@ -23170,23 +23176,23 @@
         <v>1</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G105" s="12">
         <v>0</v>
       </c>
       <c r="H105" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J105" s="12">
         <v>1</v>
@@ -23201,23 +23207,23 @@
         <v>1</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E106" s="12"/>
       <c r="F106" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G106" s="8">
         <v>0</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J106" s="12"/>
     </row>
@@ -23231,7 +23237,7 @@
       </c>
       <c r="C107" s="12"/>
       <c r="D107" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E107" s="12"/>
       <c r="F107" s="8"/>
@@ -23249,19 +23255,19 @@
         <v>1</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
       <c r="H108" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J108" s="12"/>
     </row>
@@ -23274,10 +23280,10 @@
         <v>1</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="8"/>
@@ -23295,23 +23301,23 @@
         <v>1</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G110" s="8">
         <v>0</v>
       </c>
       <c r="H110" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J110" s="12"/>
     </row>
@@ -23324,19 +23330,19 @@
         <v>1</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
       <c r="H111" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J111" s="12"/>
     </row>
@@ -23349,17 +23355,17 @@
         <v>1</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D112" s="12"/>
       <c r="E112" s="12"/>
       <c r="F112" s="8"/>
       <c r="G112" s="8"/>
       <c r="H112" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J112" s="12"/>
     </row>
@@ -23372,19 +23378,19 @@
         <v>1</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
       <c r="H113" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J113" s="12"/>
     </row>
@@ -23397,14 +23403,14 @@
         <v>1</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G114" s="8"/>
       <c r="H114" s="12"/>
@@ -23420,7 +23426,7 @@
         <v>1</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D115" s="12"/>
       <c r="E115" s="12"/>
@@ -23439,7 +23445,7 @@
         <v>1</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D116" s="12"/>
       <c r="E116" s="12"/>
@@ -23458,10 +23464,10 @@
         <v>1</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="8"/>
@@ -23479,10 +23485,10 @@
         <v>1</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="8"/>
@@ -23500,10 +23506,10 @@
         <v>1</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E119" s="12"/>
       <c r="F119" s="8"/>
@@ -23521,23 +23527,23 @@
         <v>1</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="G120" s="8">
+        <v>0</v>
+      </c>
+      <c r="H120" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="G120" s="8">
-        <v>0</v>
-      </c>
-      <c r="H120" s="12" t="s">
-        <v>281</v>
-      </c>
       <c r="I120" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J120" s="12"/>
     </row>
@@ -25744,10 +25750,10 @@
         <v>177</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -25755,7 +25761,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C2" s="28"/>
     </row>
@@ -25764,7 +25770,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C3" s="12"/>
     </row>
@@ -25773,7 +25779,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C4" s="12"/>
     </row>
@@ -25782,7 +25788,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -25791,7 +25797,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C6" s="12"/>
     </row>
@@ -25800,7 +25806,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C7" s="12"/>
     </row>
@@ -25809,7 +25815,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C8" s="12"/>
     </row>
@@ -25818,7 +25824,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C9" s="12"/>
     </row>
@@ -25827,7 +25833,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C10" s="12"/>
     </row>
@@ -25836,7 +25842,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C11" s="12"/>
     </row>
@@ -25845,7 +25851,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -25854,7 +25860,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C13" s="12"/>
     </row>
@@ -25863,7 +25869,7 @@
         <v>39</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C14" s="12"/>
     </row>
@@ -25879,16 +25885,16 @@
         <v>45</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C16" s="12"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C17" s="12"/>
     </row>
@@ -25904,7 +25910,7 @@
         <v>50</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C19" s="12"/>
     </row>
@@ -25920,7 +25926,7 @@
         <v>53</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C21" s="12"/>
     </row>
@@ -25929,7 +25935,7 @@
         <v>55</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C22" s="12"/>
     </row>
@@ -25945,7 +25951,7 @@
         <v>59</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C24" s="12"/>
     </row>
@@ -25954,7 +25960,7 @@
         <v>61</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C25" s="12"/>
     </row>
@@ -25963,7 +25969,7 @@
         <v>62</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C26" s="12"/>
     </row>
@@ -25972,7 +25978,7 @@
         <v>63</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C27" s="12"/>
     </row>
@@ -25981,7 +25987,7 @@
         <v>64</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C28" s="12"/>
     </row>
@@ -25990,7 +25996,7 @@
         <v>65</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C29" s="12"/>
     </row>
@@ -25999,7 +26005,7 @@
         <v>67</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C30" s="12"/>
     </row>
@@ -26008,7 +26014,7 @@
         <v>69</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C31" s="12"/>
     </row>
@@ -26017,7 +26023,7 @@
         <v>70</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C32" s="12"/>
     </row>
@@ -26026,7 +26032,7 @@
         <v>72</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C33" s="12"/>
     </row>
@@ -26035,7 +26041,7 @@
         <v>73</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C34" s="12"/>
     </row>
@@ -26044,7 +26050,7 @@
         <v>75</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C35" s="12"/>
     </row>
@@ -26060,7 +26066,7 @@
         <v>77</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C37" s="12"/>
     </row>
@@ -26069,7 +26075,7 @@
         <v>78</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C38" s="12"/>
     </row>
@@ -26078,7 +26084,7 @@
         <v>79</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C39" s="12"/>
     </row>
@@ -26094,7 +26100,7 @@
         <v>81</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C41" s="12"/>
     </row>
@@ -26103,7 +26109,7 @@
         <v>82</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C42" s="12"/>
     </row>
@@ -26112,7 +26118,7 @@
         <v>83</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C43" s="12"/>
     </row>
@@ -26219,7 +26225,7 @@
         <v>99</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C58" s="12"/>
     </row>
@@ -26228,7 +26234,7 @@
         <v>100</v>
       </c>
       <c r="B59" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C59" s="12"/>
     </row>
@@ -26237,7 +26243,7 @@
         <v>101</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C60" s="12"/>
     </row>
@@ -26246,7 +26252,7 @@
         <v>102</v>
       </c>
       <c r="B61" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C61" s="12"/>
     </row>
@@ -26255,7 +26261,7 @@
         <v>104</v>
       </c>
       <c r="B62" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C62" s="12"/>
     </row>
@@ -26264,7 +26270,7 @@
         <v>105</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C63" s="12"/>
     </row>
@@ -26273,7 +26279,7 @@
         <v>106</v>
       </c>
       <c r="B64" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C64" s="12"/>
     </row>
@@ -26282,7 +26288,7 @@
         <v>109</v>
       </c>
       <c r="B65" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C65" s="12"/>
     </row>
@@ -26291,7 +26297,7 @@
         <v>111</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C66" s="12"/>
     </row>
@@ -26300,7 +26306,7 @@
         <v>112</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C67" s="12"/>
     </row>
@@ -26309,7 +26315,7 @@
         <v>113</v>
       </c>
       <c r="B68" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C68" s="12"/>
     </row>
@@ -26318,7 +26324,7 @@
         <v>114</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C69" s="12"/>
     </row>
@@ -26327,7 +26333,7 @@
         <v>115</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C70" s="12"/>
     </row>
@@ -26336,7 +26342,7 @@
         <v>116</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C71" s="12"/>
     </row>
@@ -26345,7 +26351,7 @@
         <v>117</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C72" s="12"/>
     </row>
@@ -26354,7 +26360,7 @@
         <v>118</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C73" s="12"/>
     </row>
@@ -26363,7 +26369,7 @@
         <v>119</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C74" s="12"/>
     </row>
@@ -26372,7 +26378,7 @@
         <v>120</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C75" s="12"/>
     </row>
@@ -26381,7 +26387,7 @@
         <v>121</v>
       </c>
       <c r="B76" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C76" s="12"/>
     </row>
@@ -26390,7 +26396,7 @@
         <v>123</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C77" s="12"/>
     </row>
@@ -26399,7 +26405,7 @@
         <v>126</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C78" s="12"/>
     </row>
@@ -26408,7 +26414,7 @@
         <v>127</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C79" s="12"/>
     </row>
@@ -26417,7 +26423,7 @@
         <v>128</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C80" s="12"/>
     </row>
@@ -26426,7 +26432,7 @@
         <v>131</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C81" s="12"/>
     </row>
@@ -26435,7 +26441,7 @@
         <v>132</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C82" s="12"/>
     </row>
@@ -26444,7 +26450,7 @@
         <v>133</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C83" s="12"/>
     </row>
@@ -26453,7 +26459,7 @@
         <v>135</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C84" s="12"/>
     </row>
@@ -26462,7 +26468,7 @@
         <v>136</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C85" s="12"/>
     </row>
@@ -26471,7 +26477,7 @@
         <v>138</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C86" s="12"/>
     </row>
@@ -26480,7 +26486,7 @@
         <v>139</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C87" s="12"/>
     </row>
@@ -26489,7 +26495,7 @@
         <v>140</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C88" s="12"/>
     </row>
@@ -26498,7 +26504,7 @@
         <v>142</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C89" s="12"/>
     </row>
@@ -26507,7 +26513,7 @@
         <v>144</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C90" s="12"/>
     </row>
@@ -26516,7 +26522,7 @@
         <v>146</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C91" s="12"/>
     </row>
@@ -26525,7 +26531,7 @@
         <v>148</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C92" s="12"/>
     </row>
@@ -26534,7 +26540,7 @@
         <v>150</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C93" s="12"/>
     </row>
@@ -26543,7 +26549,7 @@
         <v>152</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C94" s="12"/>
     </row>
@@ -26552,7 +26558,7 @@
         <v>154</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C95" s="12"/>
     </row>
@@ -26561,7 +26567,7 @@
         <v>156</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C96" s="12"/>
     </row>
@@ -26570,7 +26576,7 @@
         <v>158</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C97" s="12"/>
     </row>
@@ -26579,7 +26585,7 @@
         <v>160</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C98" s="12"/>
     </row>
@@ -26588,7 +26594,7 @@
         <v>162</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C99" s="12"/>
     </row>
@@ -26597,7 +26603,7 @@
         <v>110</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C100" s="12"/>
     </row>
@@ -26606,7 +26612,7 @@
         <v>165</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C101" s="12"/>
     </row>
@@ -26615,7 +26621,7 @@
         <v>167</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C102" s="12"/>
     </row>
@@ -26624,7 +26630,7 @@
         <v>168</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C103" s="12"/>
     </row>
@@ -26633,7 +26639,7 @@
         <v>169</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C104" s="12"/>
     </row>
@@ -26642,7 +26648,7 @@
         <v>170</v>
       </c>
       <c r="B105" s="32" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C105" s="12"/>
     </row>
@@ -26651,7 +26657,7 @@
         <v>171</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C106" s="12"/>
     </row>
@@ -26660,7 +26666,7 @@
         <v>172</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C107" s="12"/>
     </row>
@@ -26669,7 +26675,7 @@
         <v>174</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C108" s="12"/>
     </row>
@@ -26786,13 +26792,13 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>45960.506171875</v>
+        <v>45967.468476851849</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.natsikas\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanos\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA4ACF1-EE57-4CCA-ACF0-5BE54D9362BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF703AC-3EC3-4CEA-80C2-544837132E58}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,19 +26,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Read Settings'!$A$1:$I$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Time Settings'!$A$1:$J$120</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -1209,7 +1198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="342">
   <si>
     <t>Report Name</t>
   </si>
@@ -2233,6 +2222,12 @@
   </si>
   <si>
     <t>{'FYROM':'NORTH MACEDONIA', 'CET Hour': 'Hour (CET)'}</t>
+  </si>
+  <si>
+    <t>{'ΝΕΤ CBS SCHEDULES': 'NET CBS SCHEDULES'}</t>
+  </si>
+  <si>
+    <t>IMBABE.csv</t>
   </si>
 </sst>
 </file>
@@ -3680,9 +3675,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3720,7 +3715,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3826,7 +3821,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3968,7 +3963,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -10657,7 +10652,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L120" xr:uid="{D0972C50-907B-4A2C-82F0-ED51F06329AA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L120">
+    <sortState ref="A2:L120">
       <sortCondition ref="A2:A120"/>
     </sortState>
   </autoFilter>
@@ -15684,7 +15679,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I111" xr:uid="{776C4DE2-2957-440A-A09D-B0AB3152981D}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I120">
+    <sortState ref="A2:I120">
       <sortCondition ref="A1:A111"/>
     </sortState>
   </autoFilter>
@@ -15980,7 +15975,9 @@
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="F11" s="8" t="s">
+        <v>340</v>
+      </c>
       <c r="G11" s="12" t="s">
         <v>246</v>
       </c>
@@ -17278,7 +17275,9 @@
         <v>1</v>
       </c>
       <c r="C70" s="23"/>
-      <c r="D70" s="24"/>
+      <c r="D70" s="24" t="s">
+        <v>341</v>
+      </c>
       <c r="E70" s="23"/>
       <c r="F70" s="8"/>
       <c r="G70" s="12" t="s">
@@ -20203,7 +20202,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I109" xr:uid="{44BD8FFD-EDA1-47AD-AC03-3890015323F4}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I120">
+    <sortState ref="A2:I120">
       <sortCondition ref="A1:A109"/>
     </sortState>
   </autoFilter>
@@ -26798,7 +26797,7 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>45967.468476851849</v>
+        <v>46134.461413425925</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanos\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF703AC-3EC3-4CEA-80C2-544837132E58}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AB93B1-9F52-48A5-BCE8-607A8E2AA959}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,7 +69,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{0C07F9CF-50DA-48C6-BF10-24C4FC2A23BC}">
+    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -93,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -118,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="F24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -168,7 +168,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -193,7 +193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
+    <comment ref="G26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -218,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="F27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -243,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="F29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -268,7 +268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="F31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -293,7 +293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
+    <comment ref="G32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -318,7 +318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -343,7 +343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F72" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="F72" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -368,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F100" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="F100" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -393,7 +393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="F101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -422,7 +422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="F102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -451,7 +451,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="F104" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -476,7 +476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F105" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="F105" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -501,7 +501,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
+    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
         <r>
           <rPr>
@@ -527,7 +527,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
         <r>
           <rPr>
@@ -552,7 +552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
       <text>
         <r>
           <rPr>
@@ -577,7 +577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
       <text>
         <r>
           <rPr>
@@ -612,7 +612,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -637,7 +637,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -662,7 +662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -693,7 +693,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -718,7 +718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -744,7 +744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -769,7 +769,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -786,7 +786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
+    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1008,7 +1008,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1035,7 +1035,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -1052,7 +1052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="F26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1077,7 +1077,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G84" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
+    <comment ref="G84" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1092,7 +1092,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J87" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
+    <comment ref="J87" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1117,7 +1117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="F101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1134,7 +1134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="F102" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1151,7 +1151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F105" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="F105" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1176,7 +1176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
+    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -2799,6 +2799,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
@@ -2939,13 +2953,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
@@ -2961,13 +2968,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3212,6 +3212,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
@@ -3220,20 +3234,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3281,21 +3281,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3344,6 +3344,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
@@ -3359,13 +3366,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3414,6 +3414,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
@@ -3429,13 +3436,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3519,14 +3519,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF99"/>
+          <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF93CDDD"/>
+          <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3568,6 +3568,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
@@ -3576,20 +3590,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -10651,25 +10651,25 @@
       <c r="L300" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L120" xr:uid="{D0972C50-907B-4A2C-82F0-ED51F06329AA}">
+  <autoFilter ref="A1:L120" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState ref="A2:L120">
       <sortCondition ref="A2:A120"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A103">
-    <cfRule type="expression" dxfId="114" priority="117">
+    <cfRule type="expression" dxfId="114" priority="116">
+      <formula>COLUMN()=CELL("col")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="117">
       <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="116">
-      <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104">
-    <cfRule type="expression" dxfId="112" priority="113">
+    <cfRule type="expression" dxfId="112" priority="112">
+      <formula>ROW()=CELL("row")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="111" priority="113">
       <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="111" priority="112">
-      <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A106">
@@ -10694,11 +10694,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102:C102">
-    <cfRule type="expression" dxfId="105" priority="153">
+    <cfRule type="expression" dxfId="105" priority="152">
+      <formula>COLUMN()=CELL("col")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="153">
       <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="104" priority="152">
-      <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102:C104">
@@ -10753,19 +10753,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B103:C104">
-    <cfRule type="expression" dxfId="92" priority="123">
+    <cfRule type="expression" dxfId="92" priority="122">
+      <formula>COLUMN()=CELL("col")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="91" priority="123">
       <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="122">
-      <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B106:C107">
-    <cfRule type="expression" dxfId="90" priority="72">
+    <cfRule type="expression" dxfId="90" priority="71">
+      <formula>COLUMN()=CELL("col")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="72">
       <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="71">
-      <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78:D82">
@@ -10799,19 +10799,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:H107">
-    <cfRule type="expression" dxfId="82" priority="2">
+    <cfRule type="expression" dxfId="82" priority="1">
+      <formula>ROW()=CELL("row")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="2">
       <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="1">
-      <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112:H120 F121:I300">
-    <cfRule type="expression" dxfId="80" priority="36">
+    <cfRule type="expression" dxfId="80" priority="35">
+      <formula>ROW()=CELL("row")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="36">
       <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="35">
-      <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:I2 I3:I120 A108:H111">
@@ -10845,11 +10845,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J300">
-    <cfRule type="cellIs" dxfId="72" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="33" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="34" operator="equal">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="33" operator="equal">
-      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L98 K108:L111">
@@ -10883,19 +10883,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K100:L100">
-    <cfRule type="expression" dxfId="64" priority="174">
+    <cfRule type="expression" dxfId="64" priority="166">
+      <formula>ROW()=CELL("row")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="174">
       <formula>COLUMN()=CELL("col")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="166">
-      <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K101:L101">
-    <cfRule type="expression" dxfId="62" priority="190">
+    <cfRule type="expression" dxfId="62" priority="189">
+      <formula>COLUMN()=CELL("col")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="190">
       <formula>ROW()=CELL("row")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="189">
-      <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K102:L102">
@@ -10959,13 +10959,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K112:L300">
-    <cfRule type="expression" dxfId="46" priority="47">
+    <cfRule type="expression" dxfId="46" priority="38">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="45" priority="46">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="38">
+    <cfRule type="expression" dxfId="44" priority="47">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15678,7 +15678,7 @@
       <c r="I300" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I111" xr:uid="{776C4DE2-2957-440A-A09D-B0AB3152981D}">
+  <autoFilter ref="A1:I111" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <sortState ref="A2:I120">
       <sortCondition ref="A1:A111"/>
     </sortState>
@@ -15766,7 +15766,7 @@
   <cols>
     <col min="1" max="2" width="34.5546875" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" style="1" customWidth="1"/>
     <col min="5" max="6" width="16.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" customWidth="1"/>
@@ -17751,8 +17751,7 @@
         <v>1</v>
       </c>
       <c r="C94" s="23"/>
-      <c r="D94" s="24"/>
-      <c r="E94" s="8"/>
+      <c r="E94" s="24"/>
       <c r="F94" s="8"/>
       <c r="G94" s="12" t="s">
         <v>247</v>
@@ -20201,86 +20200,86 @@
       <c r="I300" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I109" xr:uid="{44BD8FFD-EDA1-47AD-AC03-3890015323F4}">
+  <autoFilter ref="A1:I109" xr:uid="{00000000-0009-0000-0000-000002000000}">
     <sortState ref="A2:I120">
       <sortCondition ref="A1:A109"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A77:A86">
-    <cfRule type="expression" dxfId="28" priority="50">
+  <conditionalFormatting sqref="A77:A86 C64:E93 C94 E94">
+    <cfRule type="expression" dxfId="1" priority="50">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:A300">
-    <cfRule type="expression" dxfId="27" priority="11">
+    <cfRule type="expression" dxfId="28" priority="11">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B300">
-    <cfRule type="expression" dxfId="26" priority="9">
+    <cfRule type="expression" dxfId="27" priority="9">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="10">
+    <cfRule type="expression" dxfId="26" priority="10">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C82:C88">
-    <cfRule type="expression" dxfId="24" priority="21">
+    <cfRule type="expression" dxfId="25" priority="21">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95:H300">
-    <cfRule type="expression" dxfId="23" priority="3">
+    <cfRule type="expression" dxfId="24" priority="3">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="4">
+    <cfRule type="expression" dxfId="23" priority="4">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:I2 C3:F63 G56:H68 I56:I81 F64:F68 C64:E94 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94 A1:I1">
-    <cfRule type="expression" dxfId="21" priority="20">
+  <conditionalFormatting sqref="C2:I2 C3:F63 G56:H68 I56:I81 F64:F68 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94 A1:I1 C64:E93 C94 E94">
+    <cfRule type="expression" dxfId="0" priority="20">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:I2 C3:F63 G56:H68 I56:I81 F64:F68 C64:E94 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94">
-    <cfRule type="expression" dxfId="20" priority="19">
+  <conditionalFormatting sqref="C2:I2 C3:F63 G56:H68 I56:I81 F64:F68 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94">
+    <cfRule type="expression" dxfId="22" priority="19">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D25:F25">
-    <cfRule type="expression" dxfId="19" priority="22">
+    <cfRule type="expression" dxfId="21" priority="22">
       <formula>OR(ROW()=CELL("row"),col()=CELL("col"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G81">
-    <cfRule type="expression" dxfId="18" priority="106">
+    <cfRule type="expression" dxfId="20" priority="106">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="107">
+    <cfRule type="expression" dxfId="19" priority="107">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:I55">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H94:I94">
-    <cfRule type="expression" dxfId="14" priority="36">
+    <cfRule type="expression" dxfId="16" priority="36">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="37">
+    <cfRule type="expression" dxfId="15" priority="37">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H95:I300">
-    <cfRule type="expression" dxfId="12" priority="7">
+    <cfRule type="expression" dxfId="14" priority="7">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="8">
+    <cfRule type="expression" dxfId="13" priority="8">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21039,7 +21038,7 @@
         <v>279</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
@@ -21141,7 +21140,7 @@
         <v>279</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12" t="s">
@@ -22890,7 +22889,7 @@
         <v>285</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="E93" s="12"/>
       <c r="F93" s="12"/>
@@ -23257,7 +23256,7 @@
         <v>279</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="8"/>
@@ -23282,7 +23281,7 @@
         <v>279</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="8"/>
@@ -23332,7 +23331,7 @@
         <v>279</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="8"/>
@@ -23529,7 +23528,7 @@
         <v>274</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="E120" s="12"/>
       <c r="F120" s="8" t="s">
@@ -25708,22 +25707,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A88:A300">
-    <cfRule type="expression" dxfId="10" priority="12">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:J300">
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:J300">
-    <cfRule type="expression" dxfId="8" priority="36">
+    <cfRule type="expression" dxfId="10" priority="36">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E300">
-    <cfRule type="expression" dxfId="7" priority="9">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26739,35 +26738,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A108">
-    <cfRule type="expression" dxfId="6" priority="11">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="12">
+    <cfRule type="expression" dxfId="7" priority="12">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A77:A86">
-    <cfRule type="expression" dxfId="4" priority="13">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:A108">
-    <cfRule type="expression" dxfId="3" priority="18">
+    <cfRule type="expression" dxfId="5" priority="18">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112:A116">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C80 B81:B108 C81:C110 B106:C116 A109:B111 A112:C121">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C80 B81:B108 C81:C111 A109:B111 A112:C121 A1:C1">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26797,7 +26796,7 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>46134.461413425925</v>
+        <v>46199.074578703701</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanos\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AB93B1-9F52-48A5-BCE8-607A8E2AA959}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51EDC53-DD0A-464C-B7AB-CAB29306852F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1198,7 +1198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="343">
   <si>
     <t>Report Name</t>
   </si>
@@ -2228,6 +2228,9 @@
   </si>
   <si>
     <t>IMBABE.csv</t>
+  </si>
+  <si>
+    <t>HEnEx_ResultsSummary.csv</t>
   </si>
 </sst>
 </file>
@@ -2785,14 +2788,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF99"/>
+          <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF93CDDD"/>
+          <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2939,13 +2942,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF93CDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF99"/>
         </patternFill>
       </fill>
@@ -2968,6 +2964,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF93CDDD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4589,16 +4592,14 @@
       <c r="F18" s="40">
         <v>44136</v>
       </c>
-      <c r="G18" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G18" s="47"/>
       <c r="H18" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I18" s="7" t="b">
         <f>IF(Metadata!G18="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="13" t="b">
         <f>TRUE()</f>
@@ -4659,16 +4660,14 @@
       <c r="F20" s="40">
         <v>44136</v>
       </c>
-      <c r="G20" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G20" s="47"/>
       <c r="H20" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I20" s="7" t="b">
         <f>IF(Metadata!G20="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="13" t="b">
         <f>TRUE()</f>
@@ -5569,16 +5568,14 @@
       <c r="F46" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="G46" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G46" s="47"/>
       <c r="H46" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I46" s="7" t="b">
         <f>IF(Metadata!G46="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="13" t="b">
         <f>TRUE()</f>
@@ -5637,16 +5634,14 @@
       <c r="F48" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="G48" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G48" s="47"/>
       <c r="H48" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I48" s="7" t="b">
         <f>IF(Metadata!G48="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="13" t="b">
         <f>TRUE()</f>
@@ -5705,16 +5700,14 @@
       <c r="F50" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="G50" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G50" s="47"/>
       <c r="H50" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I50" s="7" t="b">
         <f>IF(Metadata!G50="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="13" t="b">
         <f>TRUE()</f>
@@ -5773,16 +5766,14 @@
       <c r="F52" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="G52" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G52" s="47"/>
       <c r="H52" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I52" s="7" t="b">
         <f>IF(Metadata!G52="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="13" t="b">
         <f>TRUE()</f>
@@ -5841,16 +5832,14 @@
       <c r="F54" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="G54" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G54" s="47"/>
       <c r="H54" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I54" s="7" t="b">
         <f>IF(Metadata!G54="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="13" t="b">
         <f>TRUE()</f>
@@ -5909,16 +5898,14 @@
       <c r="F56" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="G56" s="47">
-        <v>45930</v>
-      </c>
+      <c r="G56" s="47"/>
       <c r="H56" s="8" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I56" s="7" t="b">
         <f>IF(Metadata!G56="",TRUE(),FALSE())</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="13" t="b">
         <f>TRUE()</f>
@@ -11437,9 +11424,7 @@
       <c r="H20" s="12">
         <v>1</v>
       </c>
-      <c r="I20" s="12" t="s">
-        <v>202</v>
-      </c>
+      <c r="I20" s="12"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="42" t="s">
@@ -12087,9 +12072,7 @@
       <c r="H48" s="12">
         <v>1</v>
       </c>
-      <c r="I48" s="12" t="s">
-        <v>202</v>
-      </c>
+      <c r="I48" s="12"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
@@ -12187,9 +12170,7 @@
       <c r="H52" s="12">
         <v>1</v>
       </c>
-      <c r="I52" s="12" t="s">
-        <v>202</v>
-      </c>
+      <c r="I52" s="12"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
@@ -12287,9 +12268,7 @@
       <c r="H56" s="12">
         <v>1</v>
       </c>
-      <c r="I56" s="12" t="s">
-        <v>202</v>
-      </c>
+      <c r="I56" s="12"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="42" t="s">
@@ -16179,7 +16158,9 @@
         <v>249</v>
       </c>
       <c r="D20" s="24"/>
-      <c r="E20" s="14"/>
+      <c r="E20" s="14" t="s">
+        <v>342</v>
+      </c>
       <c r="F20" s="8"/>
       <c r="G20" s="12" t="s">
         <v>246</v>
@@ -16774,7 +16755,9 @@
         <v>249</v>
       </c>
       <c r="D48" s="24"/>
-      <c r="E48" s="8"/>
+      <c r="E48" s="14" t="s">
+        <v>342</v>
+      </c>
       <c r="F48" s="8"/>
       <c r="G48" s="12" t="s">
         <v>246</v>
@@ -16866,7 +16849,9 @@
         <v>249</v>
       </c>
       <c r="D52" s="12"/>
-      <c r="E52" s="8"/>
+      <c r="E52" s="14" t="s">
+        <v>342</v>
+      </c>
       <c r="F52" s="8"/>
       <c r="G52" s="12" t="s">
         <v>246</v>
@@ -16958,7 +16943,9 @@
         <v>249</v>
       </c>
       <c r="D56" s="12"/>
-      <c r="E56" s="8"/>
+      <c r="E56" s="14" t="s">
+        <v>342</v>
+      </c>
       <c r="F56" s="8"/>
       <c r="G56" s="12" t="s">
         <v>246</v>
@@ -20206,43 +20193,43 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A77:A86 C64:E93 C94 E94">
-    <cfRule type="expression" dxfId="1" priority="50">
+    <cfRule type="expression" dxfId="28" priority="50">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:A300">
-    <cfRule type="expression" dxfId="28" priority="11">
+    <cfRule type="expression" dxfId="27" priority="11">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B300">
-    <cfRule type="expression" dxfId="27" priority="9">
+    <cfRule type="expression" dxfId="26" priority="9">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="10">
+    <cfRule type="expression" dxfId="25" priority="10">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C82:C88">
-    <cfRule type="expression" dxfId="25" priority="21">
+    <cfRule type="expression" dxfId="24" priority="21">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95:H300">
-    <cfRule type="expression" dxfId="24" priority="3">
+    <cfRule type="expression" dxfId="23" priority="3">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="4">
+    <cfRule type="expression" dxfId="22" priority="4">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:I2 C3:F63 G56:H68 I56:I81 F64:F68 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94 A1:I1 C64:E93 C94 E94">
-    <cfRule type="expression" dxfId="0" priority="20">
+  <conditionalFormatting sqref="C2:I2 G56:H68 I56:I81 F64:F68 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94 A1:I1 C64:E93 C94 E94 C3:F63">
+    <cfRule type="expression" dxfId="1" priority="20">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:I2 C3:F63 G56:H68 I56:I81 F64:F68 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94">
-    <cfRule type="expression" dxfId="22" priority="19">
+  <conditionalFormatting sqref="C2:I2 G56:H68 I56:I81 F64:F68 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94 C3:F63">
+    <cfRule type="expression" dxfId="0" priority="19">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26796,7 +26783,7 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>46199.074578703701</v>
+        <v>46237.523952546297</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanos\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C05CFF8-ABB7-49DC-A4F6-4E61272A5F70}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85816B1-3204-4A01-A3E5-6827900267A5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -2795,26 +2795,6 @@
   </cellStyles>
   <dxfs count="115">
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF99"/>
@@ -3308,6 +3288,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7400,8 +7400,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="13" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" s="14" t="s">
         <v>141</v>
@@ -8085,7 +8084,7 @@
         <v>1</v>
       </c>
       <c r="J120" s="13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K120" s="14" t="s">
         <v>175</v>
@@ -10807,127 +10806,127 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J300">
-    <cfRule type="cellIs" dxfId="1" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="34" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="33" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L98 K108:L111">
-    <cfRule type="expression" dxfId="72" priority="386">
+    <cfRule type="expression" dxfId="70" priority="386">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:L99">
-    <cfRule type="expression" dxfId="71" priority="205">
+    <cfRule type="expression" dxfId="69" priority="205">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78:L81">
-    <cfRule type="expression" dxfId="70" priority="387">
+    <cfRule type="expression" dxfId="68" priority="387">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K88:L98 K108:L111">
-    <cfRule type="expression" dxfId="69" priority="388">
+    <cfRule type="expression" dxfId="67" priority="388">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:L99">
-    <cfRule type="expression" dxfId="68" priority="204">
+    <cfRule type="expression" dxfId="66" priority="204">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:L101">
-    <cfRule type="expression" dxfId="67" priority="175">
+    <cfRule type="expression" dxfId="65" priority="175">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K100:L100">
-    <cfRule type="expression" dxfId="66" priority="174">
+    <cfRule type="expression" dxfId="64" priority="174">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="166">
+    <cfRule type="expression" dxfId="63" priority="166">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K101:L101">
-    <cfRule type="expression" dxfId="64" priority="190">
+    <cfRule type="expression" dxfId="62" priority="190">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="189">
+    <cfRule type="expression" dxfId="61" priority="189">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K102:L102">
-    <cfRule type="expression" dxfId="62" priority="159">
+    <cfRule type="expression" dxfId="60" priority="159">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="160">
+    <cfRule type="expression" dxfId="59" priority="160">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K102:L104">
-    <cfRule type="expression" dxfId="60" priority="130">
+    <cfRule type="expression" dxfId="58" priority="130">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K103:L103">
-    <cfRule type="expression" dxfId="59" priority="121">
+    <cfRule type="expression" dxfId="57" priority="121">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="129">
+    <cfRule type="expression" dxfId="56" priority="129">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K104:L104">
-    <cfRule type="expression" dxfId="57" priority="144">
+    <cfRule type="expression" dxfId="55" priority="144">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="145">
+    <cfRule type="expression" dxfId="54" priority="145">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K105:L105">
-    <cfRule type="expression" dxfId="55" priority="105">
+    <cfRule type="expression" dxfId="53" priority="105">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="106">
+    <cfRule type="expression" dxfId="52" priority="106">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K105:L107">
-    <cfRule type="expression" dxfId="53" priority="78">
+    <cfRule type="expression" dxfId="51" priority="78">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K106:L106">
-    <cfRule type="expression" dxfId="52" priority="70">
+    <cfRule type="expression" dxfId="50" priority="70">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="77">
+    <cfRule type="expression" dxfId="49" priority="77">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107:L107">
-    <cfRule type="expression" dxfId="50" priority="91">
+    <cfRule type="expression" dxfId="48" priority="91">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K107:L111">
-    <cfRule type="expression" dxfId="49" priority="92">
+    <cfRule type="expression" dxfId="47" priority="92">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K112:L300">
-    <cfRule type="expression" dxfId="48" priority="47">
+    <cfRule type="expression" dxfId="46" priority="47">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="46">
+    <cfRule type="expression" dxfId="45" priority="46">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="38">
+    <cfRule type="expression" dxfId="44" priority="38">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15654,71 +15653,71 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A61">
-    <cfRule type="expression" dxfId="45" priority="11">
+    <cfRule type="expression" dxfId="43" priority="11">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:A106 C88:E106">
-    <cfRule type="expression" dxfId="44" priority="32">
+    <cfRule type="expression" dxfId="42" priority="32">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:D61 F61:H61">
-    <cfRule type="expression" dxfId="43" priority="3">
+    <cfRule type="expression" dxfId="41" priority="3">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="4">
+    <cfRule type="expression" dxfId="40" priority="4">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:I1">
-    <cfRule type="expression" dxfId="41" priority="16">
+    <cfRule type="expression" dxfId="39" priority="16">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:I60 A62:I109">
-    <cfRule type="expression" dxfId="40" priority="30">
+    <cfRule type="expression" dxfId="38" priority="30">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:I60 C1:E60 A62:I109">
-    <cfRule type="expression" dxfId="39" priority="29">
+    <cfRule type="expression" dxfId="37" priority="29">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110:I300">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="2">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90">
-    <cfRule type="expression" dxfId="36" priority="114">
+    <cfRule type="expression" dxfId="34" priority="114">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E106">
-    <cfRule type="expression" dxfId="35" priority="5">
+    <cfRule type="expression" dxfId="33" priority="5">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61">
-    <cfRule type="expression" dxfId="34" priority="6">
+    <cfRule type="expression" dxfId="32" priority="6">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25">
-    <cfRule type="expression" dxfId="33" priority="17">
+    <cfRule type="expression" dxfId="31" priority="17">
       <formula>OR(ROW()=CELL("row"),col()=CELL("col"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H61:I61">
-    <cfRule type="expression" dxfId="32" priority="7">
+    <cfRule type="expression" dxfId="30" priority="7">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="8">
+    <cfRule type="expression" dxfId="29" priority="8">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20178,80 +20177,80 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A88:A300">
-    <cfRule type="expression" dxfId="30" priority="11">
+    <cfRule type="expression" dxfId="28" priority="11">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B300">
-    <cfRule type="expression" dxfId="29" priority="9">
+    <cfRule type="expression" dxfId="27" priority="9">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="10">
+    <cfRule type="expression" dxfId="26" priority="10">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C82:C88">
-    <cfRule type="expression" dxfId="27" priority="21">
+    <cfRule type="expression" dxfId="25" priority="21">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C64:E93 C94 E94 A77:A86">
-    <cfRule type="expression" dxfId="26" priority="50">
+    <cfRule type="expression" dxfId="24" priority="50">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95:H300">
-    <cfRule type="expression" dxfId="25" priority="3">
+    <cfRule type="expression" dxfId="23" priority="3">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="4">
+    <cfRule type="expression" dxfId="22" priority="4">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:I2 C3:F63 G56:H68 I56:I81 F64:F68 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94 A1:I1 C64:E93 C94 E94">
-    <cfRule type="expression" dxfId="23" priority="20">
+    <cfRule type="expression" dxfId="21" priority="20">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:I2 C3:F63 G56:H68 I56:I81 F64:F68 F69:H74 G75:H81 F75:F94 G82:I93 G94:H94">
-    <cfRule type="expression" dxfId="22" priority="19">
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D25:F25">
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="19" priority="22">
       <formula>OR(ROW()=CELL("row"),col()=CELL("col"))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G81">
-    <cfRule type="expression" dxfId="20" priority="106">
+    <cfRule type="expression" dxfId="18" priority="106">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="107">
+    <cfRule type="expression" dxfId="17" priority="107">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:I55">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H94:I94">
-    <cfRule type="expression" dxfId="16" priority="36">
+    <cfRule type="expression" dxfId="14" priority="36">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="37">
+    <cfRule type="expression" dxfId="13" priority="37">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H95:I300">
-    <cfRule type="expression" dxfId="14" priority="7">
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="8">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25681,22 +25680,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A88:A300">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:J300">
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:J300">
-    <cfRule type="expression" dxfId="10" priority="36">
+    <cfRule type="expression" dxfId="8" priority="36">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E300">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26712,35 +26711,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A108">
-    <cfRule type="expression" dxfId="8" priority="11">
+    <cfRule type="expression" dxfId="6" priority="11">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="12">
+    <cfRule type="expression" dxfId="5" priority="12">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A77:A86">
-    <cfRule type="expression" dxfId="6" priority="13">
+    <cfRule type="expression" dxfId="4" priority="13">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A88:A108">
-    <cfRule type="expression" dxfId="5" priority="18">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112:A116">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C80 B81:B108 C81:C110 B106:C116 A109:B111 A112:C121">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C80 B81:B108 C81:C111 A109:B111 A112:C121 A1:C1">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>COLUMN()=CELL("col")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26770,7 +26769,7 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>46240.675889467595</v>
+        <v>46241.771665046297</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">

--- a/exso/Files/ReportsInfo.xlsx
+++ b/exso/Files/ReportsInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanos\Desktop\Admie-Desktop\Projects\exso\exso\exso\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85816B1-3204-4A01-A3E5-6827900267A5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2946D9B0-5B5F-4F59-86A8-D17D13F89EF9}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5083,8 +5083,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="13" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="14"/>
       <c r="L32" s="15"/>
@@ -26769,7 +26768,7 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <f ca="1">NOW()</f>
-        <v>46241.771665046297</v>
+        <v>46241.794534837965</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
